--- a/VerveStacks_BRA_grids/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA_grids/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CAAB0777-2185-4A4A-8FE6-89685CC1B0F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3EE27490-5D61-4863-8D38-02CF10F98F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2702041D-9390-4D8B-964B-3E71BF36335F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{178120FA-7AF6-4C47-B1FB-E27AAF499F8F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -81,24 +81,78 @@
     <t>bioenergy</t>
   </si>
   <si>
+    <t>e_BR487-500</t>
+  </si>
+  <si>
+    <t>e_BR630-440</t>
+  </si>
+  <si>
+    <t>e_BR579-500</t>
+  </si>
+  <si>
+    <t>e_BR515-500</t>
+  </si>
+  <si>
+    <t>e_BR663-440</t>
+  </si>
+  <si>
+    <t>e_BR650-440</t>
+  </si>
+  <si>
+    <t>e_BR657-440</t>
+  </si>
+  <si>
+    <t>e_BR624-440</t>
+  </si>
+  <si>
+    <t>e_BR141-500</t>
+  </si>
+  <si>
+    <t>e_BR629-500</t>
+  </si>
+  <si>
     <t>e_BR292-500</t>
   </si>
   <si>
+    <t>e_BR662-440</t>
+  </si>
+  <si>
+    <t>e_BR984-525</t>
+  </si>
+  <si>
+    <t>e_BR621-440</t>
+  </si>
+  <si>
     <t>e_BR446-500</t>
   </si>
   <si>
-    <t>e_BR984-525</t>
-  </si>
-  <si>
-    <t>e_BR662-440</t>
-  </si>
-  <si>
     <t>e_BR626-440</t>
   </si>
   <si>
     <t>e_BR606-500</t>
   </si>
   <si>
+    <t>e_w537470701-500</t>
+  </si>
+  <si>
+    <t>e_BR550-500</t>
+  </si>
+  <si>
+    <t>e_r6844204-500</t>
+  </si>
+  <si>
+    <t>e_w174017677-440</t>
+  </si>
+  <si>
+    <t>e_BR641-500</t>
+  </si>
+  <si>
+    <t>e_BR661-440</t>
+  </si>
+  <si>
+    <t>e_BR732-500</t>
+  </si>
+  <si>
     <t>e_BR592-500</t>
   </si>
   <si>
@@ -108,60 +162,6 @@
     <t>e_w174852067-500</t>
   </si>
   <si>
-    <t>e_BR487-500</t>
-  </si>
-  <si>
-    <t>e_BR515-500</t>
-  </si>
-  <si>
-    <t>e_BR579-500</t>
-  </si>
-  <si>
-    <t>e_BR630-440</t>
-  </si>
-  <si>
-    <t>e_BR663-440</t>
-  </si>
-  <si>
-    <t>e_r6844204-500</t>
-  </si>
-  <si>
-    <t>e_w174017677-440</t>
-  </si>
-  <si>
-    <t>e_BR550-500</t>
-  </si>
-  <si>
-    <t>e_BR624-440</t>
-  </si>
-  <si>
-    <t>e_BR641-500</t>
-  </si>
-  <si>
-    <t>e_BR661-440</t>
-  </si>
-  <si>
-    <t>e_BR732-500</t>
-  </si>
-  <si>
-    <t>e_BR141-500</t>
-  </si>
-  <si>
-    <t>e_BR629-500</t>
-  </si>
-  <si>
-    <t>e_w537470701-500</t>
-  </si>
-  <si>
-    <t>e_BR621-440</t>
-  </si>
-  <si>
-    <t>e_BR650-440</t>
-  </si>
-  <si>
-    <t>e_BR657-440</t>
-  </si>
-  <si>
     <t>ep_bioenergy_BR227-500</t>
   </si>
   <si>
@@ -867,12 +867,12 @@
     <t>ep_coal_subcritical_</t>
   </si>
   <si>
+    <t>e_BR63-500</t>
+  </si>
+  <si>
     <t>e_BR886-500</t>
   </si>
   <si>
-    <t>e_BR63-500</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_G100000100611</t>
   </si>
   <si>
@@ -930,72 +930,72 @@
     <t>gas</t>
   </si>
   <si>
+    <t>e_BR683-500</t>
+  </si>
+  <si>
     <t>e_BR713-500</t>
   </si>
   <si>
+    <t>e_BR949-525</t>
+  </si>
+  <si>
+    <t>e_BR691-500</t>
+  </si>
+  <si>
+    <t>e_BR644-500</t>
+  </si>
+  <si>
+    <t>e_BR340-500</t>
+  </si>
+  <si>
+    <t>e_BR273-230</t>
+  </si>
+  <si>
+    <t>e_BR652-500</t>
+  </si>
+  <si>
+    <t>e_BR613-500</t>
+  </si>
+  <si>
+    <t>e_w131742617-500</t>
+  </si>
+  <si>
+    <t>e_w626479359-500</t>
+  </si>
+  <si>
+    <t>e_BR148-500</t>
+  </si>
+  <si>
+    <t>e_r9328495-500</t>
+  </si>
+  <si>
+    <t>e_BR258-500</t>
+  </si>
+  <si>
     <t>e_BR125-500</t>
   </si>
   <si>
+    <t>e_BR758-440</t>
+  </si>
+  <si>
+    <t>e_BR583-500</t>
+  </si>
+  <si>
+    <t>e_BR610-500</t>
+  </si>
+  <si>
+    <t>e_w287374167-500</t>
+  </si>
+  <si>
+    <t>e_BR764-440</t>
+  </si>
+  <si>
     <t>e_w302901044-440</t>
   </si>
   <si>
-    <t>e_BR764-440</t>
-  </si>
-  <si>
-    <t>e_BR691-500</t>
-  </si>
-  <si>
-    <t>e_w287374167-500</t>
-  </si>
-  <si>
-    <t>e_BR610-500</t>
-  </si>
-  <si>
-    <t>e_BR583-500</t>
-  </si>
-  <si>
-    <t>e_w626479359-500</t>
-  </si>
-  <si>
-    <t>e_w131742617-500</t>
-  </si>
-  <si>
-    <t>e_BR683-500</t>
-  </si>
-  <si>
     <t>e_BR679-500</t>
   </si>
   <si>
-    <t>e_BR148-500</t>
-  </si>
-  <si>
-    <t>e_r9328495-500</t>
-  </si>
-  <si>
-    <t>e_BR273-230</t>
-  </si>
-  <si>
-    <t>e_BR340-500</t>
-  </si>
-  <si>
-    <t>e_BR644-500</t>
-  </si>
-  <si>
-    <t>e_BR949-525</t>
-  </si>
-  <si>
-    <t>e_BR613-500</t>
-  </si>
-  <si>
-    <t>e_BR652-500</t>
-  </si>
-  <si>
-    <t>e_BR758-440</t>
-  </si>
-  <si>
-    <t>e_BR258-500</t>
-  </si>
-  <si>
     <t>ep_gas_combined_cycle_G100000406744</t>
   </si>
   <si>
@@ -1197,15 +1197,15 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_BR803-500</t>
+  </si>
+  <si>
+    <t>e_w215284729-500</t>
+  </si>
+  <si>
     <t>e_BR52-500</t>
   </si>
   <si>
-    <t>e_w215284729-500</t>
-  </si>
-  <si>
-    <t>e_BR803-500</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_BR184-500</t>
   </si>
   <si>
@@ -2019,15 +2019,15 @@
     <t>solar</t>
   </si>
   <si>
+    <t>elc_spv_030</t>
+  </si>
+  <si>
+    <t>elc_spv_100</t>
+  </si>
+  <si>
     <t>elc_spv_113</t>
   </si>
   <si>
-    <t>elc_spv_030</t>
-  </si>
-  <si>
-    <t>elc_spv_100</t>
-  </si>
-  <si>
     <t>ep_solar_pv_001</t>
   </si>
   <si>
@@ -2697,61 +2697,73 @@
     <t>ele</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - relation/6844204-500_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>TWh</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - BR626-440_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - BR663-440_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - BR292-500_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>GW</t>
-  </si>
-  <si>
-    <t>TWh</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR663-440_Missing Bioenergy Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - BR487-500_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - BR662-440_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - BR632-440_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - BR515-500_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - BR629-500_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/537470701-500_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - BR630-440_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - BR650-440_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - BR657-440_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - BR446-500_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - BR621-440_Missing Bioenergy Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - BR550-500_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - BR621-440_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR446-500_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR630-440_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR650-440_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR657-440_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR626-440_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR515-500_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR629-500_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/537470701-500_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - BR579-500_Missing Bioenergy Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/174017677-440_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - relation/6844204-500_Missing Bioenergy Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - BR141-500_Missing Bioenergy Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - BR661-440_Missing Bioenergy Capacity</t>
@@ -2763,10 +2775,10 @@
     <t>Aggregated Plant - EMBER Gap - way/174852067-500_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - BR141-500_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR487-500_Missing Bioenergy Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - BR606-500_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - BR732-500_Missing Bioenergy Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - BR624-440_Missing Bioenergy Capacity</t>
@@ -2778,18 +2790,6 @@
     <t>Aggregated Plant - EMBER Gap - BR641-500_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - BR662-440_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR632-440_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR606-500_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR732-500_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant</t>
   </si>
   <si>
@@ -3183,90 +3183,90 @@
     <t>Presidente Médici Candiota power station_Presidente Médici-C power station Unit 5</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/304646981-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/626479359-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - BR713-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/302901044-440_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - BR691-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - BR340-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - BR579-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - BR949-525_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - BR758-440_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - BR583-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/131742617-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - BR273-230_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - BR63-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - BR20-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/168664395-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - BR258-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - BR610-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - BR764-440_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - BR652-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - BR148-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - BR679-500_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - relation/9328495-500_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - BR613-500_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - BR679-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR758-440_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/304646981-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/168664395-500_Missing Gas Capacity</t>
+    <t>Aggregated Plant - EMBER Gap - BR644-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/287374167-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - BR400-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - BR683-500_Missing Gas Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - BR125-500_Missing Gas Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - BR273-230_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR340-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR691-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/302901044-440_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR583-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR258-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR764-440_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR610-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR148-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR652-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR20-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR579-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR949-525_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/287374167-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR400-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR683-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR644-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR713-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/626479359-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/131742617-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - BR63-500_Missing Gas Capacity</t>
-  </si>
-  <si>
     <t>Uruguaiana power station_1</t>
   </si>
   <si>
@@ -3465,12 +3465,12 @@
     <t>Aggregated Plant - IRENA Gap - way/215284729-500_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - BR803-500_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - BR52-500_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - BR803-500_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Água Vermelha hydroelectric plant_</t>
   </si>
   <si>
@@ -4323,12 +4323,12 @@
     <t>ccs retrofit of -- Presidente Médici Candiota power station_Presidente Médici-C power station Unit 5</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR886-500_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR63-500_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR886-500_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>ccs retrofit of -- Uruguaiana power station_1</t>
   </si>
   <si>
@@ -4422,88 +4422,88 @@
     <t>ccs retrofit of -- Azulão power station_II</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR258-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/626479359-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR579-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR713-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/131742617-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/168664395-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - relation/9328495-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/302901044-440_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR652-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR683-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR20-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR610-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR949-525_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR400-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR340-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR758-440_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/287374167-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR583-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR63-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR679-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR644-500_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/304646981-500_Missing Gas Capacity</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR273-230_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR764-440_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR613-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR125-500_Missing Gas Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR691-500_Missing Gas Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR148-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR949-525_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR679-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR758-440_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR340-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/302901044-440_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/287374167-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - relation/9328495-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/626479359-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR613-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR125-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/168664395-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/131742617-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR258-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR691-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR273-230_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR652-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR683-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR713-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR610-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR20-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR400-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR583-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR579-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR644-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR63-500_Missing Gas Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR764-440_Missing Gas Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Termoceará power station_1</t>
@@ -5078,7 +5078,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC435E06-D431-4E7F-BB2B-855ADDED69AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3108B0E-B3FB-40D3-867F-2EA240A7AAB6}">
   <dimension ref="B9:T154"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5322,7 +5322,7 @@
         <v>273</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E14">
         <v>8.4633600000000017E-2</v>
@@ -5378,7 +5378,7 @@
         <v>273</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E15">
         <v>8.4633600000000017E-2</v>
@@ -5434,7 +5434,7 @@
         <v>273</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E16">
         <v>9.3388800000000008E-2</v>
@@ -5490,7 +5490,7 @@
         <v>273</v>
       </c>
       <c r="D17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E17">
         <v>9.3388800000000008E-2</v>
@@ -5546,7 +5546,7 @@
         <v>273</v>
       </c>
       <c r="D18" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E18">
         <v>9.3388800000000008E-2</v>
@@ -5602,7 +5602,7 @@
         <v>273</v>
       </c>
       <c r="D19" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E19">
         <v>0.128304</v>
@@ -5658,7 +5658,7 @@
         <v>273</v>
       </c>
       <c r="D20" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E20">
         <v>0.17072639999999997</v>
@@ -5770,7 +5770,7 @@
         <v>273</v>
       </c>
       <c r="D22" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E22">
         <v>0.17072639999999997</v>
@@ -5826,7 +5826,7 @@
         <v>273</v>
       </c>
       <c r="D23" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E23">
         <v>0.17072639999999997</v>
@@ -5882,7 +5882,7 @@
         <v>273</v>
       </c>
       <c r="D24" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E24">
         <v>0.17072639999999997</v>
@@ -6106,7 +6106,7 @@
         <v>296</v>
       </c>
       <c r="D28" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E28">
         <v>0.441</v>
@@ -6162,7 +6162,7 @@
         <v>296</v>
       </c>
       <c r="D29" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E29">
         <v>0.45779999999999998</v>
@@ -6218,7 +6218,7 @@
         <v>296</v>
       </c>
       <c r="D30" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="E30">
         <v>0.45779999999999998</v>
@@ -6274,7 +6274,7 @@
         <v>296</v>
       </c>
       <c r="D31" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="E31">
         <v>0.47040000000000004</v>
@@ -6330,7 +6330,7 @@
         <v>296</v>
       </c>
       <c r="D32" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E32">
         <v>0.504</v>
@@ -6442,7 +6442,7 @@
         <v>296</v>
       </c>
       <c r="D34" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="E34">
         <v>0.48719999999999997</v>
@@ -6498,7 +6498,7 @@
         <v>296</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="E35">
         <v>0.504</v>
@@ -6554,7 +6554,7 @@
         <v>296</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="E36">
         <v>0.48719999999999997</v>
@@ -6666,7 +6666,7 @@
         <v>296</v>
       </c>
       <c r="D38" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="E38">
         <v>0.45779999999999998</v>
@@ -6778,7 +6778,7 @@
         <v>296</v>
       </c>
       <c r="D40" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="E40">
         <v>0.504</v>
@@ -6834,7 +6834,7 @@
         <v>296</v>
       </c>
       <c r="D41" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="E41">
         <v>0.48719999999999997</v>
@@ -6946,7 +6946,7 @@
         <v>296</v>
       </c>
       <c r="D43" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E43">
         <v>0.45779999999999998</v>
@@ -7002,7 +7002,7 @@
         <v>296</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E44">
         <v>0.45779999999999998</v>
@@ -7058,7 +7058,7 @@
         <v>296</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E45">
         <v>0.45779999999999998</v>
@@ -7114,7 +7114,7 @@
         <v>296</v>
       </c>
       <c r="D46" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="E46">
         <v>0.504</v>
@@ -7170,7 +7170,7 @@
         <v>296</v>
       </c>
       <c r="D47" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="E47">
         <v>0.504</v>
@@ -7226,7 +7226,7 @@
         <v>296</v>
       </c>
       <c r="D48" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E48">
         <v>0.45779999999999998</v>
@@ -7282,7 +7282,7 @@
         <v>296</v>
       </c>
       <c r="D49" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="E49">
         <v>0.45779999999999998</v>
@@ -7338,7 +7338,7 @@
         <v>296</v>
       </c>
       <c r="D50" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="E50">
         <v>0.43680000000000002</v>
@@ -7506,7 +7506,7 @@
         <v>296</v>
       </c>
       <c r="D53" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="E53">
         <v>0.48719999999999997</v>
@@ -7562,7 +7562,7 @@
         <v>296</v>
       </c>
       <c r="D54" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="E54">
         <v>0.43680000000000002</v>
@@ -7674,7 +7674,7 @@
         <v>296</v>
       </c>
       <c r="D56" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="E56">
         <v>0.43680000000000002</v>
@@ -7786,7 +7786,7 @@
         <v>296</v>
       </c>
       <c r="D58" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="E58">
         <v>0.504</v>
@@ -7842,7 +7842,7 @@
         <v>296</v>
       </c>
       <c r="D59" t="s">
-        <v>299</v>
+        <v>250</v>
       </c>
       <c r="E59">
         <v>0.504</v>
@@ -7954,7 +7954,7 @@
         <v>296</v>
       </c>
       <c r="D61" t="s">
-        <v>300</v>
+        <v>125</v>
       </c>
       <c r="E61">
         <v>0.504</v>
@@ -8010,7 +8010,7 @@
         <v>296</v>
       </c>
       <c r="D62" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E62">
         <v>0.504</v>
@@ -8066,7 +8066,7 @@
         <v>296</v>
       </c>
       <c r="D63" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E63">
         <v>0.504</v>
@@ -8122,7 +8122,7 @@
         <v>296</v>
       </c>
       <c r="D64" t="s">
-        <v>303</v>
+        <v>16</v>
       </c>
       <c r="E64">
         <v>0.504</v>
@@ -8178,7 +8178,7 @@
         <v>296</v>
       </c>
       <c r="D65" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E65">
         <v>0.504</v>
@@ -8234,7 +8234,7 @@
         <v>296</v>
       </c>
       <c r="D66" t="s">
-        <v>311</v>
+        <v>279</v>
       </c>
       <c r="E66">
         <v>0.504</v>
@@ -8290,7 +8290,7 @@
         <v>296</v>
       </c>
       <c r="D67" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E67">
         <v>0.504</v>
@@ -8346,7 +8346,7 @@
         <v>296</v>
       </c>
       <c r="D68" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E68">
         <v>0.504</v>
@@ -8402,7 +8402,7 @@
         <v>296</v>
       </c>
       <c r="D69" t="s">
-        <v>308</v>
+        <v>51</v>
       </c>
       <c r="E69">
         <v>0.504</v>
@@ -8458,7 +8458,7 @@
         <v>296</v>
       </c>
       <c r="D70" t="s">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E70">
         <v>0.504</v>
@@ -8570,7 +8570,7 @@
         <v>296</v>
       </c>
       <c r="D72" t="s">
-        <v>277</v>
+        <v>316</v>
       </c>
       <c r="E72">
         <v>0.504</v>
@@ -8626,7 +8626,7 @@
         <v>296</v>
       </c>
       <c r="D73" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="E73">
         <v>0.504</v>
@@ -8682,7 +8682,7 @@
         <v>296</v>
       </c>
       <c r="D74" t="s">
-        <v>279</v>
+        <v>307</v>
       </c>
       <c r="E74">
         <v>0.504</v>
@@ -8738,7 +8738,7 @@
         <v>296</v>
       </c>
       <c r="D75" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E75">
         <v>0.504</v>
@@ -8794,7 +8794,7 @@
         <v>296</v>
       </c>
       <c r="D76" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E76">
         <v>0.504</v>
@@ -8850,7 +8850,7 @@
         <v>296</v>
       </c>
       <c r="D77" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E77">
         <v>0.504</v>
@@ -8906,7 +8906,7 @@
         <v>296</v>
       </c>
       <c r="D78" t="s">
-        <v>314</v>
+        <v>276</v>
       </c>
       <c r="E78">
         <v>0.504</v>
@@ -8962,7 +8962,7 @@
         <v>296</v>
       </c>
       <c r="D79" t="s">
-        <v>25</v>
+        <v>310</v>
       </c>
       <c r="E79">
         <v>0.504</v>
@@ -9018,7 +9018,7 @@
         <v>296</v>
       </c>
       <c r="D80" t="s">
-        <v>125</v>
+        <v>312</v>
       </c>
       <c r="E80">
         <v>0.504</v>
@@ -9074,7 +9074,7 @@
         <v>296</v>
       </c>
       <c r="D81" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E81">
         <v>0.504</v>
@@ -9130,7 +9130,7 @@
         <v>296</v>
       </c>
       <c r="D82" t="s">
-        <v>51</v>
+        <v>313</v>
       </c>
       <c r="E82">
         <v>0.504</v>
@@ -9242,7 +9242,7 @@
         <v>296</v>
       </c>
       <c r="D84" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E84">
         <v>0.504</v>
@@ -9298,7 +9298,7 @@
         <v>296</v>
       </c>
       <c r="D85" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E85">
         <v>0.504</v>
@@ -9410,7 +9410,7 @@
         <v>296</v>
       </c>
       <c r="D87" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E87">
         <v>0.24359999999999998</v>
@@ -9634,7 +9634,7 @@
         <v>296</v>
       </c>
       <c r="D91" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="E91">
         <v>0.26039999999999996</v>
@@ -9690,7 +9690,7 @@
         <v>296</v>
       </c>
       <c r="D92" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E92">
         <v>0.24359999999999998</v>
@@ -9746,7 +9746,7 @@
         <v>296</v>
       </c>
       <c r="D93" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E93">
         <v>0.24359999999999998</v>
@@ -9858,7 +9858,7 @@
         <v>296</v>
       </c>
       <c r="D95" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="E95">
         <v>0.2772</v>
@@ -9970,7 +9970,7 @@
         <v>296</v>
       </c>
       <c r="D97" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E97">
         <v>0.3024</v>
@@ -10026,7 +10026,7 @@
         <v>296</v>
       </c>
       <c r="D98" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E98">
         <v>0.3024</v>
@@ -10082,7 +10082,7 @@
         <v>296</v>
       </c>
       <c r="D99" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="E99">
         <v>0.3024</v>
@@ -10194,7 +10194,7 @@
         <v>296</v>
       </c>
       <c r="D101" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="E101">
         <v>0.29820000000000002</v>
@@ -10306,7 +10306,7 @@
         <v>296</v>
       </c>
       <c r="D103" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E103">
         <v>0.28979999999999995</v>
@@ -10362,7 +10362,7 @@
         <v>296</v>
       </c>
       <c r="D104" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E104">
         <v>0.3024</v>
@@ -10418,7 +10418,7 @@
         <v>296</v>
       </c>
       <c r="D105" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E105">
         <v>0.3024</v>
@@ -10586,7 +10586,7 @@
         <v>296</v>
       </c>
       <c r="D108" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E108">
         <v>0.26039999999999996</v>
@@ -10642,7 +10642,7 @@
         <v>296</v>
       </c>
       <c r="D109" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="E109">
         <v>0.28979999999999995</v>
@@ -10698,7 +10698,7 @@
         <v>296</v>
       </c>
       <c r="D110" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E110">
         <v>0.2772</v>
@@ -10754,7 +10754,7 @@
         <v>296</v>
       </c>
       <c r="D111" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="E111">
         <v>0.28560000000000002</v>
@@ -10810,7 +10810,7 @@
         <v>296</v>
       </c>
       <c r="D112" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="E112">
         <v>0.28560000000000002</v>
@@ -10866,7 +10866,7 @@
         <v>296</v>
       </c>
       <c r="D113" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="E113">
         <v>0.28560000000000002</v>
@@ -10922,7 +10922,7 @@
         <v>296</v>
       </c>
       <c r="D114" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E114">
         <v>0.28559999999999997</v>
@@ -10978,7 +10978,7 @@
         <v>296</v>
       </c>
       <c r="D115" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E115">
         <v>0.28559999999999997</v>
@@ -11034,7 +11034,7 @@
         <v>296</v>
       </c>
       <c r="D116" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="E116">
         <v>0.28560000000000002</v>
@@ -11090,7 +11090,7 @@
         <v>296</v>
       </c>
       <c r="D117" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="E117">
         <v>0.28560000000000002</v>
@@ -11146,7 +11146,7 @@
         <v>296</v>
       </c>
       <c r="D118" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E118">
         <v>0.28979999999999989</v>
@@ -11202,7 +11202,7 @@
         <v>296</v>
       </c>
       <c r="D119" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E119">
         <v>0.28979999999999989</v>
@@ -11258,7 +11258,7 @@
         <v>296</v>
       </c>
       <c r="D120" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="E120">
         <v>0.28559999999999997</v>
@@ -11314,7 +11314,7 @@
         <v>618</v>
       </c>
       <c r="D121" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E121">
         <v>0.252</v>
@@ -11370,7 +11370,7 @@
         <v>618</v>
       </c>
       <c r="D122" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E122">
         <v>0.252</v>
@@ -11482,7 +11482,7 @@
         <v>618</v>
       </c>
       <c r="D124" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="E124">
         <v>0.28560000000000002</v>
@@ -11706,7 +11706,7 @@
         <v>618</v>
       </c>
       <c r="D128" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="E128">
         <v>0.27300000000000002</v>
@@ -12714,7 +12714,7 @@
         <v>618</v>
       </c>
       <c r="D146" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E146">
         <v>0.29399999999999998</v>
@@ -12994,7 +12994,7 @@
         <v>618</v>
       </c>
       <c r="D151" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E151">
         <v>0.27300000000000002</v>
@@ -13050,7 +13050,7 @@
         <v>618</v>
       </c>
       <c r="D152" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E152">
         <v>0.27300000000000002</v>
@@ -13106,7 +13106,7 @@
         <v>618</v>
       </c>
       <c r="D153" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="E153">
         <v>0.252</v>
@@ -13162,7 +13162,7 @@
         <v>618</v>
       </c>
       <c r="D154" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E154">
         <v>0.29820000000000002</v>
@@ -13216,7 +13216,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D2BCC08-43B4-4E74-BB8E-413C8C862CAB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC84470E-815E-436A-8010-54B71C3A608A}">
   <dimension ref="B9:T1090"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -13298,7 +13298,7 @@
         <v>2022</v>
       </c>
       <c r="F11">
-        <v>5.2580647421524691E-2</v>
+        <v>8.3229260089686133E-2</v>
       </c>
       <c r="G11">
         <v>0.31680000000000003</v>
@@ -13351,13 +13351,13 @@
         <v>2022</v>
       </c>
       <c r="F12">
-        <v>5.3705367152466391E-2</v>
+        <v>7.9292741031390168E-2</v>
       </c>
       <c r="G12">
         <v>0.31680000000000003</v>
       </c>
       <c r="H12">
-        <v>3421.2499999999995</v>
+        <v>3421.25</v>
       </c>
       <c r="I12">
         <v>128.70000000000002</v>
@@ -13404,7 +13404,7 @@
         <v>2022</v>
       </c>
       <c r="F13">
-        <v>7.0294983183856533E-2</v>
+        <v>0.12400035033632292</v>
       </c>
       <c r="G13">
         <v>0.31680000000000003</v>
@@ -13416,7 +13416,7 @@
         <v>128.70000000000002</v>
       </c>
       <c r="J13">
-        <v>7.9200000000000017</v>
+        <v>7.9200000000000008</v>
       </c>
       <c r="K13">
         <v>50</v>
@@ -13457,19 +13457,19 @@
         <v>2022</v>
       </c>
       <c r="F14">
-        <v>0.10234949551569511</v>
+        <v>0.13327928811659198</v>
       </c>
       <c r="G14">
         <v>0.31680000000000003</v>
       </c>
       <c r="H14">
-        <v>3421.2499999999991</v>
+        <v>3421.2499999999995</v>
       </c>
       <c r="I14">
         <v>128.70000000000002</v>
       </c>
       <c r="J14">
-        <v>7.9200000000000017</v>
+        <v>7.92</v>
       </c>
       <c r="K14">
         <v>50</v>
@@ -13510,7 +13510,7 @@
         <v>2022</v>
       </c>
       <c r="F15">
-        <v>0.2440641816143499</v>
+        <v>0.1937329736547086</v>
       </c>
       <c r="G15">
         <v>0.31680000000000003</v>
@@ -13563,13 +13563,13 @@
         <v>2022</v>
       </c>
       <c r="F16">
-        <v>5.3424187219730968E-2</v>
+        <v>7.7605661434977616E-2</v>
       </c>
       <c r="G16">
         <v>0.31680000000000003</v>
       </c>
       <c r="H16">
-        <v>3421.2499999999995</v>
+        <v>3421.2499999999991</v>
       </c>
       <c r="I16">
         <v>128.70000000000002</v>
@@ -13616,7 +13616,7 @@
         <v>2022</v>
       </c>
       <c r="F17">
-        <v>6.4952564461883439E-2</v>
+        <v>0.29692600896860999</v>
       </c>
       <c r="G17">
         <v>0.31680000000000003</v>
@@ -13669,19 +13669,19 @@
         <v>2022</v>
       </c>
       <c r="F18">
-        <v>7.7886841367713039E-2</v>
+        <v>5.2018287556053824E-2</v>
       </c>
       <c r="G18">
         <v>0.31680000000000003</v>
       </c>
       <c r="H18">
-        <v>3421.25</v>
+        <v>3421.2499999999995</v>
       </c>
       <c r="I18">
         <v>128.70000000000002</v>
       </c>
       <c r="J18">
-        <v>7.9200000000000017</v>
+        <v>7.92</v>
       </c>
       <c r="K18">
         <v>50</v>
@@ -13722,7 +13722,7 @@
         <v>2022</v>
       </c>
       <c r="F19">
-        <v>5.7360706278026925E-2</v>
+        <v>7.1700882847533662E-2</v>
       </c>
       <c r="G19">
         <v>0.31680000000000003</v>
@@ -13775,7 +13775,7 @@
         <v>2022</v>
       </c>
       <c r="F20">
-        <v>8.3229260089686133E-2</v>
+        <v>0.23590996356502253</v>
       </c>
       <c r="G20">
         <v>0.31680000000000003</v>
@@ -13828,7 +13828,7 @@
         <v>2022</v>
       </c>
       <c r="F21">
-        <v>0.13327928811659198</v>
+        <v>5.2580647421524691E-2</v>
       </c>
       <c r="G21">
         <v>0.31680000000000003</v>
@@ -13840,7 +13840,7 @@
         <v>128.70000000000002</v>
       </c>
       <c r="J21">
-        <v>7.92</v>
+        <v>7.9200000000000008</v>
       </c>
       <c r="K21">
         <v>50</v>
@@ -13881,19 +13881,19 @@
         <v>2022</v>
       </c>
       <c r="F22">
-        <v>0.12400035033632292</v>
+        <v>0.10234949551569511</v>
       </c>
       <c r="G22">
         <v>0.31680000000000003</v>
       </c>
       <c r="H22">
-        <v>3421.2499999999995</v>
+        <v>3421.2499999999991</v>
       </c>
       <c r="I22">
         <v>128.70000000000002</v>
       </c>
       <c r="J22">
-        <v>7.9200000000000008</v>
+        <v>7.9200000000000017</v>
       </c>
       <c r="K22">
         <v>50</v>
@@ -13934,19 +13934,19 @@
         <v>2022</v>
       </c>
       <c r="F23">
-        <v>7.9292741031390168E-2</v>
+        <v>7.0294983183856533E-2</v>
       </c>
       <c r="G23">
         <v>0.31680000000000003</v>
       </c>
       <c r="H23">
-        <v>3421.25</v>
+        <v>3421.2499999999995</v>
       </c>
       <c r="I23">
         <v>128.70000000000002</v>
       </c>
       <c r="J23">
-        <v>7.9200000000000008</v>
+        <v>7.9200000000000017</v>
       </c>
       <c r="K23">
         <v>50</v>
@@ -13987,7 +13987,7 @@
         <v>2022</v>
       </c>
       <c r="F24">
-        <v>0.1937329736547086</v>
+        <v>6.3546664798206309E-2</v>
       </c>
       <c r="G24">
         <v>0.31680000000000003</v>
@@ -14040,7 +14040,7 @@
         <v>2022</v>
       </c>
       <c r="F25">
-        <v>0.10403657511210765</v>
+        <v>5.3705367152466391E-2</v>
       </c>
       <c r="G25">
         <v>0.31680000000000003</v>
@@ -14052,7 +14052,7 @@
         <v>128.70000000000002</v>
       </c>
       <c r="J25">
-        <v>7.92</v>
+        <v>7.9200000000000008</v>
       </c>
       <c r="K25">
         <v>50</v>
@@ -14093,7 +14093,7 @@
         <v>2022</v>
       </c>
       <c r="F26">
-        <v>7.6199761771300473E-2</v>
+        <v>0.2440641816143499</v>
       </c>
       <c r="G26">
         <v>0.31680000000000003</v>
@@ -14146,7 +14146,7 @@
         <v>2022</v>
       </c>
       <c r="F27">
-        <v>0.11809557174887898</v>
+        <v>5.3424187219730968E-2</v>
       </c>
       <c r="G27">
         <v>0.31680000000000003</v>
@@ -14199,7 +14199,7 @@
         <v>2022</v>
       </c>
       <c r="F28">
-        <v>5.2018287556053824E-2</v>
+        <v>8.5197519618834108E-2</v>
       </c>
       <c r="G28">
         <v>0.31680000000000003</v>
@@ -14211,7 +14211,7 @@
         <v>128.70000000000002</v>
       </c>
       <c r="J28">
-        <v>7.92</v>
+        <v>7.9200000000000008</v>
       </c>
       <c r="K28">
         <v>50</v>
@@ -14252,7 +14252,7 @@
         <v>2022</v>
       </c>
       <c r="F29">
-        <v>6.6639644058295991E-2</v>
+        <v>0.11809557174887898</v>
       </c>
       <c r="G29">
         <v>0.31680000000000003</v>
@@ -14264,7 +14264,7 @@
         <v>128.70000000000002</v>
       </c>
       <c r="J29">
-        <v>7.92</v>
+        <v>7.9200000000000008</v>
       </c>
       <c r="K29">
         <v>50</v>
@@ -14305,7 +14305,7 @@
         <v>2022</v>
       </c>
       <c r="F30">
-        <v>6.7764363789237697E-2</v>
+        <v>0.10403657511210765</v>
       </c>
       <c r="G30">
         <v>0.31680000000000003</v>
@@ -14317,7 +14317,7 @@
         <v>128.70000000000002</v>
       </c>
       <c r="J30">
-        <v>7.9200000000000008</v>
+        <v>7.92</v>
       </c>
       <c r="K30">
         <v>50</v>
@@ -14358,7 +14358,7 @@
         <v>2022</v>
       </c>
       <c r="F31">
-        <v>0.16870795964125568</v>
+        <v>7.6199761771300473E-2</v>
       </c>
       <c r="G31">
         <v>0.31680000000000003</v>
@@ -14411,7 +14411,7 @@
         <v>2022</v>
       </c>
       <c r="F32">
-        <v>7.1700882847533662E-2</v>
+        <v>6.6639644058295991E-2</v>
       </c>
       <c r="G32">
         <v>0.31680000000000003</v>
@@ -14423,7 +14423,7 @@
         <v>128.70000000000002</v>
       </c>
       <c r="J32">
-        <v>7.9200000000000008</v>
+        <v>7.92</v>
       </c>
       <c r="K32">
         <v>50</v>
@@ -14464,7 +14464,7 @@
         <v>2022</v>
       </c>
       <c r="F33">
-        <v>0.23590996356502253</v>
+        <v>6.7764363789237697E-2</v>
       </c>
       <c r="G33">
         <v>0.31680000000000003</v>
@@ -14517,7 +14517,7 @@
         <v>2022</v>
       </c>
       <c r="F34">
-        <v>8.5197519618834108E-2</v>
+        <v>0.16870795964125568</v>
       </c>
       <c r="G34">
         <v>0.31680000000000003</v>
@@ -14570,7 +14570,7 @@
         <v>2022</v>
       </c>
       <c r="F35">
-        <v>6.3546664798206309E-2</v>
+        <v>6.4952564461883439E-2</v>
       </c>
       <c r="G35">
         <v>0.31680000000000003</v>
@@ -14582,7 +14582,7 @@
         <v>128.70000000000002</v>
       </c>
       <c r="J35">
-        <v>7.9200000000000008</v>
+        <v>7.92</v>
       </c>
       <c r="K35">
         <v>50</v>
@@ -14623,19 +14623,19 @@
         <v>2022</v>
       </c>
       <c r="F36">
-        <v>7.7605661434977616E-2</v>
+        <v>7.7886841367713039E-2</v>
       </c>
       <c r="G36">
         <v>0.31680000000000003</v>
       </c>
       <c r="H36">
-        <v>3421.2499999999991</v>
+        <v>3421.25</v>
       </c>
       <c r="I36">
         <v>128.70000000000002</v>
       </c>
       <c r="J36">
-        <v>7.9200000000000008</v>
+        <v>7.9200000000000017</v>
       </c>
       <c r="K36">
         <v>50</v>
@@ -14676,7 +14676,7 @@
         <v>2022</v>
       </c>
       <c r="F37">
-        <v>0.29692600896860999</v>
+        <v>5.7360706278026925E-2</v>
       </c>
       <c r="G37">
         <v>0.31680000000000003</v>
@@ -14688,7 +14688,7 @@
         <v>128.70000000000002</v>
       </c>
       <c r="J37">
-        <v>7.92</v>
+        <v>7.9200000000000008</v>
       </c>
       <c r="K37">
         <v>50</v>
@@ -14829,7 +14829,7 @@
         <v>13</v>
       </c>
       <c r="D40" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E40">
         <v>2006</v>
@@ -14882,7 +14882,7 @@
         <v>13</v>
       </c>
       <c r="D41" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E41">
         <v>2023</v>
@@ -15359,7 +15359,7 @@
         <v>13</v>
       </c>
       <c r="D50" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E50">
         <v>2011</v>
@@ -15412,7 +15412,7 @@
         <v>13</v>
       </c>
       <c r="D51" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E51">
         <v>2021</v>
@@ -15465,7 +15465,7 @@
         <v>13</v>
       </c>
       <c r="D52" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E52">
         <v>2028</v>
@@ -15677,7 +15677,7 @@
         <v>13</v>
       </c>
       <c r="D56" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E56">
         <v>2011</v>
@@ -15730,7 +15730,7 @@
         <v>13</v>
       </c>
       <c r="D57" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E57">
         <v>2013</v>
@@ -15783,7 +15783,7 @@
         <v>13</v>
       </c>
       <c r="D58" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E58">
         <v>2014</v>
@@ -15836,7 +15836,7 @@
         <v>13</v>
       </c>
       <c r="D59" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E59">
         <v>2017</v>
@@ -16313,7 +16313,7 @@
         <v>13</v>
       </c>
       <c r="D68" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E68">
         <v>2010</v>
@@ -16366,7 +16366,7 @@
         <v>13</v>
       </c>
       <c r="D69" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E69">
         <v>2012</v>
@@ -16631,7 +16631,7 @@
         <v>13</v>
       </c>
       <c r="D74" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E74">
         <v>1992</v>
@@ -16684,7 +16684,7 @@
         <v>13</v>
       </c>
       <c r="D75" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E75">
         <v>2001</v>
@@ -16949,7 +16949,7 @@
         <v>13</v>
       </c>
       <c r="D80" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E80">
         <v>2014</v>
@@ -17002,7 +17002,7 @@
         <v>13</v>
       </c>
       <c r="D81" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E81">
         <v>2015</v>
@@ -17320,7 +17320,7 @@
         <v>13</v>
       </c>
       <c r="D87" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E87">
         <v>2006</v>
@@ -17373,7 +17373,7 @@
         <v>13</v>
       </c>
       <c r="D88" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E88">
         <v>2007</v>
@@ -17426,7 +17426,7 @@
         <v>13</v>
       </c>
       <c r="D89" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E89">
         <v>2008</v>
@@ -17479,7 +17479,7 @@
         <v>13</v>
       </c>
       <c r="D90" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E90">
         <v>2010</v>
@@ -17532,7 +17532,7 @@
         <v>13</v>
       </c>
       <c r="D91" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E91">
         <v>2013</v>
@@ -17691,7 +17691,7 @@
         <v>13</v>
       </c>
       <c r="D94" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E94">
         <v>2013</v>
@@ -17850,7 +17850,7 @@
         <v>13</v>
       </c>
       <c r="D97" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="E97">
         <v>1983</v>
@@ -17903,7 +17903,7 @@
         <v>13</v>
       </c>
       <c r="D98" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="E98">
         <v>1987</v>
@@ -17956,7 +17956,7 @@
         <v>13</v>
       </c>
       <c r="D99" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="E99">
         <v>2012</v>
@@ -18009,7 +18009,7 @@
         <v>13</v>
       </c>
       <c r="D100" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="E100">
         <v>2013</v>
@@ -18062,7 +18062,7 @@
         <v>13</v>
       </c>
       <c r="D101" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="E101">
         <v>2015</v>
@@ -18115,7 +18115,7 @@
         <v>13</v>
       </c>
       <c r="D102" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="E102">
         <v>2019</v>
@@ -18168,7 +18168,7 @@
         <v>13</v>
       </c>
       <c r="D103" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E103">
         <v>1900</v>
@@ -18221,7 +18221,7 @@
         <v>13</v>
       </c>
       <c r="D104" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E104">
         <v>2008</v>
@@ -18274,7 +18274,7 @@
         <v>13</v>
       </c>
       <c r="D105" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="E105">
         <v>2009</v>
@@ -18327,7 +18327,7 @@
         <v>13</v>
       </c>
       <c r="D106" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="E106">
         <v>2015</v>
@@ -18539,7 +18539,7 @@
         <v>13</v>
       </c>
       <c r="D110" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E110">
         <v>2002</v>
@@ -18592,7 +18592,7 @@
         <v>13</v>
       </c>
       <c r="D111" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E111">
         <v>2010</v>
@@ -18857,7 +18857,7 @@
         <v>13</v>
       </c>
       <c r="D116" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="E116">
         <v>1975</v>
@@ -18910,7 +18910,7 @@
         <v>13</v>
       </c>
       <c r="D117" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="E117">
         <v>1986</v>
@@ -18963,7 +18963,7 @@
         <v>13</v>
       </c>
       <c r="D118" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="E118">
         <v>2010</v>
@@ -19016,7 +19016,7 @@
         <v>13</v>
       </c>
       <c r="D119" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E119">
         <v>2001</v>
@@ -19069,7 +19069,7 @@
         <v>13</v>
       </c>
       <c r="D120" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E120">
         <v>2007</v>
@@ -19122,7 +19122,7 @@
         <v>13</v>
       </c>
       <c r="D121" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E121">
         <v>2008</v>
@@ -19175,7 +19175,7 @@
         <v>13</v>
       </c>
       <c r="D122" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E122">
         <v>2010</v>
@@ -19228,7 +19228,7 @@
         <v>13</v>
       </c>
       <c r="D123" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E123">
         <v>2011</v>
@@ -19281,7 +19281,7 @@
         <v>13</v>
       </c>
       <c r="D124" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E124">
         <v>2013</v>
@@ -19334,7 +19334,7 @@
         <v>13</v>
       </c>
       <c r="D125" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E125">
         <v>2014</v>
@@ -19387,7 +19387,7 @@
         <v>13</v>
       </c>
       <c r="D126" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E126">
         <v>2015</v>
@@ -19440,7 +19440,7 @@
         <v>13</v>
       </c>
       <c r="D127" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E127">
         <v>2018</v>
@@ -19493,7 +19493,7 @@
         <v>13</v>
       </c>
       <c r="D128" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E128">
         <v>2010</v>
@@ -19546,7 +19546,7 @@
         <v>13</v>
       </c>
       <c r="D129" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E129">
         <v>1995</v>
@@ -19599,7 +19599,7 @@
         <v>13</v>
       </c>
       <c r="D130" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E130">
         <v>2007</v>
@@ -19652,7 +19652,7 @@
         <v>13</v>
       </c>
       <c r="D131" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E131">
         <v>2009</v>
@@ -19705,7 +19705,7 @@
         <v>13</v>
       </c>
       <c r="D132" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E132">
         <v>2015</v>
@@ -19758,7 +19758,7 @@
         <v>13</v>
       </c>
       <c r="D133" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E133">
         <v>1987</v>
@@ -19811,7 +19811,7 @@
         <v>13</v>
       </c>
       <c r="D134" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E134">
         <v>2014</v>
@@ -20765,7 +20765,7 @@
         <v>13</v>
       </c>
       <c r="D152" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E152">
         <v>2024</v>
@@ -20818,7 +20818,7 @@
         <v>13</v>
       </c>
       <c r="D153" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E153">
         <v>2026</v>
@@ -20924,7 +20924,7 @@
         <v>13</v>
       </c>
       <c r="D155" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E155">
         <v>2023</v>
@@ -20977,7 +20977,7 @@
         <v>13</v>
       </c>
       <c r="D156" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E156">
         <v>2026</v>
@@ -21030,7 +21030,7 @@
         <v>13</v>
       </c>
       <c r="D157" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="E157">
         <v>2008</v>
@@ -21083,7 +21083,7 @@
         <v>13</v>
       </c>
       <c r="D158" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="E158">
         <v>2012</v>
@@ -21189,7 +21189,7 @@
         <v>13</v>
       </c>
       <c r="D160" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="E160">
         <v>1994</v>
@@ -21242,7 +21242,7 @@
         <v>13</v>
       </c>
       <c r="D161" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E161">
         <v>2009</v>
@@ -21295,7 +21295,7 @@
         <v>13</v>
       </c>
       <c r="D162" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E162">
         <v>2002</v>
@@ -21401,7 +21401,7 @@
         <v>13</v>
       </c>
       <c r="D164" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E164">
         <v>2003</v>
@@ -21454,7 +21454,7 @@
         <v>13</v>
       </c>
       <c r="D165" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E165">
         <v>2013</v>
@@ -21507,7 +21507,7 @@
         <v>13</v>
       </c>
       <c r="D166" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E166">
         <v>2013</v>
@@ -21666,7 +21666,7 @@
         <v>13</v>
       </c>
       <c r="D169" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E169">
         <v>2014</v>
@@ -21719,7 +21719,7 @@
         <v>13</v>
       </c>
       <c r="D170" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E170">
         <v>2021</v>
@@ -21772,7 +21772,7 @@
         <v>13</v>
       </c>
       <c r="D171" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E171">
         <v>2021</v>
@@ -21825,7 +21825,7 @@
         <v>13</v>
       </c>
       <c r="D172" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E172">
         <v>2021</v>
@@ -21878,7 +21878,7 @@
         <v>13</v>
       </c>
       <c r="D173" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="E173">
         <v>2011</v>
@@ -22090,7 +22090,7 @@
         <v>13</v>
       </c>
       <c r="D177" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E177">
         <v>2001</v>
@@ -22143,7 +22143,7 @@
         <v>13</v>
       </c>
       <c r="D178" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="E178">
         <v>2021</v>
@@ -22196,7 +22196,7 @@
         <v>13</v>
       </c>
       <c r="D179" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E179">
         <v>2009</v>
@@ -22249,7 +22249,7 @@
         <v>13</v>
       </c>
       <c r="D180" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E180">
         <v>2006</v>
@@ -22302,7 +22302,7 @@
         <v>13</v>
       </c>
       <c r="D181" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E181">
         <v>1971</v>
@@ -22355,7 +22355,7 @@
         <v>13</v>
       </c>
       <c r="D182" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E182">
         <v>2015</v>
@@ -22408,7 +22408,7 @@
         <v>13</v>
       </c>
       <c r="D183" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E183">
         <v>2015</v>
@@ -22567,7 +22567,7 @@
         <v>13</v>
       </c>
       <c r="D186" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E186">
         <v>2000</v>
@@ -22673,7 +22673,7 @@
         <v>13</v>
       </c>
       <c r="D188" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="E188">
         <v>1981</v>
@@ -22726,7 +22726,7 @@
         <v>13</v>
       </c>
       <c r="D189" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E189">
         <v>2010</v>
@@ -22832,7 +22832,7 @@
         <v>13</v>
       </c>
       <c r="D191" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="E191">
         <v>2022</v>
@@ -22885,7 +22885,7 @@
         <v>13</v>
       </c>
       <c r="D192" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="E192">
         <v>2001</v>
@@ -22938,7 +22938,7 @@
         <v>13</v>
       </c>
       <c r="D193" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E193">
         <v>2013</v>
@@ -22991,7 +22991,7 @@
         <v>13</v>
       </c>
       <c r="D194" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E194">
         <v>2013</v>
@@ -23044,7 +23044,7 @@
         <v>13</v>
       </c>
       <c r="D195" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E195">
         <v>2015</v>
@@ -23097,7 +23097,7 @@
         <v>13</v>
       </c>
       <c r="D196" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E196">
         <v>2015</v>
@@ -23150,7 +23150,7 @@
         <v>13</v>
       </c>
       <c r="D197" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E197">
         <v>2002</v>
@@ -23256,7 +23256,7 @@
         <v>13</v>
       </c>
       <c r="D199" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E199">
         <v>2006</v>
@@ -23309,7 +23309,7 @@
         <v>13</v>
       </c>
       <c r="D200" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="E200">
         <v>1982</v>
@@ -23362,7 +23362,7 @@
         <v>13</v>
       </c>
       <c r="D201" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E201">
         <v>2009</v>
@@ -23415,7 +23415,7 @@
         <v>13</v>
       </c>
       <c r="D202" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E202">
         <v>2017</v>
@@ -23468,7 +23468,7 @@
         <v>13</v>
       </c>
       <c r="D203" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E203">
         <v>2017</v>
@@ -23521,7 +23521,7 @@
         <v>13</v>
       </c>
       <c r="D204" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="E204">
         <v>2010</v>
@@ -23574,7 +23574,7 @@
         <v>13</v>
       </c>
       <c r="D205" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E205">
         <v>1982</v>
@@ -23733,7 +23733,7 @@
         <v>13</v>
       </c>
       <c r="D208" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E208">
         <v>2010</v>
@@ -23786,7 +23786,7 @@
         <v>13</v>
       </c>
       <c r="D209" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E209">
         <v>2010</v>
@@ -23892,7 +23892,7 @@
         <v>13</v>
       </c>
       <c r="D211" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E211">
         <v>2016</v>
@@ -23945,7 +23945,7 @@
         <v>13</v>
       </c>
       <c r="D212" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E212">
         <v>2016</v>
@@ -24051,7 +24051,7 @@
         <v>13</v>
       </c>
       <c r="D214" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E214">
         <v>2022</v>
@@ -24104,7 +24104,7 @@
         <v>13</v>
       </c>
       <c r="D215" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E215">
         <v>2009</v>
@@ -24157,7 +24157,7 @@
         <v>13</v>
       </c>
       <c r="D216" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="E216">
         <v>2006</v>
@@ -24263,7 +24263,7 @@
         <v>13</v>
       </c>
       <c r="D218" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E218">
         <v>1994</v>
@@ -24316,7 +24316,7 @@
         <v>13</v>
       </c>
       <c r="D219" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="E219">
         <v>1994</v>
@@ -24422,7 +24422,7 @@
         <v>13</v>
       </c>
       <c r="D221" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E221">
         <v>2012</v>
@@ -24528,7 +24528,7 @@
         <v>13</v>
       </c>
       <c r="D223" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E223">
         <v>2022</v>
@@ -24687,7 +24687,7 @@
         <v>13</v>
       </c>
       <c r="D226" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E226">
         <v>2009</v>
@@ -24846,7 +24846,7 @@
         <v>13</v>
       </c>
       <c r="D229" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E229">
         <v>2009</v>
@@ -24899,7 +24899,7 @@
         <v>13</v>
       </c>
       <c r="D230" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="E230">
         <v>2002</v>
@@ -24952,7 +24952,7 @@
         <v>13</v>
       </c>
       <c r="D231" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E231">
         <v>2010</v>
@@ -25005,7 +25005,7 @@
         <v>13</v>
       </c>
       <c r="D232" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E232">
         <v>2010</v>
@@ -25058,7 +25058,7 @@
         <v>13</v>
       </c>
       <c r="D233" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E233">
         <v>2012</v>
@@ -25217,7 +25217,7 @@
         <v>13</v>
       </c>
       <c r="D236" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="E236">
         <v>2008</v>
@@ -25270,7 +25270,7 @@
         <v>13</v>
       </c>
       <c r="D237" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E237">
         <v>2009</v>
@@ -25376,7 +25376,7 @@
         <v>13</v>
       </c>
       <c r="D239" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="E239">
         <v>1999</v>
@@ -25482,7 +25482,7 @@
         <v>13</v>
       </c>
       <c r="D241" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E241">
         <v>2014</v>
@@ -25535,7 +25535,7 @@
         <v>13</v>
       </c>
       <c r="D242" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E242">
         <v>2014</v>
@@ -25588,7 +25588,7 @@
         <v>13</v>
       </c>
       <c r="D243" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E243">
         <v>2014</v>
@@ -25641,7 +25641,7 @@
         <v>13</v>
       </c>
       <c r="D244" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E244">
         <v>2014</v>
@@ -25747,7 +25747,7 @@
         <v>13</v>
       </c>
       <c r="D246" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E246">
         <v>2022</v>
@@ -25800,7 +25800,7 @@
         <v>13</v>
       </c>
       <c r="D247" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E247">
         <v>2013</v>
@@ -25853,7 +25853,7 @@
         <v>13</v>
       </c>
       <c r="D248" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E248">
         <v>2013</v>
@@ -25906,7 +25906,7 @@
         <v>13</v>
       </c>
       <c r="D249" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="E249">
         <v>1994</v>
@@ -26065,7 +26065,7 @@
         <v>13</v>
       </c>
       <c r="D252" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E252">
         <v>2005</v>
@@ -26171,7 +26171,7 @@
         <v>13</v>
       </c>
       <c r="D254" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E254">
         <v>2009</v>
@@ -26277,7 +26277,7 @@
         <v>13</v>
       </c>
       <c r="D256" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="E256">
         <v>2000</v>
@@ -26330,7 +26330,7 @@
         <v>13</v>
       </c>
       <c r="D257" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E257">
         <v>2022</v>
@@ -26436,7 +26436,7 @@
         <v>13</v>
       </c>
       <c r="D259" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E259">
         <v>2028</v>
@@ -26489,7 +26489,7 @@
         <v>13</v>
       </c>
       <c r="D260" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E260">
         <v>2022</v>
@@ -26542,7 +26542,7 @@
         <v>13</v>
       </c>
       <c r="D261" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E261">
         <v>2023</v>
@@ -26595,7 +26595,7 @@
         <v>13</v>
       </c>
       <c r="D262" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E262">
         <v>2022</v>
@@ -26648,7 +26648,7 @@
         <v>13</v>
       </c>
       <c r="D263" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E263">
         <v>2022</v>
@@ -26701,7 +26701,7 @@
         <v>13</v>
       </c>
       <c r="D264" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E264">
         <v>2005</v>
@@ -26754,7 +26754,7 @@
         <v>13</v>
       </c>
       <c r="D265" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E265">
         <v>2013</v>
@@ -26807,7 +26807,7 @@
         <v>13</v>
       </c>
       <c r="D266" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E266">
         <v>2020</v>
@@ -26860,7 +26860,7 @@
         <v>13</v>
       </c>
       <c r="D267" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E267">
         <v>2026</v>
@@ -26913,7 +26913,7 @@
         <v>13</v>
       </c>
       <c r="D268" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E268">
         <v>2028</v>
@@ -27549,7 +27549,7 @@
         <v>13</v>
       </c>
       <c r="D280" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E280">
         <v>2007</v>
@@ -27602,7 +27602,7 @@
         <v>13</v>
       </c>
       <c r="D281" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E281">
         <v>2008</v>
@@ -27655,7 +27655,7 @@
         <v>13</v>
       </c>
       <c r="D282" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E282">
         <v>2010</v>
@@ -27920,7 +27920,7 @@
         <v>13</v>
       </c>
       <c r="D287" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E287">
         <v>2003</v>
@@ -27973,7 +27973,7 @@
         <v>13</v>
       </c>
       <c r="D288" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E288">
         <v>2012</v>
@@ -28026,7 +28026,7 @@
         <v>13</v>
       </c>
       <c r="D289" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E289">
         <v>2020</v>
@@ -28821,7 +28821,7 @@
         <v>13</v>
       </c>
       <c r="D304" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E304">
         <v>2002</v>
@@ -28874,7 +28874,7 @@
         <v>13</v>
       </c>
       <c r="D305" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E305">
         <v>2008</v>
@@ -28927,7 +28927,7 @@
         <v>13</v>
       </c>
       <c r="D306" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E306">
         <v>2020</v>
@@ -29092,19 +29092,19 @@
         <v>2022</v>
       </c>
       <c r="F309">
-        <v>2.1832634633989084E-2</v>
+        <v>5.7167365366011094E-2</v>
       </c>
       <c r="G309">
-        <v>0.31680000000000003</v>
+        <v>0.32640000000000002</v>
       </c>
       <c r="H309">
-        <v>2295</v>
+        <v>1955</v>
       </c>
       <c r="I309">
-        <v>70.2</v>
+        <v>59.399999999999991</v>
       </c>
       <c r="J309">
-        <v>5.4</v>
+        <v>4.95</v>
       </c>
       <c r="K309">
         <v>50</v>
@@ -29145,19 +29145,19 @@
         <v>2022</v>
       </c>
       <c r="F310">
-        <v>5.7167365366011094E-2</v>
+        <v>2.1832634633989084E-2</v>
       </c>
       <c r="G310">
-        <v>0.32640000000000002</v>
+        <v>0.31680000000000003</v>
       </c>
       <c r="H310">
-        <v>1955</v>
+        <v>2295</v>
       </c>
       <c r="I310">
-        <v>59.399999999999991</v>
+        <v>70.2</v>
       </c>
       <c r="J310">
-        <v>4.95</v>
+        <v>5.4</v>
       </c>
       <c r="K310">
         <v>50</v>
@@ -29298,7 +29298,7 @@
         <v>273</v>
       </c>
       <c r="D313" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E313">
         <v>1965</v>
@@ -29351,7 +29351,7 @@
         <v>273</v>
       </c>
       <c r="D314" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E314">
         <v>1967</v>
@@ -29404,7 +29404,7 @@
         <v>273</v>
       </c>
       <c r="D315" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E315">
         <v>1974</v>
@@ -29457,7 +29457,7 @@
         <v>273</v>
       </c>
       <c r="D316" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E316">
         <v>1973</v>
@@ -29510,7 +29510,7 @@
         <v>273</v>
       </c>
       <c r="D317" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E317">
         <v>1979</v>
@@ -29563,7 +29563,7 @@
         <v>273</v>
       </c>
       <c r="D318" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E318">
         <v>1982</v>
@@ -29616,7 +29616,7 @@
         <v>273</v>
       </c>
       <c r="D319" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E319">
         <v>1996</v>
@@ -29722,7 +29722,7 @@
         <v>273</v>
       </c>
       <c r="D321" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E321">
         <v>2012</v>
@@ -29775,7 +29775,7 @@
         <v>273</v>
       </c>
       <c r="D322" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E322">
         <v>2013</v>
@@ -29828,7 +29828,7 @@
         <v>273</v>
       </c>
       <c r="D323" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E323">
         <v>2013</v>
@@ -29940,19 +29940,19 @@
         <v>2022</v>
       </c>
       <c r="F325">
-        <v>1.6740910777858737E-2</v>
+        <v>0.12672508144217959</v>
       </c>
       <c r="G325">
-        <v>0.53760000000000008</v>
+        <v>0.55679999999999996</v>
       </c>
       <c r="H325">
-        <v>1147.5</v>
+        <v>977.5</v>
       </c>
       <c r="I325">
-        <v>35.1</v>
+        <v>29.7</v>
       </c>
       <c r="J325">
-        <v>3.2399999999999998</v>
+        <v>2.97</v>
       </c>
       <c r="K325">
         <v>50</v>
@@ -29993,19 +29993,19 @@
         <v>2022</v>
       </c>
       <c r="F326">
-        <v>0.22960339789143816</v>
+        <v>1.6740910777858737E-2</v>
       </c>
       <c r="G326">
-        <v>0.55679999999999996</v>
+        <v>0.53760000000000008</v>
       </c>
       <c r="H326">
-        <v>977.5</v>
+        <v>1147.5</v>
       </c>
       <c r="I326">
-        <v>29.700000000000003</v>
+        <v>35.1</v>
       </c>
       <c r="J326">
-        <v>2.97</v>
+        <v>3.2399999999999998</v>
       </c>
       <c r="K326">
         <v>50</v>
@@ -30040,25 +30040,25 @@
         <v>296</v>
       </c>
       <c r="D327" t="s">
-        <v>299</v>
+        <v>250</v>
       </c>
       <c r="E327">
         <v>2022</v>
       </c>
       <c r="F327">
-        <v>4.6489147915492607E-2</v>
+        <v>7.0468394936152146E-2</v>
       </c>
       <c r="G327">
-        <v>0.53760000000000008</v>
+        <v>0.55679999999999996</v>
       </c>
       <c r="H327">
-        <v>1147.5</v>
+        <v>977.5</v>
       </c>
       <c r="I327">
-        <v>35.1</v>
+        <v>29.7</v>
       </c>
       <c r="J327">
-        <v>3.2399999999999998</v>
+        <v>2.97</v>
       </c>
       <c r="K327">
         <v>50</v>
@@ -30093,19 +30093,19 @@
         <v>296</v>
       </c>
       <c r="D328" t="s">
-        <v>300</v>
+        <v>125</v>
       </c>
       <c r="E328">
         <v>2022</v>
       </c>
       <c r="F328">
-        <v>6.9372407252134061E-2</v>
+        <v>0.14102109661722875</v>
       </c>
       <c r="G328">
         <v>0.55679999999999996</v>
       </c>
       <c r="H328">
-        <v>977.49999999999989</v>
+        <v>977.5</v>
       </c>
       <c r="I328">
         <v>29.700000000000003</v>
@@ -30146,25 +30146,25 @@
         <v>296</v>
       </c>
       <c r="D329" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E329">
         <v>2022</v>
       </c>
       <c r="F329">
-        <v>0.11472943602149809</v>
+        <v>2.9989113551703785E-2</v>
       </c>
       <c r="G329">
-        <v>0.55679999999999996</v>
+        <v>0.53760000000000008</v>
       </c>
       <c r="H329">
-        <v>977.5</v>
+        <v>1147.5</v>
       </c>
       <c r="I329">
-        <v>29.7</v>
+        <v>35.099999999999994</v>
       </c>
       <c r="J329">
-        <v>2.97</v>
+        <v>3.2399999999999998</v>
       </c>
       <c r="K329">
         <v>50</v>
@@ -30199,13 +30199,13 @@
         <v>296</v>
       </c>
       <c r="D330" t="s">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="E330">
         <v>2022</v>
       </c>
       <c r="F330">
-        <v>7.0468394936152146E-2</v>
+        <v>0.11472943602149809</v>
       </c>
       <c r="G330">
         <v>0.55679999999999996</v>
@@ -30252,25 +30252,25 @@
         <v>296</v>
       </c>
       <c r="D331" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E331">
         <v>2022</v>
       </c>
       <c r="F331">
-        <v>0.11441629668320721</v>
+        <v>0.36251900317521435</v>
       </c>
       <c r="G331">
-        <v>0.55679999999999996</v>
+        <v>0.57599999999999996</v>
       </c>
       <c r="H331">
-        <v>977.5</v>
+        <v>850</v>
       </c>
       <c r="I331">
-        <v>29.7</v>
+        <v>27</v>
       </c>
       <c r="J331">
-        <v>2.9700000000000006</v>
+        <v>2.7</v>
       </c>
       <c r="K331">
         <v>50</v>
@@ -30305,13 +30305,13 @@
         <v>296</v>
       </c>
       <c r="D332" t="s">
-        <v>303</v>
+        <v>16</v>
       </c>
       <c r="E332">
         <v>2022</v>
       </c>
       <c r="F332">
-        <v>2.6363923519951642E-2</v>
+        <v>3.8058473423045767E-2</v>
       </c>
       <c r="G332">
         <v>0.53760000000000008</v>
@@ -30358,25 +30358,25 @@
         <v>296</v>
       </c>
       <c r="D333" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E333">
         <v>2022</v>
       </c>
       <c r="F333">
-        <v>2.8302978653214416E-2</v>
+        <v>0.19185806380668324</v>
       </c>
       <c r="G333">
-        <v>0.53760000000000008</v>
+        <v>0.55679999999999996</v>
       </c>
       <c r="H333">
-        <v>1147.5</v>
+        <v>977.5</v>
       </c>
       <c r="I333">
-        <v>35.1</v>
+        <v>29.700000000000003</v>
       </c>
       <c r="J333">
-        <v>3.2399999999999998</v>
+        <v>2.9699999999999998</v>
       </c>
       <c r="K333">
         <v>50</v>
@@ -30411,13 +30411,13 @@
         <v>296</v>
       </c>
       <c r="D334" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E334">
         <v>2022</v>
       </c>
       <c r="F334">
-        <v>2.8327066294621405E-2</v>
+        <v>4.2032934255199286E-2</v>
       </c>
       <c r="G334">
         <v>0.53760000000000008</v>
@@ -30464,25 +30464,25 @@
         <v>296</v>
       </c>
       <c r="D335" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E335">
         <v>2022</v>
       </c>
       <c r="F335">
-        <v>5.8292092204918204E-2</v>
+        <v>0.16764998419265731</v>
       </c>
       <c r="G335">
         <v>0.55679999999999996</v>
       </c>
       <c r="H335">
-        <v>977.5</v>
+        <v>977.50000000000011</v>
       </c>
       <c r="I335">
         <v>29.699999999999996</v>
       </c>
       <c r="J335">
-        <v>2.9700000000000006</v>
+        <v>2.97</v>
       </c>
       <c r="K335">
         <v>50</v>
@@ -30517,13 +30517,13 @@
         <v>296</v>
       </c>
       <c r="D336" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E336">
         <v>2022</v>
       </c>
       <c r="F336">
-        <v>0.12672508144217959</v>
+        <v>5.0945361575785941E-2</v>
       </c>
       <c r="G336">
         <v>0.55679999999999996</v>
@@ -30532,7 +30532,7 @@
         <v>977.5</v>
       </c>
       <c r="I336">
-        <v>29.7</v>
+        <v>29.699999999999996</v>
       </c>
       <c r="J336">
         <v>2.97</v>
@@ -30570,25 +30570,25 @@
         <v>296</v>
       </c>
       <c r="D337" t="s">
-        <v>308</v>
+        <v>51</v>
       </c>
       <c r="E337">
         <v>2022</v>
       </c>
       <c r="F337">
-        <v>6.3832249728526122E-2</v>
+        <v>4.4923451224038201E-2</v>
       </c>
       <c r="G337">
-        <v>0.55679999999999996</v>
+        <v>0.53760000000000008</v>
       </c>
       <c r="H337">
-        <v>977.5</v>
+        <v>1147.5</v>
       </c>
       <c r="I337">
-        <v>29.7</v>
+        <v>35.1</v>
       </c>
       <c r="J337">
-        <v>2.97</v>
+        <v>3.2399999999999993</v>
       </c>
       <c r="K337">
         <v>50</v>
@@ -30623,25 +30623,25 @@
         <v>296</v>
       </c>
       <c r="D338" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="E338">
         <v>2022</v>
       </c>
       <c r="F338">
-        <v>3.8901540872290453E-2</v>
+        <v>5.8292092204918204E-2</v>
       </c>
       <c r="G338">
-        <v>0.53760000000000008</v>
+        <v>0.55679999999999996</v>
       </c>
       <c r="H338">
-        <v>1147.5</v>
+        <v>977.5</v>
       </c>
       <c r="I338">
-        <v>35.1</v>
+        <v>29.699999999999996</v>
       </c>
       <c r="J338">
-        <v>3.2399999999999998</v>
+        <v>2.9700000000000006</v>
       </c>
       <c r="K338">
         <v>50</v>
@@ -30676,25 +30676,25 @@
         <v>296</v>
       </c>
       <c r="D339" t="s">
-        <v>279</v>
+        <v>307</v>
       </c>
       <c r="E339">
         <v>2022</v>
       </c>
       <c r="F339">
-        <v>0.26568668471911061</v>
+        <v>2.8327066294621405E-2</v>
       </c>
       <c r="G339">
-        <v>0.55679999999999996</v>
+        <v>0.53760000000000008</v>
       </c>
       <c r="H339">
-        <v>977.5</v>
+        <v>1147.5</v>
       </c>
       <c r="I339">
-        <v>29.7</v>
+        <v>35.1</v>
       </c>
       <c r="J339">
-        <v>2.97</v>
+        <v>3.2399999999999998</v>
       </c>
       <c r="K339">
         <v>50</v>
@@ -30729,25 +30729,25 @@
         <v>296</v>
       </c>
       <c r="D340" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E340">
         <v>2022</v>
       </c>
       <c r="F340">
-        <v>7.708045250237118E-2</v>
+        <v>3.8901540872290453E-2</v>
       </c>
       <c r="G340">
-        <v>0.55679999999999996</v>
+        <v>0.53760000000000008</v>
       </c>
       <c r="H340">
-        <v>977.5</v>
+        <v>1147.5</v>
       </c>
       <c r="I340">
-        <v>29.7</v>
+        <v>35.1</v>
       </c>
       <c r="J340">
-        <v>2.97</v>
+        <v>3.2399999999999998</v>
       </c>
       <c r="K340">
         <v>50</v>
@@ -30782,25 +30782,25 @@
         <v>296</v>
       </c>
       <c r="D341" t="s">
-        <v>311</v>
+        <v>279</v>
       </c>
       <c r="E341">
         <v>2022</v>
       </c>
       <c r="F341">
-        <v>4.2032934255199286E-2</v>
+        <v>0.26568668471911061</v>
       </c>
       <c r="G341">
-        <v>0.53760000000000008</v>
+        <v>0.55679999999999996</v>
       </c>
       <c r="H341">
-        <v>1147.5</v>
+        <v>977.5</v>
       </c>
       <c r="I341">
-        <v>35.1</v>
+        <v>29.7</v>
       </c>
       <c r="J341">
-        <v>3.2399999999999998</v>
+        <v>2.97</v>
       </c>
       <c r="K341">
         <v>50</v>
@@ -30835,13 +30835,13 @@
         <v>296</v>
       </c>
       <c r="D342" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E342">
         <v>2022</v>
       </c>
       <c r="F342">
-        <v>0.19185806380668324</v>
+        <v>7.708045250237118E-2</v>
       </c>
       <c r="G342">
         <v>0.55679999999999996</v>
@@ -30850,10 +30850,10 @@
         <v>977.5</v>
       </c>
       <c r="I342">
-        <v>29.700000000000003</v>
+        <v>29.7</v>
       </c>
       <c r="J342">
-        <v>2.9699999999999998</v>
+        <v>2.97</v>
       </c>
       <c r="K342">
         <v>50</v>
@@ -30888,25 +30888,25 @@
         <v>296</v>
       </c>
       <c r="D343" t="s">
-        <v>25</v>
+        <v>310</v>
       </c>
       <c r="E343">
         <v>2022</v>
       </c>
       <c r="F343">
-        <v>3.8058473423045767E-2</v>
+        <v>6.4193564349630985E-2</v>
       </c>
       <c r="G343">
-        <v>0.53760000000000008</v>
+        <v>0.55679999999999996</v>
       </c>
       <c r="H343">
-        <v>1147.5</v>
+        <v>977.5</v>
       </c>
       <c r="I343">
-        <v>35.1</v>
+        <v>29.7</v>
       </c>
       <c r="J343">
-        <v>3.2399999999999998</v>
+        <v>2.97</v>
       </c>
       <c r="K343">
         <v>50</v>
@@ -30941,25 +30941,25 @@
         <v>296</v>
       </c>
       <c r="D344" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E344">
         <v>2022</v>
       </c>
       <c r="F344">
-        <v>0.36251900317521435</v>
+        <v>0.22960339789143816</v>
       </c>
       <c r="G344">
-        <v>0.57599999999999996</v>
+        <v>0.55679999999999996</v>
       </c>
       <c r="H344">
-        <v>850</v>
+        <v>977.5</v>
       </c>
       <c r="I344">
-        <v>27</v>
+        <v>29.700000000000003</v>
       </c>
       <c r="J344">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="K344">
         <v>50</v>
@@ -30994,25 +30994,25 @@
         <v>296</v>
       </c>
       <c r="D345" t="s">
-        <v>314</v>
+        <v>276</v>
       </c>
       <c r="E345">
         <v>2022</v>
       </c>
       <c r="F345">
-        <v>2.9989113551703785E-2</v>
+        <v>8.9967340655111347E-2</v>
       </c>
       <c r="G345">
-        <v>0.53760000000000008</v>
+        <v>0.55679999999999996</v>
       </c>
       <c r="H345">
-        <v>1147.5</v>
+        <v>977.5</v>
       </c>
       <c r="I345">
-        <v>35.099999999999994</v>
+        <v>29.7</v>
       </c>
       <c r="J345">
-        <v>3.2399999999999998</v>
+        <v>2.97</v>
       </c>
       <c r="K345">
         <v>50</v>
@@ -31047,25 +31047,25 @@
         <v>296</v>
       </c>
       <c r="D346" t="s">
-        <v>125</v>
+        <v>312</v>
       </c>
       <c r="E346">
         <v>2022</v>
       </c>
       <c r="F346">
-        <v>0.14102109661722875</v>
+        <v>3.0109551758738737E-2</v>
       </c>
       <c r="G346">
-        <v>0.55679999999999996</v>
+        <v>0.53760000000000008</v>
       </c>
       <c r="H346">
-        <v>977.5</v>
+        <v>1147.5</v>
       </c>
       <c r="I346">
-        <v>29.700000000000003</v>
+        <v>35.1</v>
       </c>
       <c r="J346">
-        <v>2.97</v>
+        <v>3.2399999999999998</v>
       </c>
       <c r="K346">
         <v>50</v>
@@ -31100,13 +31100,13 @@
         <v>296</v>
       </c>
       <c r="D347" t="s">
-        <v>51</v>
+        <v>313</v>
       </c>
       <c r="E347">
         <v>2022</v>
       </c>
       <c r="F347">
-        <v>4.4923451224038201E-2</v>
+        <v>2.8302978653214416E-2</v>
       </c>
       <c r="G347">
         <v>0.53760000000000008</v>
@@ -31118,7 +31118,7 @@
         <v>35.1</v>
       </c>
       <c r="J347">
-        <v>3.2399999999999993</v>
+        <v>3.2399999999999998</v>
       </c>
       <c r="K347">
         <v>50</v>
@@ -31153,25 +31153,25 @@
         <v>296</v>
       </c>
       <c r="D348" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E348">
         <v>2022</v>
       </c>
       <c r="F348">
-        <v>5.0945361575785941E-2</v>
+        <v>2.6363923519951642E-2</v>
       </c>
       <c r="G348">
-        <v>0.55679999999999996</v>
+        <v>0.53760000000000008</v>
       </c>
       <c r="H348">
-        <v>977.5</v>
+        <v>1147.5</v>
       </c>
       <c r="I348">
-        <v>29.699999999999996</v>
+        <v>35.1</v>
       </c>
       <c r="J348">
-        <v>2.97</v>
+        <v>3.2399999999999998</v>
       </c>
       <c r="K348">
         <v>50</v>
@@ -31206,25 +31206,25 @@
         <v>296</v>
       </c>
       <c r="D349" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E349">
         <v>2022</v>
       </c>
       <c r="F349">
-        <v>0.16764998419265731</v>
+        <v>0.11441629668320721</v>
       </c>
       <c r="G349">
         <v>0.55679999999999996</v>
       </c>
       <c r="H349">
-        <v>977.50000000000011</v>
+        <v>977.5</v>
       </c>
       <c r="I349">
-        <v>29.699999999999996</v>
+        <v>29.7</v>
       </c>
       <c r="J349">
-        <v>2.97</v>
+        <v>2.9700000000000006</v>
       </c>
       <c r="K349">
         <v>50</v>
@@ -31259,22 +31259,22 @@
         <v>296</v>
       </c>
       <c r="D350" t="s">
-        <v>277</v>
+        <v>316</v>
       </c>
       <c r="E350">
         <v>2022</v>
       </c>
       <c r="F350">
-        <v>8.9967340655111347E-2</v>
+        <v>6.9372407252134061E-2</v>
       </c>
       <c r="G350">
         <v>0.55679999999999996</v>
       </c>
       <c r="H350">
-        <v>977.5</v>
+        <v>977.49999999999989</v>
       </c>
       <c r="I350">
-        <v>29.7</v>
+        <v>29.700000000000003</v>
       </c>
       <c r="J350">
         <v>2.97</v>
@@ -31318,7 +31318,7 @@
         <v>2022</v>
       </c>
       <c r="F351">
-        <v>3.0109551758738737E-2</v>
+        <v>4.6489147915492607E-2</v>
       </c>
       <c r="G351">
         <v>0.53760000000000008</v>
@@ -31371,7 +31371,7 @@
         <v>2022</v>
       </c>
       <c r="F352">
-        <v>6.4193564349630985E-2</v>
+        <v>6.3832249728526122E-2</v>
       </c>
       <c r="G352">
         <v>0.55679999999999996</v>
@@ -31418,7 +31418,7 @@
         <v>296</v>
       </c>
       <c r="D353" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E353">
         <v>2000</v>
@@ -31471,7 +31471,7 @@
         <v>296</v>
       </c>
       <c r="D354" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E354">
         <v>2004</v>
@@ -31524,7 +31524,7 @@
         <v>296</v>
       </c>
       <c r="D355" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="E355">
         <v>2001</v>
@@ -31577,7 +31577,7 @@
         <v>296</v>
       </c>
       <c r="D356" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="E356">
         <v>2015</v>
@@ -31630,7 +31630,7 @@
         <v>296</v>
       </c>
       <c r="D357" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E357">
         <v>2023</v>
@@ -31736,7 +31736,7 @@
         <v>296</v>
       </c>
       <c r="D359" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="E359">
         <v>2020</v>
@@ -31789,7 +31789,7 @@
         <v>296</v>
       </c>
       <c r="D360" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="E360">
         <v>2022</v>
@@ -31842,7 +31842,7 @@
         <v>296</v>
       </c>
       <c r="D361" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="E361">
         <v>2016</v>
@@ -31948,7 +31948,7 @@
         <v>296</v>
       </c>
       <c r="D363" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="E363">
         <v>2004</v>
@@ -32054,7 +32054,7 @@
         <v>296</v>
       </c>
       <c r="D365" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="E365">
         <v>2023</v>
@@ -32107,7 +32107,7 @@
         <v>296</v>
       </c>
       <c r="D366" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="E366">
         <v>2012</v>
@@ -32213,7 +32213,7 @@
         <v>296</v>
       </c>
       <c r="D368" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E368">
         <v>2006</v>
@@ -32266,7 +32266,7 @@
         <v>296</v>
       </c>
       <c r="D369" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E369">
         <v>2006</v>
@@ -32319,7 +32319,7 @@
         <v>296</v>
       </c>
       <c r="D370" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E370">
         <v>2006</v>
@@ -32372,7 +32372,7 @@
         <v>296</v>
       </c>
       <c r="D371" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="E371">
         <v>2025</v>
@@ -32425,7 +32425,7 @@
         <v>296</v>
       </c>
       <c r="D372" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="E372">
         <v>2021</v>
@@ -32478,7 +32478,7 @@
         <v>296</v>
       </c>
       <c r="D373" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E373">
         <v>2003</v>
@@ -32531,7 +32531,7 @@
         <v>296</v>
       </c>
       <c r="D374" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="E374">
         <v>2006</v>
@@ -32584,7 +32584,7 @@
         <v>296</v>
       </c>
       <c r="D375" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="E375">
         <v>2009</v>
@@ -32743,7 +32743,7 @@
         <v>296</v>
       </c>
       <c r="D378" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="E378">
         <v>2014</v>
@@ -32796,7 +32796,7 @@
         <v>296</v>
       </c>
       <c r="D379" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="E379">
         <v>2002</v>
@@ -32902,7 +32902,7 @@
         <v>296</v>
       </c>
       <c r="D381" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="E381">
         <v>2006</v>
@@ -33008,7 +33008,7 @@
         <v>296</v>
       </c>
       <c r="D383" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="E383">
         <v>2026</v>
@@ -33061,7 +33061,7 @@
         <v>296</v>
       </c>
       <c r="D384" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E384">
         <v>2002</v>
@@ -33273,7 +33273,7 @@
         <v>296</v>
       </c>
       <c r="D388" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="E388">
         <v>2013</v>
@@ -33326,7 +33326,7 @@
         <v>296</v>
       </c>
       <c r="D389" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E389">
         <v>2008</v>
@@ -33379,7 +33379,7 @@
         <v>296</v>
       </c>
       <c r="D390" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E390">
         <v>2008</v>
@@ -33485,7 +33485,7 @@
         <v>296</v>
       </c>
       <c r="D392" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="E392">
         <v>2026</v>
@@ -33591,7 +33591,7 @@
         <v>296</v>
       </c>
       <c r="D394" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E394">
         <v>2022</v>
@@ -33644,7 +33644,7 @@
         <v>296</v>
       </c>
       <c r="D395" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E395">
         <v>2022</v>
@@ -33697,7 +33697,7 @@
         <v>296</v>
       </c>
       <c r="D396" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="E396">
         <v>2022</v>
@@ -33803,7 +33803,7 @@
         <v>296</v>
       </c>
       <c r="D398" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="E398">
         <v>2013</v>
@@ -33909,7 +33909,7 @@
         <v>296</v>
       </c>
       <c r="D400" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E400">
         <v>2010</v>
@@ -33962,7 +33962,7 @@
         <v>296</v>
       </c>
       <c r="D401" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E401">
         <v>2022</v>
@@ -34015,7 +34015,7 @@
         <v>296</v>
       </c>
       <c r="D402" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E402">
         <v>2022</v>
@@ -34174,7 +34174,7 @@
         <v>296</v>
       </c>
       <c r="D405" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E405">
         <v>1976</v>
@@ -34227,7 +34227,7 @@
         <v>296</v>
       </c>
       <c r="D406" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="E406">
         <v>2025</v>
@@ -34280,7 +34280,7 @@
         <v>296</v>
       </c>
       <c r="D407" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E407">
         <v>1994</v>
@@ -34333,7 +34333,7 @@
         <v>296</v>
       </c>
       <c r="D408" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="E408">
         <v>2003</v>
@@ -34386,7 +34386,7 @@
         <v>296</v>
       </c>
       <c r="D409" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="E409">
         <v>2003</v>
@@ -34439,7 +34439,7 @@
         <v>296</v>
       </c>
       <c r="D410" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="E410">
         <v>2003</v>
@@ -34492,7 +34492,7 @@
         <v>296</v>
       </c>
       <c r="D411" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E411">
         <v>2003</v>
@@ -34545,7 +34545,7 @@
         <v>296</v>
       </c>
       <c r="D412" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E412">
         <v>2003</v>
@@ -34598,7 +34598,7 @@
         <v>296</v>
       </c>
       <c r="D413" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="E413">
         <v>2007</v>
@@ -34651,7 +34651,7 @@
         <v>296</v>
       </c>
       <c r="D414" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="E414">
         <v>2007</v>
@@ -34704,7 +34704,7 @@
         <v>296</v>
       </c>
       <c r="D415" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E415">
         <v>2016</v>
@@ -34757,7 +34757,7 @@
         <v>296</v>
       </c>
       <c r="D416" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E416">
         <v>2016</v>
@@ -34810,7 +34810,7 @@
         <v>296</v>
       </c>
       <c r="D417" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="E417">
         <v>2002</v>
@@ -34869,19 +34869,19 @@
         <v>2022</v>
       </c>
       <c r="F418">
-        <v>0.17367245842623849</v>
+        <v>0.40156634582967088</v>
       </c>
       <c r="G418">
         <v>1</v>
       </c>
       <c r="H418">
-        <v>2443.75</v>
+        <v>2125</v>
       </c>
       <c r="I418">
-        <v>49.500000000000007</v>
+        <v>45.000000000000007</v>
       </c>
       <c r="J418">
-        <v>1.9800000000000002</v>
+        <v>1.8</v>
       </c>
       <c r="K418">
         <v>100</v>
@@ -34975,19 +34975,19 @@
         <v>2022</v>
       </c>
       <c r="F420">
-        <v>0.40156634582967088</v>
+        <v>0.17367245842623849</v>
       </c>
       <c r="G420">
         <v>1</v>
       </c>
       <c r="H420">
-        <v>2125</v>
+        <v>2443.75</v>
       </c>
       <c r="I420">
-        <v>45.000000000000007</v>
+        <v>49.500000000000007</v>
       </c>
       <c r="J420">
-        <v>1.8</v>
+        <v>1.9800000000000002</v>
       </c>
       <c r="K420">
         <v>100</v>
@@ -35923,7 +35923,7 @@
         <v>385</v>
       </c>
       <c r="D438" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E438">
         <v>2022</v>
@@ -36029,7 +36029,7 @@
         <v>385</v>
       </c>
       <c r="D440" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="E440">
         <v>2022</v>
@@ -36135,7 +36135,7 @@
         <v>385</v>
       </c>
       <c r="D442" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E442">
         <v>2022</v>
@@ -36188,7 +36188,7 @@
         <v>385</v>
       </c>
       <c r="D443" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E443">
         <v>2022</v>
@@ -36294,7 +36294,7 @@
         <v>385</v>
       </c>
       <c r="D445" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E445">
         <v>2022</v>
@@ -36400,7 +36400,7 @@
         <v>385</v>
       </c>
       <c r="D447" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E447">
         <v>1978</v>
@@ -36453,7 +36453,7 @@
         <v>385</v>
       </c>
       <c r="D448" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="E448">
         <v>2022</v>
@@ -37407,7 +37407,7 @@
         <v>385</v>
       </c>
       <c r="D466" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E466">
         <v>1963</v>
@@ -37513,7 +37513,7 @@
         <v>385</v>
       </c>
       <c r="D468" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E468">
         <v>2016</v>
@@ -37778,7 +37778,7 @@
         <v>385</v>
       </c>
       <c r="D473" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E473">
         <v>1996</v>
@@ -37990,7 +37990,7 @@
         <v>385</v>
       </c>
       <c r="D477" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E477">
         <v>1940</v>
@@ -38202,7 +38202,7 @@
         <v>385</v>
       </c>
       <c r="D481" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E481">
         <v>2012</v>
@@ -38467,7 +38467,7 @@
         <v>385</v>
       </c>
       <c r="D486" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E486">
         <v>1980</v>
@@ -38732,7 +38732,7 @@
         <v>385</v>
       </c>
       <c r="D491" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E491">
         <v>1975</v>
@@ -38785,7 +38785,7 @@
         <v>385</v>
       </c>
       <c r="D492" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E492">
         <v>1998</v>
@@ -38891,7 +38891,7 @@
         <v>385</v>
       </c>
       <c r="D494" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E494">
         <v>1994</v>
@@ -39156,7 +39156,7 @@
         <v>385</v>
       </c>
       <c r="D499" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E499">
         <v>1999</v>
@@ -39209,7 +39209,7 @@
         <v>385</v>
       </c>
       <c r="D500" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="E500">
         <v>1975</v>
@@ -39898,7 +39898,7 @@
         <v>385</v>
       </c>
       <c r="D513" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E513">
         <v>1984</v>
@@ -39951,7 +39951,7 @@
         <v>385</v>
       </c>
       <c r="D514" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E514">
         <v>2022</v>
@@ -40375,7 +40375,7 @@
         <v>385</v>
       </c>
       <c r="D522" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="E522">
         <v>2022</v>
@@ -41117,7 +41117,7 @@
         <v>385</v>
       </c>
       <c r="D536" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E536">
         <v>2002</v>
@@ -41435,7 +41435,7 @@
         <v>385</v>
       </c>
       <c r="D542" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E542">
         <v>1999</v>
@@ -41753,7 +41753,7 @@
         <v>385</v>
       </c>
       <c r="D548" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E548">
         <v>1959</v>
@@ -42283,7 +42283,7 @@
         <v>385</v>
       </c>
       <c r="D558" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="E558">
         <v>1926</v>
@@ -42389,7 +42389,7 @@
         <v>385</v>
       </c>
       <c r="D560" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="E560">
         <v>1998</v>
@@ -42442,7 +42442,7 @@
         <v>385</v>
       </c>
       <c r="D561" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="E561">
         <v>1924</v>
@@ -42760,7 +42760,7 @@
         <v>385</v>
       </c>
       <c r="D567" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="E567">
         <v>1971</v>
@@ -42866,7 +42866,7 @@
         <v>385</v>
       </c>
       <c r="D569" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="E569">
         <v>1969</v>
@@ -42972,7 +42972,7 @@
         <v>385</v>
       </c>
       <c r="D571" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E571">
         <v>1973</v>
@@ -43025,7 +43025,7 @@
         <v>385</v>
       </c>
       <c r="D572" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E572">
         <v>1953</v>
@@ -43078,7 +43078,7 @@
         <v>385</v>
       </c>
       <c r="D573" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="E573">
         <v>1982</v>
@@ -43396,7 +43396,7 @@
         <v>385</v>
       </c>
       <c r="D579" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E579">
         <v>1973</v>
@@ -43449,7 +43449,7 @@
         <v>385</v>
       </c>
       <c r="D580" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E580">
         <v>1987</v>
@@ -43661,7 +43661,7 @@
         <v>385</v>
       </c>
       <c r="D584" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="E584">
         <v>2013</v>
@@ -43714,7 +43714,7 @@
         <v>385</v>
       </c>
       <c r="D585" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E585">
         <v>1992</v>
@@ -43820,7 +43820,7 @@
         <v>385</v>
       </c>
       <c r="D587" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E587">
         <v>1993</v>
@@ -43873,7 +43873,7 @@
         <v>385</v>
       </c>
       <c r="D588" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="E588">
         <v>1974</v>
@@ -44032,7 +44032,7 @@
         <v>385</v>
       </c>
       <c r="D591" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E591">
         <v>2012</v>
@@ -44244,7 +44244,7 @@
         <v>385</v>
       </c>
       <c r="D595" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="E595">
         <v>2013</v>
@@ -44403,7 +44403,7 @@
         <v>385</v>
       </c>
       <c r="D598" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E598">
         <v>1962</v>
@@ -44615,7 +44615,7 @@
         <v>618</v>
       </c>
       <c r="D602" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E602">
         <v>2011</v>
@@ -44668,7 +44668,7 @@
         <v>618</v>
       </c>
       <c r="D603" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E603">
         <v>2011</v>
@@ -44774,7 +44774,7 @@
         <v>618</v>
       </c>
       <c r="D605" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="E605">
         <v>2009</v>
@@ -44986,7 +44986,7 @@
         <v>618</v>
       </c>
       <c r="D609" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="E609">
         <v>2000</v>
@@ -45940,7 +45940,7 @@
         <v>618</v>
       </c>
       <c r="D627" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E627">
         <v>2013</v>
@@ -46205,7 +46205,7 @@
         <v>618</v>
       </c>
       <c r="D632" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E632">
         <v>2020</v>
@@ -46258,7 +46258,7 @@
         <v>618</v>
       </c>
       <c r="D633" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="E633">
         <v>2015</v>
@@ -46311,7 +46311,7 @@
         <v>618</v>
       </c>
       <c r="D634" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="E634">
         <v>1978</v>
@@ -46364,7 +46364,7 @@
         <v>618</v>
       </c>
       <c r="D635" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E635">
         <v>2011</v>
@@ -46423,7 +46423,7 @@
         <v>2022</v>
       </c>
       <c r="F636">
-        <v>4.5022605164519689</v>
+        <v>4.3543095894137336</v>
       </c>
       <c r="G636">
         <v>1</v>
@@ -46479,7 +46479,7 @@
         <v>2022</v>
       </c>
       <c r="F637">
-        <v>4.3543095894137336</v>
+        <v>4.3823138941342954</v>
       </c>
       <c r="G637">
         <v>1</v>
@@ -46535,7 +46535,7 @@
         <v>2022</v>
       </c>
       <c r="F638">
-        <v>4.3823138941342954</v>
+        <v>4.5022605164519689</v>
       </c>
       <c r="G638">
         <v>1</v>
@@ -50197,7 +50197,7 @@
         <v>659</v>
       </c>
       <c r="D732" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E732">
         <v>2021</v>
@@ -50232,7 +50232,7 @@
         <v>659</v>
       </c>
       <c r="D733" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E733">
         <v>2022</v>
@@ -50267,7 +50267,7 @@
         <v>659</v>
       </c>
       <c r="D734" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E734">
         <v>2023</v>
@@ -50302,7 +50302,7 @@
         <v>659</v>
       </c>
       <c r="D735" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E735">
         <v>2024</v>
@@ -56952,7 +56952,7 @@
         <v>659</v>
       </c>
       <c r="D925" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E925">
         <v>2019</v>
@@ -56987,7 +56987,7 @@
         <v>659</v>
       </c>
       <c r="D926" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E926">
         <v>2021</v>
@@ -57022,7 +57022,7 @@
         <v>659</v>
       </c>
       <c r="D927" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E927">
         <v>2024</v>
@@ -58702,7 +58702,7 @@
         <v>659</v>
       </c>
       <c r="D975" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="E975">
         <v>2020</v>
@@ -58737,7 +58737,7 @@
         <v>659</v>
       </c>
       <c r="D976" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="E976">
         <v>2023</v>
@@ -61292,7 +61292,7 @@
         <v>836</v>
       </c>
       <c r="D1085" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E1085">
         <v>2015</v>

--- a/VerveStacks_BRA_grids/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA_grids/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA1CC312-E961-4A70-9135-4F276D96C5C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFF595D1-CADC-4621-9B51-A525B5279C79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{2559F678-97D1-497D-B64E-675AA7C30BD5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{01CE8406-A3BA-4016-B222-02C12EC2EA13}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -5429,7 +5429,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3A37CD2-C9BE-457A-9839-F4D69CA6958C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FDB8819-7D36-4871-8FC6-4996AD590207}">
   <dimension ref="B9:T154"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -13567,7 +13567,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{700D1ED5-C452-4B33-8597-E4AF7CC685DF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6327817-C84F-4DF1-8F39-DB5FDA72C703}">
   <dimension ref="B9:T1093"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -57873,7 +57873,7 @@
         <v>33</v>
       </c>
       <c r="L922">
-        <v>0.20197946062466646</v>
+        <v>0.20197946062466648</v>
       </c>
     </row>
     <row r="923" spans="2:12" x14ac:dyDescent="0.45">
@@ -58013,7 +58013,7 @@
         <v>33</v>
       </c>
       <c r="L926">
-        <v>0.20197946062466646</v>
+        <v>0.20197946062466648</v>
       </c>
     </row>
     <row r="927" spans="2:12" x14ac:dyDescent="0.45">
@@ -59168,7 +59168,7 @@
         <v>33</v>
       </c>
       <c r="L959">
-        <v>0.20197946062466646</v>
+        <v>0.20197946062466648</v>
       </c>
     </row>
     <row r="960" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_BRA_grids/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA_grids/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFF595D1-CADC-4621-9B51-A525B5279C79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1B63304-4D37-4F25-959D-C7597F7FEF7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{01CE8406-A3BA-4016-B222-02C12EC2EA13}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B45FD6A8-C9EB-48F9-909F-3F3BBD76431E}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -5429,7 +5429,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FDB8819-7D36-4871-8FC6-4996AD590207}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA8677EA-CFBE-413B-9431-55BEE260F79A}">
   <dimension ref="B9:T154"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -13567,7 +13567,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6327817-C84F-4DF1-8F39-DB5FDA72C703}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{872B0A94-C93B-454E-858F-A7BE7B93B40C}">
   <dimension ref="B9:T1093"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -57873,7 +57873,7 @@
         <v>33</v>
       </c>
       <c r="L922">
-        <v>0.20197946062466648</v>
+        <v>0.20197946062466646</v>
       </c>
     </row>
     <row r="923" spans="2:12" x14ac:dyDescent="0.45">
@@ -58013,7 +58013,7 @@
         <v>33</v>
       </c>
       <c r="L926">
-        <v>0.20197946062466648</v>
+        <v>0.20197946062466646</v>
       </c>
     </row>
     <row r="927" spans="2:12" x14ac:dyDescent="0.45">
@@ -59168,7 +59168,7 @@
         <v>33</v>
       </c>
       <c r="L959">
-        <v>0.20197946062466648</v>
+        <v>0.20197946062466646</v>
       </c>
     </row>
     <row r="960" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_BRA_grids/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA_grids/vt_vervestacks_BRA_v1.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8472984D-D4B6-4D40-B497-04FE48A7BC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B84C90D5-9EA9-442B-A494-EBB940DDADCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{ABB54BC3-8E97-4FD9-92BE-346CB878609E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{595D4638-0BE2-41E0-BDA1-91CEE308EC8C}"/>
   </bookViews>
   <sheets>
-    <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
-    <sheet name="new_options" sheetId="3" r:id="rId2"/>
-    <sheet name="existing_stock" sheetId="2" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="additional_hydro_pot" sheetId="5" r:id="rId1"/>
+    <sheet name="ccs_retrofits" sheetId="4" r:id="rId2"/>
+    <sheet name="new_options" sheetId="3" r:id="rId3"/>
+    <sheet name="existing_stock" sheetId="2" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12731" uniqueCount="2245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12809" uniqueCount="2272">
   <si>
     <t>~fi_t</t>
   </si>
@@ -6774,6 +6775,87 @@
   </si>
   <si>
     <t>ccs retrofit of -- Atlântico power station_1</t>
+  </si>
+  <si>
+    <t>Comm-IN</t>
+  </si>
+  <si>
+    <t>Comm-OUT</t>
+  </si>
+  <si>
+    <t>CAP_BND</t>
+  </si>
+  <si>
+    <t>INVCOST~USD21</t>
+  </si>
+  <si>
+    <t>INVCOST~USD21_ALT</t>
+  </si>
+  <si>
+    <t>CF</t>
+  </si>
+  <si>
+    <t>EN_Hydro_Chacorão</t>
+  </si>
+  <si>
+    <t>EN_Hydro_UpXinguCmplx</t>
+  </si>
+  <si>
+    <t>e_BR357-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_TrombeasCasc</t>
+  </si>
+  <si>
+    <t>e_BR24-500</t>
+  </si>
+  <si>
+    <t>EN_Hydro_AraguaiaBDev</t>
+  </si>
+  <si>
+    <t>EN_Hydro_TelesPresUpB</t>
+  </si>
+  <si>
+    <t>EN_Hydro_Uruguational</t>
+  </si>
+  <si>
+    <t>EN_Hydro_SmallH&lt;50MW)</t>
+  </si>
+  <si>
+    <t>Sets</t>
+  </si>
+  <si>
+    <t>TAct</t>
+  </si>
+  <si>
+    <t>TCap</t>
+  </si>
+  <si>
+    <t>ELE</t>
+  </si>
+  <si>
+    <t>Medium-scale hydropower facility on Tapajós. High development priority. Approved for future development</t>
+  </si>
+  <si>
+    <t>DAYNITE</t>
+  </si>
+  <si>
+    <t>Major hydropower development on Xingu. High development priority. Approved for future development</t>
+  </si>
+  <si>
+    <t>Medium-scale hydropower facility on Trombetas. High development priority. Approved for future development</t>
+  </si>
+  <si>
+    <t>Major hydropower development on Araguaia-Tocantins. High development priority. Approved for future development</t>
+  </si>
+  <si>
+    <t>Major hydropower development on Teles Pires. High development priority. Approved for future development</t>
+  </si>
+  <si>
+    <t>Medium-scale hydropower facility on Uruguay. High development priority. Approved for future development</t>
+  </si>
+  <si>
+    <t>Large-scale hydropower project on Various. High development priority. Approved for future development</t>
   </si>
 </sst>
 </file>
@@ -7144,7 +7226,353 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D484428-1BCB-4DE7-B416-CDF5EF39E36A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD85885-40CC-4588-864C-E612F6725992}">
+  <dimension ref="B9:O17"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2245</v>
+      </c>
+      <c r="D10" t="s">
+        <v>2246</v>
+      </c>
+      <c r="E10" t="s">
+        <v>2247</v>
+      </c>
+      <c r="F10" t="s">
+        <v>2248</v>
+      </c>
+      <c r="G10" t="s">
+        <v>2249</v>
+      </c>
+      <c r="H10" t="s">
+        <v>2250</v>
+      </c>
+      <c r="J10" t="s">
+        <v>2260</v>
+      </c>
+      <c r="K10" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" t="s">
+        <v>976</v>
+      </c>
+      <c r="M10" t="s">
+        <v>2261</v>
+      </c>
+      <c r="N10" t="s">
+        <v>2262</v>
+      </c>
+      <c r="O10" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B11" t="s">
+        <v>2251</v>
+      </c>
+      <c r="C11" t="s">
+        <v>478</v>
+      </c>
+      <c r="D11" t="s">
+        <v>430</v>
+      </c>
+      <c r="E11">
+        <v>3.3</v>
+      </c>
+      <c r="F11">
+        <v>2000</v>
+      </c>
+      <c r="G11">
+        <v>268.38448827464327</v>
+      </c>
+      <c r="H11">
+        <v>0.45</v>
+      </c>
+      <c r="J11" t="s">
+        <v>2263</v>
+      </c>
+      <c r="K11" t="s">
+        <v>2251</v>
+      </c>
+      <c r="L11" t="s">
+        <v>2264</v>
+      </c>
+      <c r="M11" t="s">
+        <v>984</v>
+      </c>
+      <c r="N11" t="s">
+        <v>983</v>
+      </c>
+      <c r="O11" t="s">
+        <v>2265</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B12" t="s">
+        <v>2252</v>
+      </c>
+      <c r="C12" t="s">
+        <v>478</v>
+      </c>
+      <c r="D12" t="s">
+        <v>2253</v>
+      </c>
+      <c r="E12">
+        <v>8</v>
+      </c>
+      <c r="F12">
+        <v>2000</v>
+      </c>
+      <c r="G12">
+        <v>286.13283816442208</v>
+      </c>
+      <c r="H12">
+        <v>0.45</v>
+      </c>
+      <c r="J12" t="s">
+        <v>2263</v>
+      </c>
+      <c r="K12" t="s">
+        <v>2252</v>
+      </c>
+      <c r="L12" t="s">
+        <v>2266</v>
+      </c>
+      <c r="M12" t="s">
+        <v>984</v>
+      </c>
+      <c r="N12" t="s">
+        <v>983</v>
+      </c>
+      <c r="O12" t="s">
+        <v>2265</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B13" t="s">
+        <v>2254</v>
+      </c>
+      <c r="C13" t="s">
+        <v>478</v>
+      </c>
+      <c r="D13" t="s">
+        <v>2255</v>
+      </c>
+      <c r="E13">
+        <v>4</v>
+      </c>
+      <c r="F13">
+        <v>2000</v>
+      </c>
+      <c r="G13">
+        <v>126.55976615136606</v>
+      </c>
+      <c r="H13">
+        <v>0.45</v>
+      </c>
+      <c r="J13" t="s">
+        <v>2263</v>
+      </c>
+      <c r="K13" t="s">
+        <v>2254</v>
+      </c>
+      <c r="L13" t="s">
+        <v>2267</v>
+      </c>
+      <c r="M13" t="s">
+        <v>984</v>
+      </c>
+      <c r="N13" t="s">
+        <v>983</v>
+      </c>
+      <c r="O13" t="s">
+        <v>2265</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B14" t="s">
+        <v>2256</v>
+      </c>
+      <c r="C14" t="s">
+        <v>478</v>
+      </c>
+      <c r="D14" t="s">
+        <v>481</v>
+      </c>
+      <c r="E14">
+        <v>6</v>
+      </c>
+      <c r="F14">
+        <v>2000</v>
+      </c>
+      <c r="G14">
+        <v>83.07506500298993</v>
+      </c>
+      <c r="H14">
+        <v>0.45</v>
+      </c>
+      <c r="J14" t="s">
+        <v>2263</v>
+      </c>
+      <c r="K14" t="s">
+        <v>2256</v>
+      </c>
+      <c r="L14" t="s">
+        <v>2268</v>
+      </c>
+      <c r="M14" t="s">
+        <v>984</v>
+      </c>
+      <c r="N14" t="s">
+        <v>983</v>
+      </c>
+      <c r="O14" t="s">
+        <v>2265</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B15" t="s">
+        <v>2257</v>
+      </c>
+      <c r="C15" t="s">
+        <v>478</v>
+      </c>
+      <c r="D15" t="s">
+        <v>646</v>
+      </c>
+      <c r="E15">
+        <v>5</v>
+      </c>
+      <c r="F15">
+        <v>2000</v>
+      </c>
+      <c r="G15">
+        <v>33.552556543680481</v>
+      </c>
+      <c r="H15">
+        <v>0.45</v>
+      </c>
+      <c r="J15" t="s">
+        <v>2263</v>
+      </c>
+      <c r="K15" t="s">
+        <v>2257</v>
+      </c>
+      <c r="L15" t="s">
+        <v>2269</v>
+      </c>
+      <c r="M15" t="s">
+        <v>984</v>
+      </c>
+      <c r="N15" t="s">
+        <v>983</v>
+      </c>
+      <c r="O15" t="s">
+        <v>2265</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B16" t="s">
+        <v>2258</v>
+      </c>
+      <c r="C16" t="s">
+        <v>478</v>
+      </c>
+      <c r="D16" t="s">
+        <v>636</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+      <c r="F16">
+        <v>2000</v>
+      </c>
+      <c r="G16">
+        <v>96.888562917432253</v>
+      </c>
+      <c r="H16">
+        <v>0.45</v>
+      </c>
+      <c r="J16" t="s">
+        <v>2263</v>
+      </c>
+      <c r="K16" t="s">
+        <v>2258</v>
+      </c>
+      <c r="L16" t="s">
+        <v>2270</v>
+      </c>
+      <c r="M16" t="s">
+        <v>984</v>
+      </c>
+      <c r="N16" t="s">
+        <v>983</v>
+      </c>
+      <c r="O16" t="s">
+        <v>2265</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B17" t="s">
+        <v>2259</v>
+      </c>
+      <c r="C17" t="s">
+        <v>478</v>
+      </c>
+      <c r="D17" t="s">
+        <v>270</v>
+      </c>
+      <c r="E17">
+        <v>10</v>
+      </c>
+      <c r="F17">
+        <v>2000</v>
+      </c>
+      <c r="G17">
+        <v>204.35164131717946</v>
+      </c>
+      <c r="H17">
+        <v>0.45</v>
+      </c>
+      <c r="J17" t="s">
+        <v>2263</v>
+      </c>
+      <c r="K17" t="s">
+        <v>2259</v>
+      </c>
+      <c r="L17" t="s">
+        <v>2271</v>
+      </c>
+      <c r="M17" t="s">
+        <v>984</v>
+      </c>
+      <c r="N17" t="s">
+        <v>983</v>
+      </c>
+      <c r="O17" t="s">
+        <v>2265</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F243E0AD-7682-471E-A093-A3F365603EF1}">
   <dimension ref="B9:T192"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -16737,8 +17165,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8445255-07DD-4E3A-9179-9A56403A4572}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{017CE517-585E-4313-B847-FD6547CF5A1A}">
   <dimension ref="B9:T297"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -31290,8 +31718,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEAD7B7B-FFDB-44FB-A5C7-4BAB8B1F95B4}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{324C517C-470B-444F-B659-48D5865EB6F9}">
   <dimension ref="B9:T1100"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -79924,8 +80352,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FB9A0D0-7660-4CCE-BD1D-7A1D756F6932}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9989486D-9100-4058-B398-6EF418917808}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_BRA_grids/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA_grids/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0DA444DD-AA06-47A2-A80A-FC868C3EA203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D79E2EB3-8639-4CC9-8EC2-1FDE645761DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{21F222A3-29AD-4022-84E0-C36D295E60D2}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{44CFC78F-016D-4B13-9FFB-02DD9714DBC4}"/>
   </bookViews>
   <sheets>
     <sheet name="additional_hydro_pot" sheetId="5" r:id="rId1"/>
@@ -7214,7 +7214,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CBB6643-D6E5-4A5B-88B6-6EF3E079C13E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A47EAA42-2A32-424C-9E29-FCF2CC2C6391}">
   <dimension ref="B9:O17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7560,7 +7560,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4B7B838-2B03-485C-B1BD-2E2B72159BF6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{876782CE-F49F-4CD3-89C2-533975B320F4}">
   <dimension ref="B9:T192"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17154,7 +17154,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2566B728-2665-4CB5-A721-2229E90189C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6167887D-291F-410B-8A9E-06C126AA23A9}">
   <dimension ref="B9:T294"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -31580,7 +31580,7 @@
         <v>30</v>
       </c>
       <c r="L271">
-        <v>0.29794977026086789</v>
+        <v>0.29794977026086794</v>
       </c>
       <c r="N271" t="s">
         <v>981</v>
@@ -32847,7 +32847,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CDC19A5-4125-48AF-A547-0A32B24F5658}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{613CF43D-02D9-4D47-8910-6E562042FDB2}">
   <dimension ref="B9:T1104"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -78522,7 +78522,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L987">
-        <v>0.29794977026086789</v>
+        <v>0.29794977026086794</v>
       </c>
     </row>
     <row r="988" spans="2:12" x14ac:dyDescent="0.45">
@@ -78545,7 +78545,7 @@
         <v>0.33123000000000008</v>
       </c>
       <c r="L988">
-        <v>0.29794977026086789</v>
+        <v>0.29794977026086794</v>
       </c>
     </row>
     <row r="989" spans="2:12" x14ac:dyDescent="0.45">
@@ -78568,7 +78568,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L989">
-        <v>0.29794977026086789</v>
+        <v>0.29794977026086794</v>
       </c>
     </row>
     <row r="990" spans="2:12" x14ac:dyDescent="0.45">
@@ -82602,7 +82602,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91563859-CFB2-446B-B30C-A7821680045A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A2E7C4-68E5-4AC4-B99C-5D3F246B4B69}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_BRA_grids/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA_grids/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A54D02F-AED8-4753-94AA-48601BC4E305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEE4F4EF-CC49-4DFD-AF1D-DBE6FD8302CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F6BAE250-D678-4287-8A78-7BBA93A593E1}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{29C447D0-0F3D-4A95-B3B4-C3A381ED834D}"/>
   </bookViews>
   <sheets>
     <sheet name="additional_hydro_pot" sheetId="5" r:id="rId1"/>
@@ -7226,7 +7226,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C23D1703-6587-4E2D-9464-B840BCC726C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{452AA4DB-B632-4640-BCA3-435E0EE42643}">
   <dimension ref="B9:O17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7572,7 +7572,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69E2E160-D355-4A04-BEE9-9F18F4AA3AF8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1E60037-E42B-4856-A636-446A8019B8D9}">
   <dimension ref="B9:T192"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17166,7 +17166,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCB3FDBF-1A16-4B08-B42E-5792F3B7B3FE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25C60C04-E100-4BD9-9939-904B3C59F928}">
   <dimension ref="B9:T294"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -31592,7 +31592,7 @@
         <v>30</v>
       </c>
       <c r="L271">
-        <v>0.29867587392232581</v>
+        <v>0.29867587392232575</v>
       </c>
       <c r="N271" t="s">
         <v>981</v>
@@ -32859,7 +32859,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD2520A7-24FE-42BB-A386-465749933DAA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61A8F410-E01E-4C59-A93B-90534CCC2DA4}">
   <dimension ref="B9:T1106"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -33654,7 +33654,7 @@
         <v>36</v>
       </c>
       <c r="P24" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q24" t="s">
         <v>983</v>
@@ -33707,7 +33707,7 @@
         <v>36</v>
       </c>
       <c r="P25" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q25" t="s">
         <v>983</v>
@@ -43936,7 +43936,7 @@
         <v>289</v>
       </c>
       <c r="P218" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q218" t="s">
         <v>983</v>
@@ -43989,7 +43989,7 @@
         <v>289</v>
       </c>
       <c r="P219" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q219" t="s">
         <v>983</v>
@@ -44572,7 +44572,7 @@
         <v>303</v>
       </c>
       <c r="P230" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q230" t="s">
         <v>983</v>
@@ -44625,7 +44625,7 @@
         <v>303</v>
       </c>
       <c r="P231" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q231" t="s">
         <v>983</v>
@@ -63870,7 +63870,7 @@
         <v>817</v>
       </c>
       <c r="P612" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q612" t="s">
         <v>983</v>
@@ -63923,7 +63923,7 @@
         <v>817</v>
       </c>
       <c r="P613" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q613" t="s">
         <v>983</v>
@@ -63976,7 +63976,7 @@
         <v>819</v>
       </c>
       <c r="P614" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q614" t="s">
         <v>983</v>
@@ -64029,7 +64029,7 @@
         <v>819</v>
       </c>
       <c r="P615" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q615" t="s">
         <v>983</v>
@@ -64135,7 +64135,7 @@
         <v>823</v>
       </c>
       <c r="P617" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q617" t="s">
         <v>983</v>
@@ -64188,7 +64188,7 @@
         <v>823</v>
       </c>
       <c r="P618" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q618" t="s">
         <v>983</v>
@@ -64294,7 +64294,7 @@
         <v>826</v>
       </c>
       <c r="P620" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q620" t="s">
         <v>983</v>
@@ -64347,7 +64347,7 @@
         <v>826</v>
       </c>
       <c r="P621" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q621" t="s">
         <v>983</v>
@@ -64559,7 +64559,7 @@
         <v>832</v>
       </c>
       <c r="P625" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q625" t="s">
         <v>983</v>
@@ -64612,7 +64612,7 @@
         <v>832</v>
       </c>
       <c r="P626" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q626" t="s">
         <v>983</v>
@@ -64718,7 +64718,7 @@
         <v>835</v>
       </c>
       <c r="P628" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q628" t="s">
         <v>983</v>
@@ -64771,7 +64771,7 @@
         <v>835</v>
       </c>
       <c r="P629" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q629" t="s">
         <v>983</v>
@@ -65089,7 +65089,7 @@
         <v>846</v>
       </c>
       <c r="P635" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q635" t="s">
         <v>983</v>
@@ -65142,7 +65142,7 @@
         <v>846</v>
       </c>
       <c r="P636" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q636" t="s">
         <v>983</v>
@@ -65513,7 +65513,7 @@
         <v>860</v>
       </c>
       <c r="P643" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q643" t="s">
         <v>983</v>
@@ -65566,7 +65566,7 @@
         <v>860</v>
       </c>
       <c r="P644" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q644" t="s">
         <v>983</v>
@@ -68097,7 +68097,7 @@
         <v>945</v>
       </c>
       <c r="P690" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q690" t="s">
         <v>983</v>
@@ -68153,7 +68153,7 @@
         <v>945</v>
       </c>
       <c r="P691" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q691" t="s">
         <v>983</v>
@@ -68209,7 +68209,7 @@
         <v>947</v>
       </c>
       <c r="P692" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q692" t="s">
         <v>983</v>
@@ -68265,7 +68265,7 @@
         <v>947</v>
       </c>
       <c r="P693" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q693" t="s">
         <v>983</v>
@@ -68601,7 +68601,7 @@
         <v>958</v>
       </c>
       <c r="P699" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q699" t="s">
         <v>983</v>
@@ -68657,7 +68657,7 @@
         <v>958</v>
       </c>
       <c r="P700" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q700" t="s">
         <v>983</v>
@@ -78968,7 +78968,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L988">
-        <v>0.29867587392232581</v>
+        <v>0.29867587392232575</v>
       </c>
     </row>
     <row r="989" spans="2:12" x14ac:dyDescent="0.45">
@@ -78991,7 +78991,7 @@
         <v>0.33123000000000008</v>
       </c>
       <c r="L989">
-        <v>0.29867587392232581</v>
+        <v>0.29867587392232575</v>
       </c>
     </row>
     <row r="990" spans="2:12" x14ac:dyDescent="0.45">
@@ -79014,7 +79014,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L990">
-        <v>0.29867587392232581</v>
+        <v>0.29867587392232575</v>
       </c>
     </row>
     <row r="991" spans="2:12" x14ac:dyDescent="0.45">
@@ -83083,7 +83083,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E1CA731-21E5-49B8-ACF0-6FA71BD7576F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06D4D503-687C-4BE2-8C34-5D2379FE91FC}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_BRA_grids/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA_grids/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEE4F4EF-CC49-4DFD-AF1D-DBE6FD8302CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E647EC8-AD95-4864-A4D7-7DBE370CAEE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{29C447D0-0F3D-4A95-B3B4-C3A381ED834D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{810EDFF2-3956-4BAE-BEF3-2C9EF1A43AB2}"/>
   </bookViews>
   <sheets>
     <sheet name="additional_hydro_pot" sheetId="5" r:id="rId1"/>
@@ -7226,7 +7226,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{452AA4DB-B632-4640-BCA3-435E0EE42643}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B25F7FC-EF65-423D-B7C2-6FFE3A8628A0}">
   <dimension ref="B9:O17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7572,7 +7572,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1E60037-E42B-4856-A636-446A8019B8D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4687235E-CFB3-4E8D-B805-236FF83B2B9B}">
   <dimension ref="B9:T192"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17166,7 +17166,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25C60C04-E100-4BD9-9939-904B3C59F928}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AADCB25A-0167-481C-A9B6-3F59E9AB80AC}">
   <dimension ref="B9:T294"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -32859,7 +32859,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61A8F410-E01E-4C59-A93B-90534CCC2DA4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{831BF604-E769-4D0B-9A00-62E9D28312E2}">
   <dimension ref="B9:T1106"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -33654,7 +33654,7 @@
         <v>36</v>
       </c>
       <c r="P24" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q24" t="s">
         <v>983</v>
@@ -33707,7 +33707,7 @@
         <v>36</v>
       </c>
       <c r="P25" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q25" t="s">
         <v>983</v>
@@ -63870,7 +63870,7 @@
         <v>817</v>
       </c>
       <c r="P612" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q612" t="s">
         <v>983</v>
@@ -63923,7 +63923,7 @@
         <v>817</v>
       </c>
       <c r="P613" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q613" t="s">
         <v>983</v>
@@ -63976,7 +63976,7 @@
         <v>819</v>
       </c>
       <c r="P614" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q614" t="s">
         <v>983</v>
@@ -64029,7 +64029,7 @@
         <v>819</v>
       </c>
       <c r="P615" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q615" t="s">
         <v>983</v>
@@ -64135,7 +64135,7 @@
         <v>823</v>
       </c>
       <c r="P617" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q617" t="s">
         <v>983</v>
@@ -64188,7 +64188,7 @@
         <v>823</v>
       </c>
       <c r="P618" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q618" t="s">
         <v>983</v>
@@ -64294,7 +64294,7 @@
         <v>826</v>
       </c>
       <c r="P620" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q620" t="s">
         <v>983</v>
@@ -64347,7 +64347,7 @@
         <v>826</v>
       </c>
       <c r="P621" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q621" t="s">
         <v>983</v>
@@ -64559,7 +64559,7 @@
         <v>832</v>
       </c>
       <c r="P625" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q625" t="s">
         <v>983</v>
@@ -64612,7 +64612,7 @@
         <v>832</v>
       </c>
       <c r="P626" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q626" t="s">
         <v>983</v>
@@ -64718,7 +64718,7 @@
         <v>835</v>
       </c>
       <c r="P628" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q628" t="s">
         <v>983</v>
@@ -64771,7 +64771,7 @@
         <v>835</v>
       </c>
       <c r="P629" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q629" t="s">
         <v>983</v>
@@ -65089,7 +65089,7 @@
         <v>846</v>
       </c>
       <c r="P635" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q635" t="s">
         <v>983</v>
@@ -65142,7 +65142,7 @@
         <v>846</v>
       </c>
       <c r="P636" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q636" t="s">
         <v>983</v>
@@ -68209,7 +68209,7 @@
         <v>947</v>
       </c>
       <c r="P692" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q692" t="s">
         <v>983</v>
@@ -68265,7 +68265,7 @@
         <v>947</v>
       </c>
       <c r="P693" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q693" t="s">
         <v>983</v>
@@ -68601,7 +68601,7 @@
         <v>958</v>
       </c>
       <c r="P699" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q699" t="s">
         <v>983</v>
@@ -68657,7 +68657,7 @@
         <v>958</v>
       </c>
       <c r="P700" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q700" t="s">
         <v>983</v>
@@ -72522,7 +72522,7 @@
         <v>2025</v>
       </c>
       <c r="F804">
-        <v>0.57679999999999998</v>
+        <v>0.28860000000000002</v>
       </c>
       <c r="G804">
         <v>1</v>
@@ -72531,7 +72531,7 @@
         <v>1032.75</v>
       </c>
       <c r="I804">
-        <v>17.550000000000004</v>
+        <v>17.55</v>
       </c>
       <c r="J804">
         <v>0</v>
@@ -72540,7 +72540,7 @@
         <v>30</v>
       </c>
       <c r="L804">
-        <v>0.22305009092480443</v>
+        <v>0.22305009092480438</v>
       </c>
     </row>
     <row r="805" spans="2:12" x14ac:dyDescent="0.45">
@@ -72557,7 +72557,7 @@
         <v>2025</v>
       </c>
       <c r="F805">
-        <v>0.28860000000000002</v>
+        <v>0.57679999999999998</v>
       </c>
       <c r="G805">
         <v>1</v>
@@ -72566,7 +72566,7 @@
         <v>1032.75</v>
       </c>
       <c r="I805">
-        <v>17.55</v>
+        <v>17.550000000000004</v>
       </c>
       <c r="J805">
         <v>0</v>
@@ -72575,7 +72575,7 @@
         <v>30</v>
       </c>
       <c r="L805">
-        <v>0.22305009092480438</v>
+        <v>0.22305009092480443</v>
       </c>
     </row>
     <row r="806" spans="2:12" x14ac:dyDescent="0.45">
@@ -82146,19 +82146,19 @@
         <v>2025</v>
       </c>
       <c r="F1080">
-        <v>5.1299999999999998E-2</v>
+        <v>2.2800000000000001E-2</v>
       </c>
       <c r="G1080">
         <v>1</v>
       </c>
       <c r="H1080">
-        <v>1563.9999999999998</v>
+        <v>1836</v>
       </c>
       <c r="I1080">
-        <v>39.6</v>
+        <v>46.800000000000004</v>
       </c>
       <c r="J1080">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="K1080">
         <v>30</v>
@@ -82181,19 +82181,19 @@
         <v>2025</v>
       </c>
       <c r="F1081">
-        <v>2.2800000000000001E-2</v>
+        <v>5.1299999999999998E-2</v>
       </c>
       <c r="G1081">
         <v>1</v>
       </c>
       <c r="H1081">
-        <v>1836</v>
+        <v>1563.9999999999998</v>
       </c>
       <c r="I1081">
-        <v>46.800000000000004</v>
+        <v>39.6</v>
       </c>
       <c r="J1081">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="K1081">
         <v>30</v>
@@ -83083,7 +83083,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06D4D503-687C-4BE2-8C34-5D2379FE91FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E40EF915-DFED-4F22-B060-888325E31B6E}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_BRA_grids/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA_grids/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E647EC8-AD95-4864-A4D7-7DBE370CAEE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF81E39F-C95D-4526-9E04-B1467857461E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{810EDFF2-3956-4BAE-BEF3-2C9EF1A43AB2}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{EF130C4A-702E-4F37-8DCC-C9EFB4B0551A}"/>
   </bookViews>
   <sheets>
     <sheet name="additional_hydro_pot" sheetId="5" r:id="rId1"/>
@@ -7226,7 +7226,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B25F7FC-EF65-423D-B7C2-6FFE3A8628A0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72BBE5FB-6349-4DEE-8D9C-D7FB111A963E}">
   <dimension ref="B9:O17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7572,7 +7572,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4687235E-CFB3-4E8D-B805-236FF83B2B9B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18BB1243-4305-4C27-AFCA-4A9ECE5F68F6}">
   <dimension ref="B9:T192"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17166,7 +17166,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AADCB25A-0167-481C-A9B6-3F59E9AB80AC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A6D6594-A446-4F6E-9A4D-4A6BBD9F7D21}">
   <dimension ref="B9:T294"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -31592,7 +31592,7 @@
         <v>30</v>
       </c>
       <c r="L271">
-        <v>0.29867587392232575</v>
+        <v>0.29867587392232581</v>
       </c>
       <c r="N271" t="s">
         <v>981</v>
@@ -32859,7 +32859,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{831BF604-E769-4D0B-9A00-62E9D28312E2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB41889B-11B8-41EC-A194-16CF00A932B0}">
   <dimension ref="B9:T1106"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -33654,7 +33654,7 @@
         <v>36</v>
       </c>
       <c r="P24" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q24" t="s">
         <v>983</v>
@@ -33707,7 +33707,7 @@
         <v>36</v>
       </c>
       <c r="P25" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q25" t="s">
         <v>983</v>
@@ -44572,7 +44572,7 @@
         <v>303</v>
       </c>
       <c r="P230" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q230" t="s">
         <v>983</v>
@@ -44625,7 +44625,7 @@
         <v>303</v>
       </c>
       <c r="P231" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q231" t="s">
         <v>983</v>
@@ -63870,7 +63870,7 @@
         <v>817</v>
       </c>
       <c r="P612" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q612" t="s">
         <v>983</v>
@@ -63923,7 +63923,7 @@
         <v>817</v>
       </c>
       <c r="P613" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q613" t="s">
         <v>983</v>
@@ -64135,7 +64135,7 @@
         <v>823</v>
       </c>
       <c r="P617" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q617" t="s">
         <v>983</v>
@@ -64188,7 +64188,7 @@
         <v>823</v>
       </c>
       <c r="P618" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q618" t="s">
         <v>983</v>
@@ -64294,7 +64294,7 @@
         <v>826</v>
       </c>
       <c r="P620" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q620" t="s">
         <v>983</v>
@@ -64347,7 +64347,7 @@
         <v>826</v>
       </c>
       <c r="P621" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q621" t="s">
         <v>983</v>
@@ -64400,7 +64400,7 @@
         <v>828</v>
       </c>
       <c r="P622" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q622" t="s">
         <v>983</v>
@@ -64453,7 +64453,7 @@
         <v>828</v>
       </c>
       <c r="P623" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q623" t="s">
         <v>983</v>
@@ -64559,7 +64559,7 @@
         <v>832</v>
       </c>
       <c r="P625" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q625" t="s">
         <v>983</v>
@@ -64612,7 +64612,7 @@
         <v>832</v>
       </c>
       <c r="P626" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q626" t="s">
         <v>983</v>
@@ -67929,7 +67929,7 @@
         <v>942</v>
       </c>
       <c r="P687" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q687" t="s">
         <v>983</v>
@@ -67985,7 +67985,7 @@
         <v>942</v>
       </c>
       <c r="P688" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q688" t="s">
         <v>983</v>
@@ -72522,7 +72522,7 @@
         <v>2025</v>
       </c>
       <c r="F804">
-        <v>0.28860000000000002</v>
+        <v>0.57679999999999998</v>
       </c>
       <c r="G804">
         <v>1</v>
@@ -72531,7 +72531,7 @@
         <v>1032.75</v>
       </c>
       <c r="I804">
-        <v>17.55</v>
+        <v>17.550000000000004</v>
       </c>
       <c r="J804">
         <v>0</v>
@@ -72540,7 +72540,7 @@
         <v>30</v>
       </c>
       <c r="L804">
-        <v>0.22305009092480438</v>
+        <v>0.22305009092480443</v>
       </c>
     </row>
     <row r="805" spans="2:12" x14ac:dyDescent="0.45">
@@ -72557,7 +72557,7 @@
         <v>2025</v>
       </c>
       <c r="F805">
-        <v>0.57679999999999998</v>
+        <v>0.28860000000000002</v>
       </c>
       <c r="G805">
         <v>1</v>
@@ -72566,7 +72566,7 @@
         <v>1032.75</v>
       </c>
       <c r="I805">
-        <v>17.550000000000004</v>
+        <v>17.55</v>
       </c>
       <c r="J805">
         <v>0</v>
@@ -72575,7 +72575,7 @@
         <v>30</v>
       </c>
       <c r="L805">
-        <v>0.22305009092480443</v>
+        <v>0.22305009092480438</v>
       </c>
     </row>
     <row r="806" spans="2:12" x14ac:dyDescent="0.45">
@@ -78968,7 +78968,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L988">
-        <v>0.29867587392232575</v>
+        <v>0.29867587392232581</v>
       </c>
     </row>
     <row r="989" spans="2:12" x14ac:dyDescent="0.45">
@@ -78991,7 +78991,7 @@
         <v>0.33123000000000008</v>
       </c>
       <c r="L989">
-        <v>0.29867587392232575</v>
+        <v>0.29867587392232581</v>
       </c>
     </row>
     <row r="990" spans="2:12" x14ac:dyDescent="0.45">
@@ -79014,7 +79014,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L990">
-        <v>0.29867587392232575</v>
+        <v>0.29867587392232581</v>
       </c>
     </row>
     <row r="991" spans="2:12" x14ac:dyDescent="0.45">
@@ -83083,7 +83083,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E40EF915-DFED-4F22-B060-888325E31B6E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EEC4F64-354D-4D69-9AD6-D3FDC5F21391}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_BRA_grids/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA_grids/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF81E39F-C95D-4526-9E04-B1467857461E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{384771A3-750B-495D-9C38-FE648B3043F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{EF130C4A-702E-4F37-8DCC-C9EFB4B0551A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{272B96CA-723B-40F5-8A3C-E79239499543}"/>
   </bookViews>
   <sheets>
     <sheet name="additional_hydro_pot" sheetId="5" r:id="rId1"/>
@@ -7226,7 +7226,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72BBE5FB-6349-4DEE-8D9C-D7FB111A963E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CEB4AEA-14AB-49EA-897B-02A42A9C2746}">
   <dimension ref="B9:O17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7572,7 +7572,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18BB1243-4305-4C27-AFCA-4A9ECE5F68F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B7682EC-EBB4-4B74-8CE1-B389D272B9FE}">
   <dimension ref="B9:T192"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17166,7 +17166,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A6D6594-A446-4F6E-9A4D-4A6BBD9F7D21}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1D41610-ED92-4B9C-A13B-9A0625CF53C9}">
   <dimension ref="B9:T294"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -31592,7 +31592,7 @@
         <v>30</v>
       </c>
       <c r="L271">
-        <v>0.29867587392232581</v>
+        <v>0.29867587392232586</v>
       </c>
       <c r="N271" t="s">
         <v>981</v>
@@ -32859,7 +32859,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB41889B-11B8-41EC-A194-16CF00A932B0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC499A46-1642-48A9-BA9D-8634228F0CBA}">
   <dimension ref="B9:T1106"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -33654,7 +33654,7 @@
         <v>36</v>
       </c>
       <c r="P24" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q24" t="s">
         <v>983</v>
@@ -33707,7 +33707,7 @@
         <v>36</v>
       </c>
       <c r="P25" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q25" t="s">
         <v>983</v>
@@ -34078,7 +34078,7 @@
         <v>47</v>
       </c>
       <c r="P32" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q32" t="s">
         <v>983</v>
@@ -34131,7 +34131,7 @@
         <v>47</v>
       </c>
       <c r="P33" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q33" t="s">
         <v>983</v>
@@ -43936,7 +43936,7 @@
         <v>289</v>
       </c>
       <c r="P218" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q218" t="s">
         <v>983</v>
@@ -43989,7 +43989,7 @@
         <v>289</v>
       </c>
       <c r="P219" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q219" t="s">
         <v>983</v>
@@ -44572,7 +44572,7 @@
         <v>303</v>
       </c>
       <c r="P230" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q230" t="s">
         <v>983</v>
@@ -44625,7 +44625,7 @@
         <v>303</v>
       </c>
       <c r="P231" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q231" t="s">
         <v>983</v>
@@ -63976,7 +63976,7 @@
         <v>819</v>
       </c>
       <c r="P614" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q614" t="s">
         <v>983</v>
@@ -64029,7 +64029,7 @@
         <v>819</v>
       </c>
       <c r="P615" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q615" t="s">
         <v>983</v>
@@ -64135,7 +64135,7 @@
         <v>823</v>
       </c>
       <c r="P617" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q617" t="s">
         <v>983</v>
@@ -64188,7 +64188,7 @@
         <v>823</v>
       </c>
       <c r="P618" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q618" t="s">
         <v>983</v>
@@ -64294,7 +64294,7 @@
         <v>826</v>
       </c>
       <c r="P620" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q620" t="s">
         <v>983</v>
@@ -64347,7 +64347,7 @@
         <v>826</v>
       </c>
       <c r="P621" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q621" t="s">
         <v>983</v>
@@ -64400,7 +64400,7 @@
         <v>828</v>
       </c>
       <c r="P622" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q622" t="s">
         <v>983</v>
@@ -64453,7 +64453,7 @@
         <v>828</v>
       </c>
       <c r="P623" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q623" t="s">
         <v>983</v>
@@ -64559,7 +64559,7 @@
         <v>832</v>
       </c>
       <c r="P625" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q625" t="s">
         <v>983</v>
@@ -64612,7 +64612,7 @@
         <v>832</v>
       </c>
       <c r="P626" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q626" t="s">
         <v>983</v>
@@ -64718,7 +64718,7 @@
         <v>835</v>
       </c>
       <c r="P628" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q628" t="s">
         <v>983</v>
@@ -64771,7 +64771,7 @@
         <v>835</v>
       </c>
       <c r="P629" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q629" t="s">
         <v>983</v>
@@ -65089,7 +65089,7 @@
         <v>846</v>
       </c>
       <c r="P635" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q635" t="s">
         <v>983</v>
@@ -65142,7 +65142,7 @@
         <v>846</v>
       </c>
       <c r="P636" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q636" t="s">
         <v>983</v>
@@ -65513,7 +65513,7 @@
         <v>860</v>
       </c>
       <c r="P643" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q643" t="s">
         <v>983</v>
@@ -65566,7 +65566,7 @@
         <v>860</v>
       </c>
       <c r="P644" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q644" t="s">
         <v>983</v>
@@ -67929,7 +67929,7 @@
         <v>942</v>
       </c>
       <c r="P687" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q687" t="s">
         <v>983</v>
@@ -67985,7 +67985,7 @@
         <v>942</v>
       </c>
       <c r="P688" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q688" t="s">
         <v>983</v>
@@ -68097,7 +68097,7 @@
         <v>945</v>
       </c>
       <c r="P690" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q690" t="s">
         <v>983</v>
@@ -68153,7 +68153,7 @@
         <v>945</v>
       </c>
       <c r="P691" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q691" t="s">
         <v>983</v>
@@ -68209,7 +68209,7 @@
         <v>947</v>
       </c>
       <c r="P692" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q692" t="s">
         <v>983</v>
@@ -68265,7 +68265,7 @@
         <v>947</v>
       </c>
       <c r="P693" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q693" t="s">
         <v>983</v>
@@ -68601,7 +68601,7 @@
         <v>958</v>
       </c>
       <c r="P699" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q699" t="s">
         <v>983</v>
@@ -68657,7 +68657,7 @@
         <v>958</v>
       </c>
       <c r="P700" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q700" t="s">
         <v>983</v>
@@ -78968,7 +78968,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L988">
-        <v>0.29867587392232581</v>
+        <v>0.29867587392232586</v>
       </c>
     </row>
     <row r="989" spans="2:12" x14ac:dyDescent="0.45">
@@ -78991,7 +78991,7 @@
         <v>0.33123000000000008</v>
       </c>
       <c r="L989">
-        <v>0.29867587392232581</v>
+        <v>0.29867587392232586</v>
       </c>
     </row>
     <row r="990" spans="2:12" x14ac:dyDescent="0.45">
@@ -79014,7 +79014,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L990">
-        <v>0.29867587392232581</v>
+        <v>0.29867587392232586</v>
       </c>
     </row>
     <row r="991" spans="2:12" x14ac:dyDescent="0.45">
@@ -83083,7 +83083,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EEC4F64-354D-4D69-9AD6-D3FDC5F21391}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80367680-66D2-427C-9505-46D5C3C886DB}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_BRA_grids/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA_grids/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{384771A3-750B-495D-9C38-FE648B3043F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D2E7BA2-46CC-4082-A1CB-8EC323383A66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{272B96CA-723B-40F5-8A3C-E79239499543}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4F41E43D-DDC1-41A4-B56B-D7C3221D923C}"/>
   </bookViews>
   <sheets>
     <sheet name="additional_hydro_pot" sheetId="5" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12937" uniqueCount="2272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13170" uniqueCount="2308">
   <si>
     <t>~fi_t</t>
   </si>
@@ -6327,6 +6327,102 @@
     <t>ep_oil_steam_turbine_G100001000289_ccs-rf</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Geramar III power station_A -- announced</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Laranjeiras power station_1 -- announced</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Governador Marcelo Deda power station_1 -- announced</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Geramar III power station_C -- announced</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Geramar III power station_B -- announced</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Rio Matapi II power station_1 -- announced</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Jandaia power station_1 -- announced</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Rio Negro power station_1 -- announced</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Porto de Sergipe power station_V -- announced</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Porto de Sergipe power station_IV -- announced</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Porto de Sergipe power station_III -- announced</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Carnaúba power station_1 -- announced</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Caçapava power station_1 -- announced</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Jorge Lacerda power station_Gas unit -- announced</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Pedras Altas power station_Unit 1 -- pre-construction</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Pedras Altas power station_Unit 2 -- pre-construction</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Tupã power station_1 -- pre-construction</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Presidente Kennedy power station_II -- pre-construction</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Nossa Senhora de Fatima power station_2 -- pre-construction</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Nossa Senhora de Fatima power station_1 -- pre-construction</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Nossa Senhora de Fatima power station_3 -- pre-construction</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Norte Fluminense 2 power station_1 -- pre-construction</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Norte Catarinense power station_1 -- pre-construction</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Litos power station_1 -- pre-construction</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Litos power station_4 -- pre-construction</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Litos power station_3 -- pre-construction</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Litos power station_2 -- pre-construction</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Jaci power station_1 -- pre-construction</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Gaslub power station_1 -- pre-construction</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Gaslub power station_2 -- pre-construction</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Vale Azul power station_II -- pre-construction</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Vale Azul power station_III -- pre-construction</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - BR63-500_Missing Coal Capacity -- operating</t>
   </si>
   <si>
@@ -6816,10 +6912,19 @@
     <t>EN_Hydro_TelesPresUpB</t>
   </si>
   <si>
-    <t>EN_Hydro_Uruguational</t>
-  </si>
-  <si>
-    <t>EN_Hydro_SmallHio50MW</t>
+    <t>EN_Hydro_SmallHtfolio</t>
+  </si>
+  <si>
+    <t>EN_Hydro_MadeiraUpB</t>
+  </si>
+  <si>
+    <t>e_w284868411-230</t>
+  </si>
+  <si>
+    <t>EN_Hydro_AtlantrestRs</t>
+  </si>
+  <si>
+    <t>e_BR669-500</t>
   </si>
   <si>
     <t>Sets</t>
@@ -6852,10 +6957,13 @@
     <t>Major hydropower development on Teles Pires. High development priority. Approved for future development</t>
   </si>
   <si>
-    <t>Medium-scale hydropower facility on Uruguay. High development priority. Approved for future development</t>
-  </si>
-  <si>
     <t>Large-scale hydropower project on Various. High development priority. Approved for future development</t>
+  </si>
+  <si>
+    <t>Major hydropower development on Madeira. High development priority. Approved for future development</t>
+  </si>
+  <si>
+    <t>Major hydropower development on Various SE Brazil. High development priority. Approved for future development</t>
   </si>
 </sst>
 </file>
@@ -7226,8 +7334,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CEB4AEA-14AB-49EA-897B-02A42A9C2746}">
-  <dimension ref="B9:O17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9A6ADD7-0C79-4449-A419-C24AF617D585}">
+  <dimension ref="B9:O18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="9" spans="2:15" x14ac:dyDescent="0.45">
@@ -7243,25 +7351,25 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>2245</v>
+        <v>2277</v>
       </c>
       <c r="D10" t="s">
-        <v>2246</v>
+        <v>2278</v>
       </c>
       <c r="E10" t="s">
-        <v>2247</v>
+        <v>2279</v>
       </c>
       <c r="F10" t="s">
-        <v>2248</v>
+        <v>2280</v>
       </c>
       <c r="G10" t="s">
-        <v>2249</v>
+        <v>2281</v>
       </c>
       <c r="H10" t="s">
-        <v>2250</v>
+        <v>2282</v>
       </c>
       <c r="J10" t="s">
-        <v>2260</v>
+        <v>2295</v>
       </c>
       <c r="K10" t="s">
         <v>1</v>
@@ -7270,10 +7378,10 @@
         <v>976</v>
       </c>
       <c r="M10" t="s">
-        <v>2261</v>
+        <v>2296</v>
       </c>
       <c r="N10" t="s">
-        <v>2262</v>
+        <v>2297</v>
       </c>
       <c r="O10" t="s">
         <v>979</v>
@@ -7281,7 +7389,7 @@
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>2251</v>
+        <v>2283</v>
       </c>
       <c r="C11" t="s">
         <v>478</v>
@@ -7302,13 +7410,13 @@
         <v>0.45</v>
       </c>
       <c r="J11" t="s">
-        <v>2263</v>
+        <v>2298</v>
       </c>
       <c r="K11" t="s">
-        <v>2251</v>
+        <v>2283</v>
       </c>
       <c r="L11" t="s">
-        <v>2264</v>
+        <v>2299</v>
       </c>
       <c r="M11" t="s">
         <v>984</v>
@@ -7317,18 +7425,18 @@
         <v>983</v>
       </c>
       <c r="O11" t="s">
-        <v>2265</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>2252</v>
+        <v>2284</v>
       </c>
       <c r="C12" t="s">
         <v>478</v>
       </c>
       <c r="D12" t="s">
-        <v>2253</v>
+        <v>2285</v>
       </c>
       <c r="E12">
         <v>8</v>
@@ -7343,13 +7451,13 @@
         <v>0.45</v>
       </c>
       <c r="J12" t="s">
-        <v>2263</v>
+        <v>2298</v>
       </c>
       <c r="K12" t="s">
-        <v>2252</v>
+        <v>2284</v>
       </c>
       <c r="L12" t="s">
-        <v>2266</v>
+        <v>2301</v>
       </c>
       <c r="M12" t="s">
         <v>984</v>
@@ -7358,18 +7466,18 @@
         <v>983</v>
       </c>
       <c r="O12" t="s">
-        <v>2265</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>2254</v>
+        <v>2286</v>
       </c>
       <c r="C13" t="s">
         <v>478</v>
       </c>
       <c r="D13" t="s">
-        <v>2255</v>
+        <v>2287</v>
       </c>
       <c r="E13">
         <v>4</v>
@@ -7384,13 +7492,13 @@
         <v>0.45</v>
       </c>
       <c r="J13" t="s">
-        <v>2263</v>
+        <v>2298</v>
       </c>
       <c r="K13" t="s">
-        <v>2254</v>
+        <v>2286</v>
       </c>
       <c r="L13" t="s">
-        <v>2267</v>
+        <v>2302</v>
       </c>
       <c r="M13" t="s">
         <v>984</v>
@@ -7399,12 +7507,12 @@
         <v>983</v>
       </c>
       <c r="O13" t="s">
-        <v>2265</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>2256</v>
+        <v>2288</v>
       </c>
       <c r="C14" t="s">
         <v>478</v>
@@ -7425,13 +7533,13 @@
         <v>0.45</v>
       </c>
       <c r="J14" t="s">
-        <v>2263</v>
+        <v>2298</v>
       </c>
       <c r="K14" t="s">
-        <v>2256</v>
+        <v>2288</v>
       </c>
       <c r="L14" t="s">
-        <v>2268</v>
+        <v>2303</v>
       </c>
       <c r="M14" t="s">
         <v>984</v>
@@ -7440,12 +7548,12 @@
         <v>983</v>
       </c>
       <c r="O14" t="s">
-        <v>2265</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>2257</v>
+        <v>2289</v>
       </c>
       <c r="C15" t="s">
         <v>478</v>
@@ -7466,13 +7574,13 @@
         <v>0.45</v>
       </c>
       <c r="J15" t="s">
-        <v>2263</v>
+        <v>2298</v>
       </c>
       <c r="K15" t="s">
-        <v>2257</v>
+        <v>2289</v>
       </c>
       <c r="L15" t="s">
-        <v>2269</v>
+        <v>2304</v>
       </c>
       <c r="M15" t="s">
         <v>984</v>
@@ -7481,39 +7589,39 @@
         <v>983</v>
       </c>
       <c r="O15" t="s">
-        <v>2265</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>2258</v>
+        <v>2290</v>
       </c>
       <c r="C16" t="s">
         <v>478</v>
       </c>
       <c r="D16" t="s">
-        <v>636</v>
+        <v>270</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F16">
         <v>2000</v>
       </c>
       <c r="G16">
-        <v>96.888562917432253</v>
+        <v>204.35164131717946</v>
       </c>
       <c r="H16">
         <v>0.45</v>
       </c>
       <c r="J16" t="s">
-        <v>2263</v>
+        <v>2298</v>
       </c>
       <c r="K16" t="s">
-        <v>2258</v>
+        <v>2290</v>
       </c>
       <c r="L16" t="s">
-        <v>2270</v>
+        <v>2305</v>
       </c>
       <c r="M16" t="s">
         <v>984</v>
@@ -7522,39 +7630,39 @@
         <v>983</v>
       </c>
       <c r="O16" t="s">
-        <v>2265</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>2259</v>
+        <v>2291</v>
       </c>
       <c r="C17" t="s">
         <v>478</v>
       </c>
       <c r="D17" t="s">
-        <v>270</v>
+        <v>2292</v>
       </c>
       <c r="E17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F17">
         <v>2000</v>
       </c>
       <c r="G17">
-        <v>204.35164131717946</v>
+        <v>98.491290621647906</v>
       </c>
       <c r="H17">
         <v>0.45</v>
       </c>
       <c r="J17" t="s">
-        <v>2263</v>
+        <v>2298</v>
       </c>
       <c r="K17" t="s">
-        <v>2259</v>
+        <v>2291</v>
       </c>
       <c r="L17" t="s">
-        <v>2271</v>
+        <v>2306</v>
       </c>
       <c r="M17" t="s">
         <v>984</v>
@@ -7563,7 +7671,48 @@
         <v>983</v>
       </c>
       <c r="O17" t="s">
-        <v>2265</v>
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B18" t="s">
+        <v>2293</v>
+      </c>
+      <c r="C18" t="s">
+        <v>478</v>
+      </c>
+      <c r="D18" t="s">
+        <v>2294</v>
+      </c>
+      <c r="E18">
+        <v>8</v>
+      </c>
+      <c r="F18">
+        <v>2000</v>
+      </c>
+      <c r="G18">
+        <v>77.239249024601733</v>
+      </c>
+      <c r="H18">
+        <v>0.45</v>
+      </c>
+      <c r="J18" t="s">
+        <v>2298</v>
+      </c>
+      <c r="K18" t="s">
+        <v>2293</v>
+      </c>
+      <c r="L18" t="s">
+        <v>2307</v>
+      </c>
+      <c r="M18" t="s">
+        <v>984</v>
+      </c>
+      <c r="N18" t="s">
+        <v>983</v>
+      </c>
+      <c r="O18" t="s">
+        <v>2300</v>
       </c>
     </row>
   </sheetData>
@@ -7572,7 +7721,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B7682EC-EBB4-4B74-8CE1-B389D272B9FE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA7E3FC1-6B0F-406A-97BA-1717C611EEC2}">
   <dimension ref="B9:T192"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7678,7 +7827,7 @@
         <v>981</v>
       </c>
       <c r="O11" t="s">
-        <v>1945</v>
+        <v>1913</v>
       </c>
       <c r="P11" t="s">
         <v>2095</v>
@@ -7734,7 +7883,7 @@
         <v>981</v>
       </c>
       <c r="O12" t="s">
-        <v>1946</v>
+        <v>1914</v>
       </c>
       <c r="P12" t="s">
         <v>2096</v>
@@ -7790,7 +7939,7 @@
         <v>981</v>
       </c>
       <c r="O13" t="s">
-        <v>1947</v>
+        <v>1915</v>
       </c>
       <c r="P13" t="s">
         <v>2097</v>
@@ -7846,7 +7995,7 @@
         <v>981</v>
       </c>
       <c r="O14" t="s">
-        <v>1948</v>
+        <v>1916</v>
       </c>
       <c r="P14" t="s">
         <v>2098</v>
@@ -7902,7 +8051,7 @@
         <v>981</v>
       </c>
       <c r="O15" t="s">
-        <v>1949</v>
+        <v>1917</v>
       </c>
       <c r="P15" t="s">
         <v>2099</v>
@@ -7958,7 +8107,7 @@
         <v>981</v>
       </c>
       <c r="O16" t="s">
-        <v>1950</v>
+        <v>1918</v>
       </c>
       <c r="P16" t="s">
         <v>2100</v>
@@ -8014,7 +8163,7 @@
         <v>981</v>
       </c>
       <c r="O17" t="s">
-        <v>1951</v>
+        <v>1919</v>
       </c>
       <c r="P17" t="s">
         <v>2101</v>
@@ -8070,7 +8219,7 @@
         <v>981</v>
       </c>
       <c r="O18" t="s">
-        <v>1952</v>
+        <v>1920</v>
       </c>
       <c r="P18" t="s">
         <v>2102</v>
@@ -8126,7 +8275,7 @@
         <v>981</v>
       </c>
       <c r="O19" t="s">
-        <v>1953</v>
+        <v>1921</v>
       </c>
       <c r="P19" t="s">
         <v>2103</v>
@@ -8182,7 +8331,7 @@
         <v>981</v>
       </c>
       <c r="O20" t="s">
-        <v>1954</v>
+        <v>1922</v>
       </c>
       <c r="P20" t="s">
         <v>2104</v>
@@ -8238,7 +8387,7 @@
         <v>981</v>
       </c>
       <c r="O21" t="s">
-        <v>1955</v>
+        <v>1923</v>
       </c>
       <c r="P21" t="s">
         <v>2105</v>
@@ -8294,7 +8443,7 @@
         <v>981</v>
       </c>
       <c r="O22" t="s">
-        <v>1956</v>
+        <v>1924</v>
       </c>
       <c r="P22" t="s">
         <v>2106</v>
@@ -8350,7 +8499,7 @@
         <v>981</v>
       </c>
       <c r="O23" t="s">
-        <v>1957</v>
+        <v>1925</v>
       </c>
       <c r="P23" t="s">
         <v>2107</v>
@@ -8406,7 +8555,7 @@
         <v>981</v>
       </c>
       <c r="O24" t="s">
-        <v>1958</v>
+        <v>1926</v>
       </c>
       <c r="P24" t="s">
         <v>2108</v>
@@ -8462,7 +8611,7 @@
         <v>981</v>
       </c>
       <c r="O25" t="s">
-        <v>1959</v>
+        <v>1927</v>
       </c>
       <c r="P25" t="s">
         <v>2109</v>
@@ -8518,7 +8667,7 @@
         <v>981</v>
       </c>
       <c r="O26" t="s">
-        <v>1960</v>
+        <v>1928</v>
       </c>
       <c r="P26" t="s">
         <v>2110</v>
@@ -8574,7 +8723,7 @@
         <v>981</v>
       </c>
       <c r="O27" t="s">
-        <v>1961</v>
+        <v>1929</v>
       </c>
       <c r="P27" t="s">
         <v>2111</v>
@@ -8630,7 +8779,7 @@
         <v>981</v>
       </c>
       <c r="O28" t="s">
-        <v>1962</v>
+        <v>1930</v>
       </c>
       <c r="P28" t="s">
         <v>2112</v>
@@ -8686,7 +8835,7 @@
         <v>981</v>
       </c>
       <c r="O29" t="s">
-        <v>1963</v>
+        <v>1931</v>
       </c>
       <c r="P29" t="s">
         <v>2113</v>
@@ -8742,7 +8891,7 @@
         <v>981</v>
       </c>
       <c r="O30" t="s">
-        <v>1964</v>
+        <v>1932</v>
       </c>
       <c r="P30" t="s">
         <v>2114</v>
@@ -8798,7 +8947,7 @@
         <v>981</v>
       </c>
       <c r="O31" t="s">
-        <v>1965</v>
+        <v>1933</v>
       </c>
       <c r="P31" t="s">
         <v>2115</v>
@@ -8854,7 +9003,7 @@
         <v>981</v>
       </c>
       <c r="O32" t="s">
-        <v>1966</v>
+        <v>1934</v>
       </c>
       <c r="P32" t="s">
         <v>2116</v>
@@ -8910,7 +9059,7 @@
         <v>981</v>
       </c>
       <c r="O33" t="s">
-        <v>1967</v>
+        <v>1935</v>
       </c>
       <c r="P33" t="s">
         <v>2117</v>
@@ -8966,7 +9115,7 @@
         <v>981</v>
       </c>
       <c r="O34" t="s">
-        <v>1968</v>
+        <v>1936</v>
       </c>
       <c r="P34" t="s">
         <v>2118</v>
@@ -9022,7 +9171,7 @@
         <v>981</v>
       </c>
       <c r="O35" t="s">
-        <v>1969</v>
+        <v>1937</v>
       </c>
       <c r="P35" t="s">
         <v>2119</v>
@@ -9078,7 +9227,7 @@
         <v>981</v>
       </c>
       <c r="O36" t="s">
-        <v>1970</v>
+        <v>1938</v>
       </c>
       <c r="P36" t="s">
         <v>2120</v>
@@ -9134,7 +9283,7 @@
         <v>981</v>
       </c>
       <c r="O37" t="s">
-        <v>1971</v>
+        <v>1939</v>
       </c>
       <c r="P37" t="s">
         <v>2121</v>
@@ -9190,7 +9339,7 @@
         <v>981</v>
       </c>
       <c r="O38" t="s">
-        <v>1972</v>
+        <v>1940</v>
       </c>
       <c r="P38" t="s">
         <v>2122</v>
@@ -9246,7 +9395,7 @@
         <v>981</v>
       </c>
       <c r="O39" t="s">
-        <v>1973</v>
+        <v>1941</v>
       </c>
       <c r="P39" t="s">
         <v>2123</v>
@@ -9302,7 +9451,7 @@
         <v>981</v>
       </c>
       <c r="O40" t="s">
-        <v>1974</v>
+        <v>1942</v>
       </c>
       <c r="P40" t="s">
         <v>2124</v>
@@ -9358,7 +9507,7 @@
         <v>981</v>
       </c>
       <c r="O41" t="s">
-        <v>1975</v>
+        <v>1943</v>
       </c>
       <c r="P41" t="s">
         <v>2125</v>
@@ -9414,7 +9563,7 @@
         <v>981</v>
       </c>
       <c r="O42" t="s">
-        <v>1976</v>
+        <v>1944</v>
       </c>
       <c r="P42" t="s">
         <v>2126</v>
@@ -9470,7 +9619,7 @@
         <v>981</v>
       </c>
       <c r="O43" t="s">
-        <v>1977</v>
+        <v>1945</v>
       </c>
       <c r="P43" t="s">
         <v>2127</v>
@@ -9526,7 +9675,7 @@
         <v>981</v>
       </c>
       <c r="O44" t="s">
-        <v>1978</v>
+        <v>1946</v>
       </c>
       <c r="P44" t="s">
         <v>2128</v>
@@ -9582,7 +9731,7 @@
         <v>981</v>
       </c>
       <c r="O45" t="s">
-        <v>1979</v>
+        <v>1947</v>
       </c>
       <c r="P45" t="s">
         <v>2129</v>
@@ -9638,7 +9787,7 @@
         <v>981</v>
       </c>
       <c r="O46" t="s">
-        <v>1980</v>
+        <v>1948</v>
       </c>
       <c r="P46" t="s">
         <v>2130</v>
@@ -9694,7 +9843,7 @@
         <v>981</v>
       </c>
       <c r="O47" t="s">
-        <v>1981</v>
+        <v>1949</v>
       </c>
       <c r="P47" t="s">
         <v>2131</v>
@@ -9750,7 +9899,7 @@
         <v>981</v>
       </c>
       <c r="O48" t="s">
-        <v>1982</v>
+        <v>1950</v>
       </c>
       <c r="P48" t="s">
         <v>2132</v>
@@ -9806,7 +9955,7 @@
         <v>981</v>
       </c>
       <c r="O49" t="s">
-        <v>1983</v>
+        <v>1951</v>
       </c>
       <c r="P49" t="s">
         <v>2133</v>
@@ -9862,7 +10011,7 @@
         <v>981</v>
       </c>
       <c r="O50" t="s">
-        <v>1984</v>
+        <v>1952</v>
       </c>
       <c r="P50" t="s">
         <v>2134</v>
@@ -9918,7 +10067,7 @@
         <v>981</v>
       </c>
       <c r="O51" t="s">
-        <v>1985</v>
+        <v>1953</v>
       </c>
       <c r="P51" t="s">
         <v>2135</v>
@@ -9974,7 +10123,7 @@
         <v>981</v>
       </c>
       <c r="O52" t="s">
-        <v>1986</v>
+        <v>1954</v>
       </c>
       <c r="P52" t="s">
         <v>2136</v>
@@ -10030,7 +10179,7 @@
         <v>981</v>
       </c>
       <c r="O53" t="s">
-        <v>1987</v>
+        <v>1955</v>
       </c>
       <c r="P53" t="s">
         <v>2137</v>
@@ -10086,7 +10235,7 @@
         <v>981</v>
       </c>
       <c r="O54" t="s">
-        <v>1988</v>
+        <v>1956</v>
       </c>
       <c r="P54" t="s">
         <v>2138</v>
@@ -10142,7 +10291,7 @@
         <v>981</v>
       </c>
       <c r="O55" t="s">
-        <v>1989</v>
+        <v>1957</v>
       </c>
       <c r="P55" t="s">
         <v>2139</v>
@@ -10198,7 +10347,7 @@
         <v>981</v>
       </c>
       <c r="O56" t="s">
-        <v>1990</v>
+        <v>1958</v>
       </c>
       <c r="P56" t="s">
         <v>2140</v>
@@ -10254,7 +10403,7 @@
         <v>981</v>
       </c>
       <c r="O57" t="s">
-        <v>1991</v>
+        <v>1959</v>
       </c>
       <c r="P57" t="s">
         <v>2141</v>
@@ -10310,7 +10459,7 @@
         <v>981</v>
       </c>
       <c r="O58" t="s">
-        <v>1992</v>
+        <v>1960</v>
       </c>
       <c r="P58" t="s">
         <v>2142</v>
@@ -10366,7 +10515,7 @@
         <v>981</v>
       </c>
       <c r="O59" t="s">
-        <v>1993</v>
+        <v>1961</v>
       </c>
       <c r="P59" t="s">
         <v>2143</v>
@@ -10422,7 +10571,7 @@
         <v>981</v>
       </c>
       <c r="O60" t="s">
-        <v>1994</v>
+        <v>1962</v>
       </c>
       <c r="P60" t="s">
         <v>2144</v>
@@ -10478,7 +10627,7 @@
         <v>981</v>
       </c>
       <c r="O61" t="s">
-        <v>1995</v>
+        <v>1963</v>
       </c>
       <c r="P61" t="s">
         <v>2145</v>
@@ -10534,7 +10683,7 @@
         <v>981</v>
       </c>
       <c r="O62" t="s">
-        <v>1996</v>
+        <v>1964</v>
       </c>
       <c r="P62" t="s">
         <v>2146</v>
@@ -10590,7 +10739,7 @@
         <v>981</v>
       </c>
       <c r="O63" t="s">
-        <v>1997</v>
+        <v>1965</v>
       </c>
       <c r="P63" t="s">
         <v>2147</v>
@@ -10646,7 +10795,7 @@
         <v>981</v>
       </c>
       <c r="O64" t="s">
-        <v>1998</v>
+        <v>1966</v>
       </c>
       <c r="P64" t="s">
         <v>2148</v>
@@ -10702,7 +10851,7 @@
         <v>981</v>
       </c>
       <c r="O65" t="s">
-        <v>1999</v>
+        <v>1967</v>
       </c>
       <c r="P65" t="s">
         <v>2149</v>
@@ -10758,7 +10907,7 @@
         <v>981</v>
       </c>
       <c r="O66" t="s">
-        <v>2000</v>
+        <v>1968</v>
       </c>
       <c r="P66" t="s">
         <v>2150</v>
@@ -10814,7 +10963,7 @@
         <v>981</v>
       </c>
       <c r="O67" t="s">
-        <v>2001</v>
+        <v>1969</v>
       </c>
       <c r="P67" t="s">
         <v>2151</v>
@@ -10870,7 +11019,7 @@
         <v>981</v>
       </c>
       <c r="O68" t="s">
-        <v>2002</v>
+        <v>1970</v>
       </c>
       <c r="P68" t="s">
         <v>2152</v>
@@ -10926,7 +11075,7 @@
         <v>981</v>
       </c>
       <c r="O69" t="s">
-        <v>2003</v>
+        <v>1971</v>
       </c>
       <c r="P69" t="s">
         <v>2153</v>
@@ -10982,7 +11131,7 @@
         <v>981</v>
       </c>
       <c r="O70" t="s">
-        <v>2004</v>
+        <v>1972</v>
       </c>
       <c r="P70" t="s">
         <v>2154</v>
@@ -11038,7 +11187,7 @@
         <v>981</v>
       </c>
       <c r="O71" t="s">
-        <v>2005</v>
+        <v>1973</v>
       </c>
       <c r="P71" t="s">
         <v>2155</v>
@@ -11094,7 +11243,7 @@
         <v>981</v>
       </c>
       <c r="O72" t="s">
-        <v>2006</v>
+        <v>1974</v>
       </c>
       <c r="P72" t="s">
         <v>2156</v>
@@ -11150,7 +11299,7 @@
         <v>981</v>
       </c>
       <c r="O73" t="s">
-        <v>2007</v>
+        <v>1975</v>
       </c>
       <c r="P73" t="s">
         <v>2157</v>
@@ -11206,7 +11355,7 @@
         <v>981</v>
       </c>
       <c r="O74" t="s">
-        <v>2008</v>
+        <v>1976</v>
       </c>
       <c r="P74" t="s">
         <v>2158</v>
@@ -11262,7 +11411,7 @@
         <v>981</v>
       </c>
       <c r="O75" t="s">
-        <v>2009</v>
+        <v>1977</v>
       </c>
       <c r="P75" t="s">
         <v>2159</v>
@@ -11318,7 +11467,7 @@
         <v>981</v>
       </c>
       <c r="O76" t="s">
-        <v>2010</v>
+        <v>1978</v>
       </c>
       <c r="P76" t="s">
         <v>2160</v>
@@ -11374,7 +11523,7 @@
         <v>981</v>
       </c>
       <c r="O77" t="s">
-        <v>2011</v>
+        <v>1979</v>
       </c>
       <c r="P77" t="s">
         <v>2161</v>
@@ -11430,7 +11579,7 @@
         <v>981</v>
       </c>
       <c r="O78" t="s">
-        <v>2012</v>
+        <v>1980</v>
       </c>
       <c r="P78" t="s">
         <v>2162</v>
@@ -11486,7 +11635,7 @@
         <v>981</v>
       </c>
       <c r="O79" t="s">
-        <v>2013</v>
+        <v>1981</v>
       </c>
       <c r="P79" t="s">
         <v>2163</v>
@@ -11542,7 +11691,7 @@
         <v>981</v>
       </c>
       <c r="O80" t="s">
-        <v>2014</v>
+        <v>1982</v>
       </c>
       <c r="P80" t="s">
         <v>2164</v>
@@ -11598,7 +11747,7 @@
         <v>981</v>
       </c>
       <c r="O81" t="s">
-        <v>2015</v>
+        <v>1983</v>
       </c>
       <c r="P81" t="s">
         <v>2165</v>
@@ -11654,7 +11803,7 @@
         <v>981</v>
       </c>
       <c r="O82" t="s">
-        <v>2016</v>
+        <v>1984</v>
       </c>
       <c r="P82" t="s">
         <v>2166</v>
@@ -11710,7 +11859,7 @@
         <v>981</v>
       </c>
       <c r="O83" t="s">
-        <v>2017</v>
+        <v>1985</v>
       </c>
       <c r="P83" t="s">
         <v>2167</v>
@@ -11766,7 +11915,7 @@
         <v>981</v>
       </c>
       <c r="O84" t="s">
-        <v>2018</v>
+        <v>1986</v>
       </c>
       <c r="P84" t="s">
         <v>2168</v>
@@ -11822,7 +11971,7 @@
         <v>981</v>
       </c>
       <c r="O85" t="s">
-        <v>2019</v>
+        <v>1987</v>
       </c>
       <c r="P85" t="s">
         <v>2169</v>
@@ -11878,7 +12027,7 @@
         <v>981</v>
       </c>
       <c r="O86" t="s">
-        <v>2020</v>
+        <v>1988</v>
       </c>
       <c r="P86" t="s">
         <v>2170</v>
@@ -11934,7 +12083,7 @@
         <v>981</v>
       </c>
       <c r="O87" t="s">
-        <v>2021</v>
+        <v>1989</v>
       </c>
       <c r="P87" t="s">
         <v>2171</v>
@@ -11990,7 +12139,7 @@
         <v>981</v>
       </c>
       <c r="O88" t="s">
-        <v>2022</v>
+        <v>1990</v>
       </c>
       <c r="P88" t="s">
         <v>2172</v>
@@ -12046,7 +12195,7 @@
         <v>981</v>
       </c>
       <c r="O89" t="s">
-        <v>2023</v>
+        <v>1991</v>
       </c>
       <c r="P89" t="s">
         <v>2173</v>
@@ -12102,7 +12251,7 @@
         <v>981</v>
       </c>
       <c r="O90" t="s">
-        <v>2024</v>
+        <v>1992</v>
       </c>
       <c r="P90" t="s">
         <v>2174</v>
@@ -12158,7 +12307,7 @@
         <v>981</v>
       </c>
       <c r="O91" t="s">
-        <v>2025</v>
+        <v>1993</v>
       </c>
       <c r="P91" t="s">
         <v>2175</v>
@@ -12214,7 +12363,7 @@
         <v>981</v>
       </c>
       <c r="O92" t="s">
-        <v>2026</v>
+        <v>1994</v>
       </c>
       <c r="P92" t="s">
         <v>2176</v>
@@ -12270,7 +12419,7 @@
         <v>981</v>
       </c>
       <c r="O93" t="s">
-        <v>2027</v>
+        <v>1995</v>
       </c>
       <c r="P93" t="s">
         <v>2177</v>
@@ -12326,7 +12475,7 @@
         <v>981</v>
       </c>
       <c r="O94" t="s">
-        <v>2028</v>
+        <v>1996</v>
       </c>
       <c r="P94" t="s">
         <v>2178</v>
@@ -12382,7 +12531,7 @@
         <v>981</v>
       </c>
       <c r="O95" t="s">
-        <v>2029</v>
+        <v>1997</v>
       </c>
       <c r="P95" t="s">
         <v>2179</v>
@@ -12438,7 +12587,7 @@
         <v>981</v>
       </c>
       <c r="O96" t="s">
-        <v>2030</v>
+        <v>1998</v>
       </c>
       <c r="P96" t="s">
         <v>2180</v>
@@ -12494,7 +12643,7 @@
         <v>981</v>
       </c>
       <c r="O97" t="s">
-        <v>2031</v>
+        <v>1999</v>
       </c>
       <c r="P97" t="s">
         <v>2181</v>
@@ -12550,7 +12699,7 @@
         <v>981</v>
       </c>
       <c r="O98" t="s">
-        <v>2032</v>
+        <v>2000</v>
       </c>
       <c r="P98" t="s">
         <v>2182</v>
@@ -12606,7 +12755,7 @@
         <v>981</v>
       </c>
       <c r="O99" t="s">
-        <v>2033</v>
+        <v>2001</v>
       </c>
       <c r="P99" t="s">
         <v>2183</v>
@@ -12662,7 +12811,7 @@
         <v>981</v>
       </c>
       <c r="O100" t="s">
-        <v>2034</v>
+        <v>2002</v>
       </c>
       <c r="P100" t="s">
         <v>2184</v>
@@ -12718,7 +12867,7 @@
         <v>981</v>
       </c>
       <c r="O101" t="s">
-        <v>2035</v>
+        <v>2003</v>
       </c>
       <c r="P101" t="s">
         <v>2185</v>
@@ -12774,7 +12923,7 @@
         <v>981</v>
       </c>
       <c r="O102" t="s">
-        <v>2036</v>
+        <v>2004</v>
       </c>
       <c r="P102" t="s">
         <v>2186</v>
@@ -12830,7 +12979,7 @@
         <v>981</v>
       </c>
       <c r="O103" t="s">
-        <v>2037</v>
+        <v>2005</v>
       </c>
       <c r="P103" t="s">
         <v>2187</v>
@@ -12886,7 +13035,7 @@
         <v>981</v>
       </c>
       <c r="O104" t="s">
-        <v>2038</v>
+        <v>2006</v>
       </c>
       <c r="P104" t="s">
         <v>2188</v>
@@ -12942,7 +13091,7 @@
         <v>981</v>
       </c>
       <c r="O105" t="s">
-        <v>2039</v>
+        <v>2007</v>
       </c>
       <c r="P105" t="s">
         <v>2189</v>
@@ -12998,7 +13147,7 @@
         <v>981</v>
       </c>
       <c r="O106" t="s">
-        <v>2040</v>
+        <v>2008</v>
       </c>
       <c r="P106" t="s">
         <v>2190</v>
@@ -13054,7 +13203,7 @@
         <v>981</v>
       </c>
       <c r="O107" t="s">
-        <v>2041</v>
+        <v>2009</v>
       </c>
       <c r="P107" t="s">
         <v>2191</v>
@@ -13110,7 +13259,7 @@
         <v>981</v>
       </c>
       <c r="O108" t="s">
-        <v>2042</v>
+        <v>2010</v>
       </c>
       <c r="P108" t="s">
         <v>2192</v>
@@ -13166,7 +13315,7 @@
         <v>981</v>
       </c>
       <c r="O109" t="s">
-        <v>2043</v>
+        <v>2011</v>
       </c>
       <c r="P109" t="s">
         <v>2193</v>
@@ -13222,7 +13371,7 @@
         <v>981</v>
       </c>
       <c r="O110" t="s">
-        <v>2044</v>
+        <v>2012</v>
       </c>
       <c r="P110" t="s">
         <v>2194</v>
@@ -13278,7 +13427,7 @@
         <v>981</v>
       </c>
       <c r="O111" t="s">
-        <v>2045</v>
+        <v>2013</v>
       </c>
       <c r="P111" t="s">
         <v>2195</v>
@@ -13334,7 +13483,7 @@
         <v>981</v>
       </c>
       <c r="O112" t="s">
-        <v>2046</v>
+        <v>2014</v>
       </c>
       <c r="P112" t="s">
         <v>2196</v>
@@ -13390,7 +13539,7 @@
         <v>981</v>
       </c>
       <c r="O113" t="s">
-        <v>2047</v>
+        <v>2015</v>
       </c>
       <c r="P113" t="s">
         <v>2197</v>
@@ -13446,7 +13595,7 @@
         <v>981</v>
       </c>
       <c r="O114" t="s">
-        <v>2048</v>
+        <v>2016</v>
       </c>
       <c r="P114" t="s">
         <v>2198</v>
@@ -13502,7 +13651,7 @@
         <v>981</v>
       </c>
       <c r="O115" t="s">
-        <v>2049</v>
+        <v>2017</v>
       </c>
       <c r="P115" t="s">
         <v>2199</v>
@@ -13558,7 +13707,7 @@
         <v>981</v>
       </c>
       <c r="O116" t="s">
-        <v>2050</v>
+        <v>2018</v>
       </c>
       <c r="P116" t="s">
         <v>2200</v>
@@ -13614,7 +13763,7 @@
         <v>981</v>
       </c>
       <c r="O117" t="s">
-        <v>2051</v>
+        <v>2019</v>
       </c>
       <c r="P117" t="s">
         <v>2201</v>
@@ -13670,7 +13819,7 @@
         <v>981</v>
       </c>
       <c r="O118" t="s">
-        <v>2052</v>
+        <v>2020</v>
       </c>
       <c r="P118" t="s">
         <v>2202</v>
@@ -13726,7 +13875,7 @@
         <v>981</v>
       </c>
       <c r="O119" t="s">
-        <v>2053</v>
+        <v>2021</v>
       </c>
       <c r="P119" t="s">
         <v>2203</v>
@@ -13782,7 +13931,7 @@
         <v>981</v>
       </c>
       <c r="O120" t="s">
-        <v>2054</v>
+        <v>2022</v>
       </c>
       <c r="P120" t="s">
         <v>2204</v>
@@ -13838,7 +13987,7 @@
         <v>981</v>
       </c>
       <c r="O121" t="s">
-        <v>2055</v>
+        <v>2023</v>
       </c>
       <c r="P121" t="s">
         <v>2205</v>
@@ -13894,7 +14043,7 @@
         <v>981</v>
       </c>
       <c r="O122" t="s">
-        <v>2056</v>
+        <v>2024</v>
       </c>
       <c r="P122" t="s">
         <v>2206</v>
@@ -13950,7 +14099,7 @@
         <v>981</v>
       </c>
       <c r="O123" t="s">
-        <v>2057</v>
+        <v>2025</v>
       </c>
       <c r="P123" t="s">
         <v>2207</v>
@@ -14006,7 +14155,7 @@
         <v>981</v>
       </c>
       <c r="O124" t="s">
-        <v>2058</v>
+        <v>2026</v>
       </c>
       <c r="P124" t="s">
         <v>2208</v>
@@ -14062,7 +14211,7 @@
         <v>981</v>
       </c>
       <c r="O125" t="s">
-        <v>2059</v>
+        <v>2027</v>
       </c>
       <c r="P125" t="s">
         <v>2209</v>
@@ -14118,7 +14267,7 @@
         <v>981</v>
       </c>
       <c r="O126" t="s">
-        <v>2060</v>
+        <v>2028</v>
       </c>
       <c r="P126" t="s">
         <v>2210</v>
@@ -14174,7 +14323,7 @@
         <v>981</v>
       </c>
       <c r="O127" t="s">
-        <v>2061</v>
+        <v>2029</v>
       </c>
       <c r="P127" t="s">
         <v>2211</v>
@@ -14230,7 +14379,7 @@
         <v>981</v>
       </c>
       <c r="O128" t="s">
-        <v>2062</v>
+        <v>2030</v>
       </c>
       <c r="P128" t="s">
         <v>2212</v>
@@ -14286,7 +14435,7 @@
         <v>981</v>
       </c>
       <c r="O129" t="s">
-        <v>2063</v>
+        <v>2031</v>
       </c>
       <c r="P129" t="s">
         <v>2213</v>
@@ -14342,7 +14491,7 @@
         <v>981</v>
       </c>
       <c r="O130" t="s">
-        <v>2064</v>
+        <v>2032</v>
       </c>
       <c r="P130" t="s">
         <v>2214</v>
@@ -14398,7 +14547,7 @@
         <v>981</v>
       </c>
       <c r="O131" t="s">
-        <v>2065</v>
+        <v>2033</v>
       </c>
       <c r="P131" t="s">
         <v>2215</v>
@@ -14454,7 +14603,7 @@
         <v>981</v>
       </c>
       <c r="O132" t="s">
-        <v>2066</v>
+        <v>2034</v>
       </c>
       <c r="P132" t="s">
         <v>2216</v>
@@ -14510,7 +14659,7 @@
         <v>981</v>
       </c>
       <c r="O133" t="s">
-        <v>2067</v>
+        <v>2035</v>
       </c>
       <c r="P133" t="s">
         <v>2217</v>
@@ -14566,7 +14715,7 @@
         <v>981</v>
       </c>
       <c r="O134" t="s">
-        <v>2068</v>
+        <v>2036</v>
       </c>
       <c r="P134" t="s">
         <v>2218</v>
@@ -14622,7 +14771,7 @@
         <v>981</v>
       </c>
       <c r="O135" t="s">
-        <v>2069</v>
+        <v>2037</v>
       </c>
       <c r="P135" t="s">
         <v>2219</v>
@@ -14678,7 +14827,7 @@
         <v>981</v>
       </c>
       <c r="O136" t="s">
-        <v>2070</v>
+        <v>2038</v>
       </c>
       <c r="P136" t="s">
         <v>2220</v>
@@ -14734,7 +14883,7 @@
         <v>981</v>
       </c>
       <c r="O137" t="s">
-        <v>2071</v>
+        <v>2039</v>
       </c>
       <c r="P137" t="s">
         <v>2221</v>
@@ -14790,7 +14939,7 @@
         <v>981</v>
       </c>
       <c r="O138" t="s">
-        <v>2072</v>
+        <v>2040</v>
       </c>
       <c r="P138" t="s">
         <v>2222</v>
@@ -14846,7 +14995,7 @@
         <v>981</v>
       </c>
       <c r="O139" t="s">
-        <v>2073</v>
+        <v>2041</v>
       </c>
       <c r="P139" t="s">
         <v>2223</v>
@@ -14902,7 +15051,7 @@
         <v>981</v>
       </c>
       <c r="O140" t="s">
-        <v>2074</v>
+        <v>2042</v>
       </c>
       <c r="P140" t="s">
         <v>2224</v>
@@ -14958,7 +15107,7 @@
         <v>981</v>
       </c>
       <c r="O141" t="s">
-        <v>2075</v>
+        <v>2043</v>
       </c>
       <c r="P141" t="s">
         <v>2225</v>
@@ -15014,7 +15163,7 @@
         <v>981</v>
       </c>
       <c r="O142" t="s">
-        <v>2076</v>
+        <v>2044</v>
       </c>
       <c r="P142" t="s">
         <v>2226</v>
@@ -15070,7 +15219,7 @@
         <v>981</v>
       </c>
       <c r="O143" t="s">
-        <v>2077</v>
+        <v>2045</v>
       </c>
       <c r="P143" t="s">
         <v>2227</v>
@@ -15126,7 +15275,7 @@
         <v>981</v>
       </c>
       <c r="O144" t="s">
-        <v>2078</v>
+        <v>2046</v>
       </c>
       <c r="P144" t="s">
         <v>2228</v>
@@ -15182,7 +15331,7 @@
         <v>981</v>
       </c>
       <c r="O145" t="s">
-        <v>2079</v>
+        <v>2047</v>
       </c>
       <c r="P145" t="s">
         <v>2229</v>
@@ -15238,7 +15387,7 @@
         <v>981</v>
       </c>
       <c r="O146" t="s">
-        <v>2080</v>
+        <v>2048</v>
       </c>
       <c r="P146" t="s">
         <v>2230</v>
@@ -15294,7 +15443,7 @@
         <v>981</v>
       </c>
       <c r="O147" t="s">
-        <v>2081</v>
+        <v>2049</v>
       </c>
       <c r="P147" t="s">
         <v>2231</v>
@@ -15350,7 +15499,7 @@
         <v>981</v>
       </c>
       <c r="O148" t="s">
-        <v>2082</v>
+        <v>2050</v>
       </c>
       <c r="P148" t="s">
         <v>2232</v>
@@ -15406,7 +15555,7 @@
         <v>981</v>
       </c>
       <c r="O149" t="s">
-        <v>2083</v>
+        <v>2051</v>
       </c>
       <c r="P149" t="s">
         <v>2233</v>
@@ -15462,7 +15611,7 @@
         <v>981</v>
       </c>
       <c r="O150" t="s">
-        <v>2084</v>
+        <v>2052</v>
       </c>
       <c r="P150" t="s">
         <v>2234</v>
@@ -15518,7 +15667,7 @@
         <v>981</v>
       </c>
       <c r="O151" t="s">
-        <v>2085</v>
+        <v>2053</v>
       </c>
       <c r="P151" t="s">
         <v>2235</v>
@@ -15574,7 +15723,7 @@
         <v>981</v>
       </c>
       <c r="O152" t="s">
-        <v>2086</v>
+        <v>2054</v>
       </c>
       <c r="P152" t="s">
         <v>2236</v>
@@ -15630,7 +15779,7 @@
         <v>981</v>
       </c>
       <c r="O153" t="s">
-        <v>2087</v>
+        <v>2055</v>
       </c>
       <c r="P153" t="s">
         <v>2237</v>
@@ -15686,7 +15835,7 @@
         <v>981</v>
       </c>
       <c r="O154" t="s">
-        <v>2088</v>
+        <v>2056</v>
       </c>
       <c r="P154" t="s">
         <v>2238</v>
@@ -15742,7 +15891,7 @@
         <v>981</v>
       </c>
       <c r="O155" t="s">
-        <v>2089</v>
+        <v>2057</v>
       </c>
       <c r="P155" t="s">
         <v>2239</v>
@@ -15798,7 +15947,7 @@
         <v>981</v>
       </c>
       <c r="O156" t="s">
-        <v>2090</v>
+        <v>2058</v>
       </c>
       <c r="P156" t="s">
         <v>2240</v>
@@ -15854,7 +16003,7 @@
         <v>981</v>
       </c>
       <c r="O157" t="s">
-        <v>2091</v>
+        <v>2059</v>
       </c>
       <c r="P157" t="s">
         <v>2241</v>
@@ -15910,7 +16059,7 @@
         <v>981</v>
       </c>
       <c r="O158" t="s">
-        <v>2092</v>
+        <v>2060</v>
       </c>
       <c r="P158" t="s">
         <v>2242</v>
@@ -15966,7 +16115,7 @@
         <v>981</v>
       </c>
       <c r="O159" t="s">
-        <v>2093</v>
+        <v>2061</v>
       </c>
       <c r="P159" t="s">
         <v>2243</v>
@@ -16022,7 +16171,7 @@
         <v>981</v>
       </c>
       <c r="O160" t="s">
-        <v>2094</v>
+        <v>2062</v>
       </c>
       <c r="P160" t="s">
         <v>2244</v>
@@ -16040,7 +16189,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="161" spans="2:12" x14ac:dyDescent="0.45">
+    <row r="161" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B161" t="s">
         <v>2063</v>
       </c>
@@ -16074,8 +16223,29 @@
       <c r="L161">
         <v>20</v>
       </c>
-    </row>
-    <row r="162" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="N161" t="s">
+        <v>981</v>
+      </c>
+      <c r="O161" t="s">
+        <v>2063</v>
+      </c>
+      <c r="P161" t="s">
+        <v>2245</v>
+      </c>
+      <c r="Q161" t="s">
+        <v>983</v>
+      </c>
+      <c r="R161" t="s">
+        <v>984</v>
+      </c>
+      <c r="S161" t="s">
+        <v>985</v>
+      </c>
+      <c r="T161" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="162" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B162" t="s">
         <v>2064</v>
       </c>
@@ -16109,8 +16279,29 @@
       <c r="L162">
         <v>20</v>
       </c>
-    </row>
-    <row r="163" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="N162" t="s">
+        <v>981</v>
+      </c>
+      <c r="O162" t="s">
+        <v>2064</v>
+      </c>
+      <c r="P162" t="s">
+        <v>2246</v>
+      </c>
+      <c r="Q162" t="s">
+        <v>983</v>
+      </c>
+      <c r="R162" t="s">
+        <v>984</v>
+      </c>
+      <c r="S162" t="s">
+        <v>985</v>
+      </c>
+      <c r="T162" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="163" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B163" t="s">
         <v>2065</v>
       </c>
@@ -16144,8 +16335,29 @@
       <c r="L163">
         <v>20</v>
       </c>
-    </row>
-    <row r="164" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="N163" t="s">
+        <v>981</v>
+      </c>
+      <c r="O163" t="s">
+        <v>2065</v>
+      </c>
+      <c r="P163" t="s">
+        <v>2247</v>
+      </c>
+      <c r="Q163" t="s">
+        <v>983</v>
+      </c>
+      <c r="R163" t="s">
+        <v>984</v>
+      </c>
+      <c r="S163" t="s">
+        <v>985</v>
+      </c>
+      <c r="T163" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="164" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B164" t="s">
         <v>2066</v>
       </c>
@@ -16179,8 +16391,29 @@
       <c r="L164">
         <v>20</v>
       </c>
-    </row>
-    <row r="165" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="N164" t="s">
+        <v>981</v>
+      </c>
+      <c r="O164" t="s">
+        <v>2066</v>
+      </c>
+      <c r="P164" t="s">
+        <v>2248</v>
+      </c>
+      <c r="Q164" t="s">
+        <v>983</v>
+      </c>
+      <c r="R164" t="s">
+        <v>984</v>
+      </c>
+      <c r="S164" t="s">
+        <v>985</v>
+      </c>
+      <c r="T164" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="165" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B165" t="s">
         <v>2067</v>
       </c>
@@ -16214,8 +16447,29 @@
       <c r="L165">
         <v>20</v>
       </c>
-    </row>
-    <row r="166" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="N165" t="s">
+        <v>981</v>
+      </c>
+      <c r="O165" t="s">
+        <v>2067</v>
+      </c>
+      <c r="P165" t="s">
+        <v>2249</v>
+      </c>
+      <c r="Q165" t="s">
+        <v>983</v>
+      </c>
+      <c r="R165" t="s">
+        <v>984</v>
+      </c>
+      <c r="S165" t="s">
+        <v>985</v>
+      </c>
+      <c r="T165" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="166" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B166" t="s">
         <v>2068</v>
       </c>
@@ -16249,8 +16503,29 @@
       <c r="L166">
         <v>20</v>
       </c>
-    </row>
-    <row r="167" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="N166" t="s">
+        <v>981</v>
+      </c>
+      <c r="O166" t="s">
+        <v>2068</v>
+      </c>
+      <c r="P166" t="s">
+        <v>2250</v>
+      </c>
+      <c r="Q166" t="s">
+        <v>983</v>
+      </c>
+      <c r="R166" t="s">
+        <v>984</v>
+      </c>
+      <c r="S166" t="s">
+        <v>985</v>
+      </c>
+      <c r="T166" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="167" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B167" t="s">
         <v>2069</v>
       </c>
@@ -16284,8 +16559,29 @@
       <c r="L167">
         <v>20</v>
       </c>
-    </row>
-    <row r="168" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="N167" t="s">
+        <v>981</v>
+      </c>
+      <c r="O167" t="s">
+        <v>2069</v>
+      </c>
+      <c r="P167" t="s">
+        <v>2251</v>
+      </c>
+      <c r="Q167" t="s">
+        <v>983</v>
+      </c>
+      <c r="R167" t="s">
+        <v>984</v>
+      </c>
+      <c r="S167" t="s">
+        <v>985</v>
+      </c>
+      <c r="T167" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="168" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B168" t="s">
         <v>2070</v>
       </c>
@@ -16319,8 +16615,29 @@
       <c r="L168">
         <v>20</v>
       </c>
-    </row>
-    <row r="169" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="N168" t="s">
+        <v>981</v>
+      </c>
+      <c r="O168" t="s">
+        <v>2070</v>
+      </c>
+      <c r="P168" t="s">
+        <v>2252</v>
+      </c>
+      <c r="Q168" t="s">
+        <v>983</v>
+      </c>
+      <c r="R168" t="s">
+        <v>984</v>
+      </c>
+      <c r="S168" t="s">
+        <v>985</v>
+      </c>
+      <c r="T168" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="169" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B169" t="s">
         <v>2071</v>
       </c>
@@ -16354,8 +16671,29 @@
       <c r="L169">
         <v>20</v>
       </c>
-    </row>
-    <row r="170" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="N169" t="s">
+        <v>981</v>
+      </c>
+      <c r="O169" t="s">
+        <v>2071</v>
+      </c>
+      <c r="P169" t="s">
+        <v>2253</v>
+      </c>
+      <c r="Q169" t="s">
+        <v>983</v>
+      </c>
+      <c r="R169" t="s">
+        <v>984</v>
+      </c>
+      <c r="S169" t="s">
+        <v>985</v>
+      </c>
+      <c r="T169" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="170" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B170" t="s">
         <v>2072</v>
       </c>
@@ -16389,8 +16727,29 @@
       <c r="L170">
         <v>20</v>
       </c>
-    </row>
-    <row r="171" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="N170" t="s">
+        <v>981</v>
+      </c>
+      <c r="O170" t="s">
+        <v>2072</v>
+      </c>
+      <c r="P170" t="s">
+        <v>2254</v>
+      </c>
+      <c r="Q170" t="s">
+        <v>983</v>
+      </c>
+      <c r="R170" t="s">
+        <v>984</v>
+      </c>
+      <c r="S170" t="s">
+        <v>985</v>
+      </c>
+      <c r="T170" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="171" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B171" t="s">
         <v>2073</v>
       </c>
@@ -16424,8 +16783,29 @@
       <c r="L171">
         <v>20</v>
       </c>
-    </row>
-    <row r="172" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="N171" t="s">
+        <v>981</v>
+      </c>
+      <c r="O171" t="s">
+        <v>2073</v>
+      </c>
+      <c r="P171" t="s">
+        <v>2255</v>
+      </c>
+      <c r="Q171" t="s">
+        <v>983</v>
+      </c>
+      <c r="R171" t="s">
+        <v>984</v>
+      </c>
+      <c r="S171" t="s">
+        <v>985</v>
+      </c>
+      <c r="T171" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="172" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B172" t="s">
         <v>2074</v>
       </c>
@@ -16459,8 +16839,29 @@
       <c r="L172">
         <v>20</v>
       </c>
-    </row>
-    <row r="173" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="N172" t="s">
+        <v>981</v>
+      </c>
+      <c r="O172" t="s">
+        <v>2074</v>
+      </c>
+      <c r="P172" t="s">
+        <v>2256</v>
+      </c>
+      <c r="Q172" t="s">
+        <v>983</v>
+      </c>
+      <c r="R172" t="s">
+        <v>984</v>
+      </c>
+      <c r="S172" t="s">
+        <v>985</v>
+      </c>
+      <c r="T172" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="173" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B173" t="s">
         <v>2075</v>
       </c>
@@ -16494,8 +16895,29 @@
       <c r="L173">
         <v>20</v>
       </c>
-    </row>
-    <row r="174" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="N173" t="s">
+        <v>981</v>
+      </c>
+      <c r="O173" t="s">
+        <v>2075</v>
+      </c>
+      <c r="P173" t="s">
+        <v>2257</v>
+      </c>
+      <c r="Q173" t="s">
+        <v>983</v>
+      </c>
+      <c r="R173" t="s">
+        <v>984</v>
+      </c>
+      <c r="S173" t="s">
+        <v>985</v>
+      </c>
+      <c r="T173" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="174" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B174" t="s">
         <v>2076</v>
       </c>
@@ -16529,8 +16951,29 @@
       <c r="L174">
         <v>20</v>
       </c>
-    </row>
-    <row r="175" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="N174" t="s">
+        <v>981</v>
+      </c>
+      <c r="O174" t="s">
+        <v>2076</v>
+      </c>
+      <c r="P174" t="s">
+        <v>2258</v>
+      </c>
+      <c r="Q174" t="s">
+        <v>983</v>
+      </c>
+      <c r="R174" t="s">
+        <v>984</v>
+      </c>
+      <c r="S174" t="s">
+        <v>985</v>
+      </c>
+      <c r="T174" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="175" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B175" t="s">
         <v>2077</v>
       </c>
@@ -16564,8 +17007,29 @@
       <c r="L175">
         <v>20</v>
       </c>
-    </row>
-    <row r="176" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="N175" t="s">
+        <v>981</v>
+      </c>
+      <c r="O175" t="s">
+        <v>2077</v>
+      </c>
+      <c r="P175" t="s">
+        <v>2259</v>
+      </c>
+      <c r="Q175" t="s">
+        <v>983</v>
+      </c>
+      <c r="R175" t="s">
+        <v>984</v>
+      </c>
+      <c r="S175" t="s">
+        <v>985</v>
+      </c>
+      <c r="T175" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="176" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B176" t="s">
         <v>2078</v>
       </c>
@@ -16599,8 +17063,29 @@
       <c r="L176">
         <v>20</v>
       </c>
-    </row>
-    <row r="177" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="N176" t="s">
+        <v>981</v>
+      </c>
+      <c r="O176" t="s">
+        <v>2078</v>
+      </c>
+      <c r="P176" t="s">
+        <v>2260</v>
+      </c>
+      <c r="Q176" t="s">
+        <v>983</v>
+      </c>
+      <c r="R176" t="s">
+        <v>984</v>
+      </c>
+      <c r="S176" t="s">
+        <v>985</v>
+      </c>
+      <c r="T176" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="177" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B177" t="s">
         <v>2079</v>
       </c>
@@ -16634,8 +17119,29 @@
       <c r="L177">
         <v>20</v>
       </c>
-    </row>
-    <row r="178" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="N177" t="s">
+        <v>981</v>
+      </c>
+      <c r="O177" t="s">
+        <v>2079</v>
+      </c>
+      <c r="P177" t="s">
+        <v>2261</v>
+      </c>
+      <c r="Q177" t="s">
+        <v>983</v>
+      </c>
+      <c r="R177" t="s">
+        <v>984</v>
+      </c>
+      <c r="S177" t="s">
+        <v>985</v>
+      </c>
+      <c r="T177" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="178" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B178" t="s">
         <v>2080</v>
       </c>
@@ -16669,8 +17175,29 @@
       <c r="L178">
         <v>20</v>
       </c>
-    </row>
-    <row r="179" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="N178" t="s">
+        <v>981</v>
+      </c>
+      <c r="O178" t="s">
+        <v>2080</v>
+      </c>
+      <c r="P178" t="s">
+        <v>2262</v>
+      </c>
+      <c r="Q178" t="s">
+        <v>983</v>
+      </c>
+      <c r="R178" t="s">
+        <v>984</v>
+      </c>
+      <c r="S178" t="s">
+        <v>985</v>
+      </c>
+      <c r="T178" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="179" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B179" t="s">
         <v>2081</v>
       </c>
@@ -16704,8 +17231,29 @@
       <c r="L179">
         <v>20</v>
       </c>
-    </row>
-    <row r="180" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="N179" t="s">
+        <v>981</v>
+      </c>
+      <c r="O179" t="s">
+        <v>2081</v>
+      </c>
+      <c r="P179" t="s">
+        <v>2263</v>
+      </c>
+      <c r="Q179" t="s">
+        <v>983</v>
+      </c>
+      <c r="R179" t="s">
+        <v>984</v>
+      </c>
+      <c r="S179" t="s">
+        <v>985</v>
+      </c>
+      <c r="T179" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="180" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B180" t="s">
         <v>2082</v>
       </c>
@@ -16739,8 +17287,29 @@
       <c r="L180">
         <v>20</v>
       </c>
-    </row>
-    <row r="181" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="N180" t="s">
+        <v>981</v>
+      </c>
+      <c r="O180" t="s">
+        <v>2082</v>
+      </c>
+      <c r="P180" t="s">
+        <v>2264</v>
+      </c>
+      <c r="Q180" t="s">
+        <v>983</v>
+      </c>
+      <c r="R180" t="s">
+        <v>984</v>
+      </c>
+      <c r="S180" t="s">
+        <v>985</v>
+      </c>
+      <c r="T180" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="181" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B181" t="s">
         <v>2083</v>
       </c>
@@ -16774,8 +17343,29 @@
       <c r="L181">
         <v>20</v>
       </c>
-    </row>
-    <row r="182" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="N181" t="s">
+        <v>981</v>
+      </c>
+      <c r="O181" t="s">
+        <v>2083</v>
+      </c>
+      <c r="P181" t="s">
+        <v>2265</v>
+      </c>
+      <c r="Q181" t="s">
+        <v>983</v>
+      </c>
+      <c r="R181" t="s">
+        <v>984</v>
+      </c>
+      <c r="S181" t="s">
+        <v>985</v>
+      </c>
+      <c r="T181" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="182" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B182" t="s">
         <v>2084</v>
       </c>
@@ -16809,8 +17399,29 @@
       <c r="L182">
         <v>20</v>
       </c>
-    </row>
-    <row r="183" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="N182" t="s">
+        <v>981</v>
+      </c>
+      <c r="O182" t="s">
+        <v>2084</v>
+      </c>
+      <c r="P182" t="s">
+        <v>2266</v>
+      </c>
+      <c r="Q182" t="s">
+        <v>983</v>
+      </c>
+      <c r="R182" t="s">
+        <v>984</v>
+      </c>
+      <c r="S182" t="s">
+        <v>985</v>
+      </c>
+      <c r="T182" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="183" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B183" t="s">
         <v>2085</v>
       </c>
@@ -16844,8 +17455,29 @@
       <c r="L183">
         <v>20</v>
       </c>
-    </row>
-    <row r="184" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="N183" t="s">
+        <v>981</v>
+      </c>
+      <c r="O183" t="s">
+        <v>2085</v>
+      </c>
+      <c r="P183" t="s">
+        <v>2267</v>
+      </c>
+      <c r="Q183" t="s">
+        <v>983</v>
+      </c>
+      <c r="R183" t="s">
+        <v>984</v>
+      </c>
+      <c r="S183" t="s">
+        <v>985</v>
+      </c>
+      <c r="T183" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="184" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B184" t="s">
         <v>2086</v>
       </c>
@@ -16879,8 +17511,29 @@
       <c r="L184">
         <v>20</v>
       </c>
-    </row>
-    <row r="185" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="N184" t="s">
+        <v>981</v>
+      </c>
+      <c r="O184" t="s">
+        <v>2086</v>
+      </c>
+      <c r="P184" t="s">
+        <v>2268</v>
+      </c>
+      <c r="Q184" t="s">
+        <v>983</v>
+      </c>
+      <c r="R184" t="s">
+        <v>984</v>
+      </c>
+      <c r="S184" t="s">
+        <v>985</v>
+      </c>
+      <c r="T184" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="185" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B185" t="s">
         <v>2087</v>
       </c>
@@ -16914,8 +17567,29 @@
       <c r="L185">
         <v>20</v>
       </c>
-    </row>
-    <row r="186" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="N185" t="s">
+        <v>981</v>
+      </c>
+      <c r="O185" t="s">
+        <v>2087</v>
+      </c>
+      <c r="P185" t="s">
+        <v>2269</v>
+      </c>
+      <c r="Q185" t="s">
+        <v>983</v>
+      </c>
+      <c r="R185" t="s">
+        <v>984</v>
+      </c>
+      <c r="S185" t="s">
+        <v>985</v>
+      </c>
+      <c r="T185" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="186" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B186" t="s">
         <v>2088</v>
       </c>
@@ -16949,8 +17623,29 @@
       <c r="L186">
         <v>20</v>
       </c>
-    </row>
-    <row r="187" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="N186" t="s">
+        <v>981</v>
+      </c>
+      <c r="O186" t="s">
+        <v>2088</v>
+      </c>
+      <c r="P186" t="s">
+        <v>2270</v>
+      </c>
+      <c r="Q186" t="s">
+        <v>983</v>
+      </c>
+      <c r="R186" t="s">
+        <v>984</v>
+      </c>
+      <c r="S186" t="s">
+        <v>985</v>
+      </c>
+      <c r="T186" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="187" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B187" t="s">
         <v>2089</v>
       </c>
@@ -16984,8 +17679,29 @@
       <c r="L187">
         <v>20</v>
       </c>
-    </row>
-    <row r="188" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="N187" t="s">
+        <v>981</v>
+      </c>
+      <c r="O187" t="s">
+        <v>2089</v>
+      </c>
+      <c r="P187" t="s">
+        <v>2271</v>
+      </c>
+      <c r="Q187" t="s">
+        <v>983</v>
+      </c>
+      <c r="R187" t="s">
+        <v>984</v>
+      </c>
+      <c r="S187" t="s">
+        <v>985</v>
+      </c>
+      <c r="T187" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="188" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B188" t="s">
         <v>2090</v>
       </c>
@@ -17019,8 +17735,29 @@
       <c r="L188">
         <v>20</v>
       </c>
-    </row>
-    <row r="189" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="N188" t="s">
+        <v>981</v>
+      </c>
+      <c r="O188" t="s">
+        <v>2090</v>
+      </c>
+      <c r="P188" t="s">
+        <v>2272</v>
+      </c>
+      <c r="Q188" t="s">
+        <v>983</v>
+      </c>
+      <c r="R188" t="s">
+        <v>984</v>
+      </c>
+      <c r="S188" t="s">
+        <v>985</v>
+      </c>
+      <c r="T188" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="189" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B189" t="s">
         <v>2091</v>
       </c>
@@ -17054,8 +17791,29 @@
       <c r="L189">
         <v>20</v>
       </c>
-    </row>
-    <row r="190" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="N189" t="s">
+        <v>981</v>
+      </c>
+      <c r="O189" t="s">
+        <v>2091</v>
+      </c>
+      <c r="P189" t="s">
+        <v>2273</v>
+      </c>
+      <c r="Q189" t="s">
+        <v>983</v>
+      </c>
+      <c r="R189" t="s">
+        <v>984</v>
+      </c>
+      <c r="S189" t="s">
+        <v>985</v>
+      </c>
+      <c r="T189" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="190" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B190" t="s">
         <v>2092</v>
       </c>
@@ -17089,8 +17847,29 @@
       <c r="L190">
         <v>20</v>
       </c>
-    </row>
-    <row r="191" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="N190" t="s">
+        <v>981</v>
+      </c>
+      <c r="O190" t="s">
+        <v>2092</v>
+      </c>
+      <c r="P190" t="s">
+        <v>2274</v>
+      </c>
+      <c r="Q190" t="s">
+        <v>983</v>
+      </c>
+      <c r="R190" t="s">
+        <v>984</v>
+      </c>
+      <c r="S190" t="s">
+        <v>985</v>
+      </c>
+      <c r="T190" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="191" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B191" t="s">
         <v>2093</v>
       </c>
@@ -17124,8 +17903,29 @@
       <c r="L191">
         <v>20</v>
       </c>
-    </row>
-    <row r="192" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="N191" t="s">
+        <v>981</v>
+      </c>
+      <c r="O191" t="s">
+        <v>2093</v>
+      </c>
+      <c r="P191" t="s">
+        <v>2275</v>
+      </c>
+      <c r="Q191" t="s">
+        <v>983</v>
+      </c>
+      <c r="R191" t="s">
+        <v>984</v>
+      </c>
+      <c r="S191" t="s">
+        <v>985</v>
+      </c>
+      <c r="T191" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="192" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B192" t="s">
         <v>2094</v>
       </c>
@@ -17158,6 +17958,27 @@
       </c>
       <c r="L192">
         <v>20</v>
+      </c>
+      <c r="N192" t="s">
+        <v>981</v>
+      </c>
+      <c r="O192" t="s">
+        <v>2094</v>
+      </c>
+      <c r="P192" t="s">
+        <v>2276</v>
+      </c>
+      <c r="Q192" t="s">
+        <v>983</v>
+      </c>
+      <c r="R192" t="s">
+        <v>984</v>
+      </c>
+      <c r="S192" t="s">
+        <v>985</v>
+      </c>
+      <c r="T192" t="s">
+        <v>1008</v>
       </c>
     </row>
   </sheetData>
@@ -17166,7 +17987,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1D41610-ED92-4B9C-A13B-9A0625CF53C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60643B43-A968-480A-9509-BDCC86D72FCE}">
   <dimension ref="B9:T294"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -31592,7 +32413,7 @@
         <v>30</v>
       </c>
       <c r="L271">
-        <v>0.29867587392232586</v>
+        <v>0.29867587392232575</v>
       </c>
       <c r="N271" t="s">
         <v>981</v>
@@ -32859,7 +33680,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC499A46-1642-48A9-BA9D-8634228F0CBA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4987F84C-C3A0-4DCB-9C49-6BB4866C3FEB}">
   <dimension ref="B9:T1106"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -34078,7 +34899,7 @@
         <v>47</v>
       </c>
       <c r="P32" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q32" t="s">
         <v>983</v>
@@ -34131,7 +34952,7 @@
         <v>47</v>
       </c>
       <c r="P33" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q33" t="s">
         <v>983</v>
@@ -43936,7 +44757,7 @@
         <v>289</v>
       </c>
       <c r="P218" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q218" t="s">
         <v>983</v>
@@ -43989,7 +44810,7 @@
         <v>289</v>
       </c>
       <c r="P219" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q219" t="s">
         <v>983</v>
@@ -63870,7 +64691,7 @@
         <v>817</v>
       </c>
       <c r="P612" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q612" t="s">
         <v>983</v>
@@ -63923,7 +64744,7 @@
         <v>817</v>
       </c>
       <c r="P613" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q613" t="s">
         <v>983</v>
@@ -65089,7 +65910,7 @@
         <v>846</v>
       </c>
       <c r="P635" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q635" t="s">
         <v>983</v>
@@ -65142,7 +65963,7 @@
         <v>846</v>
       </c>
       <c r="P636" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q636" t="s">
         <v>983</v>
@@ -65513,7 +66334,7 @@
         <v>860</v>
       </c>
       <c r="P643" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q643" t="s">
         <v>983</v>
@@ -65566,7 +66387,7 @@
         <v>860</v>
       </c>
       <c r="P644" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q644" t="s">
         <v>983</v>
@@ -66865,7 +67686,7 @@
         <v>908</v>
       </c>
       <c r="P668" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q668" t="s">
         <v>983</v>
@@ -66921,7 +67742,7 @@
         <v>908</v>
       </c>
       <c r="P669" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q669" t="s">
         <v>983</v>
@@ -68209,7 +69030,7 @@
         <v>947</v>
       </c>
       <c r="P692" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q692" t="s">
         <v>983</v>
@@ -68265,7 +69086,7 @@
         <v>947</v>
       </c>
       <c r="P693" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q693" t="s">
         <v>983</v>
@@ -68881,7 +69702,7 @@
         <v>965</v>
       </c>
       <c r="P704" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q704" t="s">
         <v>983</v>
@@ -68937,7 +69758,7 @@
         <v>965</v>
       </c>
       <c r="P705" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q705" t="s">
         <v>983</v>
@@ -72522,7 +73343,7 @@
         <v>2025</v>
       </c>
       <c r="F804">
-        <v>0.57679999999999998</v>
+        <v>0.28860000000000002</v>
       </c>
       <c r="G804">
         <v>1</v>
@@ -72531,7 +73352,7 @@
         <v>1032.75</v>
       </c>
       <c r="I804">
-        <v>17.550000000000004</v>
+        <v>17.55</v>
       </c>
       <c r="J804">
         <v>0</v>
@@ -72540,7 +73361,7 @@
         <v>30</v>
       </c>
       <c r="L804">
-        <v>0.22305009092480443</v>
+        <v>0.22305009092480438</v>
       </c>
     </row>
     <row r="805" spans="2:12" x14ac:dyDescent="0.45">
@@ -72557,7 +73378,7 @@
         <v>2025</v>
       </c>
       <c r="F805">
-        <v>0.28860000000000002</v>
+        <v>0.57679999999999998</v>
       </c>
       <c r="G805">
         <v>1</v>
@@ -72566,7 +73387,7 @@
         <v>1032.75</v>
       </c>
       <c r="I805">
-        <v>17.55</v>
+        <v>17.550000000000004</v>
       </c>
       <c r="J805">
         <v>0</v>
@@ -72575,7 +73396,7 @@
         <v>30</v>
       </c>
       <c r="L805">
-        <v>0.22305009092480438</v>
+        <v>0.22305009092480443</v>
       </c>
     </row>
     <row r="806" spans="2:12" x14ac:dyDescent="0.45">
@@ -78968,7 +79789,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L988">
-        <v>0.29867587392232586</v>
+        <v>0.29867587392232575</v>
       </c>
     </row>
     <row r="989" spans="2:12" x14ac:dyDescent="0.45">
@@ -78991,7 +79812,7 @@
         <v>0.33123000000000008</v>
       </c>
       <c r="L989">
-        <v>0.29867587392232586</v>
+        <v>0.29867587392232575</v>
       </c>
     </row>
     <row r="990" spans="2:12" x14ac:dyDescent="0.45">
@@ -79014,7 +79835,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L990">
-        <v>0.29867587392232586</v>
+        <v>0.29867587392232575</v>
       </c>
     </row>
     <row r="991" spans="2:12" x14ac:dyDescent="0.45">
@@ -83083,7 +83904,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80367680-66D2-427C-9505-46D5C3C886DB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8849A602-EFD9-44FF-8F53-23A63E186173}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_BRA_grids/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA_grids/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D2E7BA2-46CC-4082-A1CB-8EC323383A66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{38EF2314-D77A-4BDD-98B8-9EC3F0D06133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4F41E43D-DDC1-41A4-B56B-D7C3221D923C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{17FFA557-4A63-4799-849B-7396792958D7}"/>
   </bookViews>
   <sheets>
     <sheet name="additional_hydro_pot" sheetId="5" r:id="rId1"/>
@@ -7334,7 +7334,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9A6ADD7-0C79-4449-A419-C24AF617D585}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3774AB2D-2809-406C-802D-DA91A64E659C}">
   <dimension ref="B9:O18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7721,7 +7721,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA7E3FC1-6B0F-406A-97BA-1717C611EEC2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97B9602D-F4EC-4EE1-A6DA-D4DD662F8628}">
   <dimension ref="B9:T192"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17987,7 +17987,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60643B43-A968-480A-9509-BDCC86D72FCE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{349FDEEC-94F8-4B32-8EFD-AF9D61E604AE}">
   <dimension ref="B9:T294"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -33680,7 +33680,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4987F84C-C3A0-4DCB-9C49-6BB4866C3FEB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93FBBBAA-F44F-4AB1-A9EB-4FD132ACD499}">
   <dimension ref="B9:T1106"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -44757,7 +44757,7 @@
         <v>289</v>
       </c>
       <c r="P218" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q218" t="s">
         <v>983</v>
@@ -44810,7 +44810,7 @@
         <v>289</v>
       </c>
       <c r="P219" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q219" t="s">
         <v>983</v>
@@ -64797,7 +64797,7 @@
         <v>819</v>
       </c>
       <c r="P614" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q614" t="s">
         <v>983</v>
@@ -64850,7 +64850,7 @@
         <v>819</v>
       </c>
       <c r="P615" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q615" t="s">
         <v>983</v>
@@ -65539,7 +65539,7 @@
         <v>835</v>
       </c>
       <c r="P628" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q628" t="s">
         <v>983</v>
@@ -65592,7 +65592,7 @@
         <v>835</v>
       </c>
       <c r="P629" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q629" t="s">
         <v>983</v>
@@ -67686,7 +67686,7 @@
         <v>908</v>
       </c>
       <c r="P668" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q668" t="s">
         <v>983</v>
@@ -67742,7 +67742,7 @@
         <v>908</v>
       </c>
       <c r="P669" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q669" t="s">
         <v>983</v>
@@ -69422,7 +69422,7 @@
         <v>958</v>
       </c>
       <c r="P699" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q699" t="s">
         <v>983</v>
@@ -69478,7 +69478,7 @@
         <v>958</v>
       </c>
       <c r="P700" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q700" t="s">
         <v>983</v>
@@ -69702,7 +69702,7 @@
         <v>965</v>
       </c>
       <c r="P704" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q704" t="s">
         <v>983</v>
@@ -69758,7 +69758,7 @@
         <v>965</v>
       </c>
       <c r="P705" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q705" t="s">
         <v>983</v>
@@ -73343,7 +73343,7 @@
         <v>2025</v>
       </c>
       <c r="F804">
-        <v>0.28860000000000002</v>
+        <v>0.57679999999999998</v>
       </c>
       <c r="G804">
         <v>1</v>
@@ -73352,7 +73352,7 @@
         <v>1032.75</v>
       </c>
       <c r="I804">
-        <v>17.55</v>
+        <v>17.550000000000004</v>
       </c>
       <c r="J804">
         <v>0</v>
@@ -73361,7 +73361,7 @@
         <v>30</v>
       </c>
       <c r="L804">
-        <v>0.22305009092480438</v>
+        <v>0.22305009092480443</v>
       </c>
     </row>
     <row r="805" spans="2:12" x14ac:dyDescent="0.45">
@@ -73378,7 +73378,7 @@
         <v>2025</v>
       </c>
       <c r="F805">
-        <v>0.57679999999999998</v>
+        <v>0.28860000000000002</v>
       </c>
       <c r="G805">
         <v>1</v>
@@ -73387,7 +73387,7 @@
         <v>1032.75</v>
       </c>
       <c r="I805">
-        <v>17.550000000000004</v>
+        <v>17.55</v>
       </c>
       <c r="J805">
         <v>0</v>
@@ -73396,7 +73396,7 @@
         <v>30</v>
       </c>
       <c r="L805">
-        <v>0.22305009092480443</v>
+        <v>0.22305009092480438</v>
       </c>
     </row>
     <row r="806" spans="2:12" x14ac:dyDescent="0.45">
@@ -82967,19 +82967,19 @@
         <v>2025</v>
       </c>
       <c r="F1080">
-        <v>2.2800000000000001E-2</v>
+        <v>5.1299999999999998E-2</v>
       </c>
       <c r="G1080">
         <v>1</v>
       </c>
       <c r="H1080">
-        <v>1836</v>
+        <v>1563.9999999999998</v>
       </c>
       <c r="I1080">
-        <v>46.800000000000004</v>
+        <v>39.6</v>
       </c>
       <c r="J1080">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="K1080">
         <v>30</v>
@@ -83002,19 +83002,19 @@
         <v>2025</v>
       </c>
       <c r="F1081">
-        <v>5.1299999999999998E-2</v>
+        <v>2.2800000000000001E-2</v>
       </c>
       <c r="G1081">
         <v>1</v>
       </c>
       <c r="H1081">
-        <v>1563.9999999999998</v>
+        <v>1836</v>
       </c>
       <c r="I1081">
-        <v>39.6</v>
+        <v>46.800000000000004</v>
       </c>
       <c r="J1081">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="K1081">
         <v>30</v>
@@ -83904,7 +83904,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8849A602-EFD9-44FF-8F53-23A63E186173}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16B400D3-5B96-4E84-BACC-6B5BB955F21D}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_BRA_grids/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA_grids/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{38EF2314-D77A-4BDD-98B8-9EC3F0D06133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D91CE030-1B14-418F-8A3C-6E9A7D3268DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{17FFA557-4A63-4799-849B-7396792958D7}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0E0DD59D-4252-45EE-A989-36B7532FD915}"/>
   </bookViews>
   <sheets>
     <sheet name="additional_hydro_pot" sheetId="5" r:id="rId1"/>
@@ -7334,7 +7334,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3774AB2D-2809-406C-802D-DA91A64E659C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA066B3C-FB7E-4A12-8078-4ADC593A7FC9}">
   <dimension ref="B9:O18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7721,7 +7721,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97B9602D-F4EC-4EE1-A6DA-D4DD662F8628}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA71C4A1-02B5-4B4B-A15F-8CCB0483B9AB}">
   <dimension ref="B9:T192"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17987,7 +17987,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{349FDEEC-94F8-4B32-8EFD-AF9D61E604AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67192C0A-0913-4775-A07E-EBBF999B4897}">
   <dimension ref="B9:T294"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -32413,7 +32413,7 @@
         <v>30</v>
       </c>
       <c r="L271">
-        <v>0.29867587392232575</v>
+        <v>0.29867587392232581</v>
       </c>
       <c r="N271" t="s">
         <v>981</v>
@@ -33680,7 +33680,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93FBBBAA-F44F-4AB1-A9EB-4FD132ACD499}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{139F5AAD-258D-421C-A381-DBA4F82216DC}">
   <dimension ref="B9:T1106"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -34475,7 +34475,7 @@
         <v>36</v>
       </c>
       <c r="P24" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q24" t="s">
         <v>983</v>
@@ -34528,7 +34528,7 @@
         <v>36</v>
       </c>
       <c r="P25" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q25" t="s">
         <v>983</v>
@@ -34899,7 +34899,7 @@
         <v>47</v>
       </c>
       <c r="P32" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q32" t="s">
         <v>983</v>
@@ -34952,7 +34952,7 @@
         <v>47</v>
       </c>
       <c r="P33" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q33" t="s">
         <v>983</v>
@@ -45393,7 +45393,7 @@
         <v>303</v>
       </c>
       <c r="P230" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q230" t="s">
         <v>983</v>
@@ -45446,7 +45446,7 @@
         <v>303</v>
       </c>
       <c r="P231" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q231" t="s">
         <v>983</v>
@@ -64691,7 +64691,7 @@
         <v>817</v>
       </c>
       <c r="P612" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q612" t="s">
         <v>983</v>
@@ -64744,7 +64744,7 @@
         <v>817</v>
       </c>
       <c r="P613" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q613" t="s">
         <v>983</v>
@@ -64956,7 +64956,7 @@
         <v>823</v>
       </c>
       <c r="P617" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q617" t="s">
         <v>983</v>
@@ -65009,7 +65009,7 @@
         <v>823</v>
       </c>
       <c r="P618" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q618" t="s">
         <v>983</v>
@@ -65115,7 +65115,7 @@
         <v>826</v>
       </c>
       <c r="P620" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q620" t="s">
         <v>983</v>
@@ -65168,7 +65168,7 @@
         <v>826</v>
       </c>
       <c r="P621" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q621" t="s">
         <v>983</v>
@@ -65221,7 +65221,7 @@
         <v>828</v>
       </c>
       <c r="P622" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q622" t="s">
         <v>983</v>
@@ -65274,7 +65274,7 @@
         <v>828</v>
       </c>
       <c r="P623" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q623" t="s">
         <v>983</v>
@@ -65539,7 +65539,7 @@
         <v>835</v>
       </c>
       <c r="P628" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q628" t="s">
         <v>983</v>
@@ -65592,7 +65592,7 @@
         <v>835</v>
       </c>
       <c r="P629" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q629" t="s">
         <v>983</v>
@@ -65910,7 +65910,7 @@
         <v>846</v>
       </c>
       <c r="P635" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q635" t="s">
         <v>983</v>
@@ -65963,7 +65963,7 @@
         <v>846</v>
       </c>
       <c r="P636" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q636" t="s">
         <v>983</v>
@@ -66334,7 +66334,7 @@
         <v>860</v>
       </c>
       <c r="P643" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q643" t="s">
         <v>983</v>
@@ -66387,7 +66387,7 @@
         <v>860</v>
       </c>
       <c r="P644" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q644" t="s">
         <v>983</v>
@@ -68750,7 +68750,7 @@
         <v>942</v>
       </c>
       <c r="P687" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q687" t="s">
         <v>983</v>
@@ -68806,7 +68806,7 @@
         <v>942</v>
       </c>
       <c r="P688" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q688" t="s">
         <v>983</v>
@@ -69030,7 +69030,7 @@
         <v>947</v>
       </c>
       <c r="P692" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q692" t="s">
         <v>983</v>
@@ -69086,7 +69086,7 @@
         <v>947</v>
       </c>
       <c r="P693" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q693" t="s">
         <v>983</v>
@@ -69422,7 +69422,7 @@
         <v>958</v>
       </c>
       <c r="P699" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q699" t="s">
         <v>983</v>
@@ -69478,7 +69478,7 @@
         <v>958</v>
       </c>
       <c r="P700" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="Q700" t="s">
         <v>983</v>
@@ -79789,7 +79789,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L988">
-        <v>0.29867587392232575</v>
+        <v>0.29867587392232581</v>
       </c>
     </row>
     <row r="989" spans="2:12" x14ac:dyDescent="0.45">
@@ -79812,7 +79812,7 @@
         <v>0.33123000000000008</v>
       </c>
       <c r="L989">
-        <v>0.29867587392232575</v>
+        <v>0.29867587392232581</v>
       </c>
     </row>
     <row r="990" spans="2:12" x14ac:dyDescent="0.45">
@@ -79835,7 +79835,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L990">
-        <v>0.29867587392232575</v>
+        <v>0.29867587392232581</v>
       </c>
     </row>
     <row r="991" spans="2:12" x14ac:dyDescent="0.45">
@@ -82967,19 +82967,19 @@
         <v>2025</v>
       </c>
       <c r="F1080">
-        <v>5.1299999999999998E-2</v>
+        <v>2.2800000000000001E-2</v>
       </c>
       <c r="G1080">
         <v>1</v>
       </c>
       <c r="H1080">
-        <v>1563.9999999999998</v>
+        <v>1836</v>
       </c>
       <c r="I1080">
-        <v>39.6</v>
+        <v>46.800000000000004</v>
       </c>
       <c r="J1080">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="K1080">
         <v>30</v>
@@ -83002,19 +83002,19 @@
         <v>2025</v>
       </c>
       <c r="F1081">
-        <v>2.2800000000000001E-2</v>
+        <v>5.1299999999999998E-2</v>
       </c>
       <c r="G1081">
         <v>1</v>
       </c>
       <c r="H1081">
-        <v>1836</v>
+        <v>1563.9999999999998</v>
       </c>
       <c r="I1081">
-        <v>46.800000000000004</v>
+        <v>39.6</v>
       </c>
       <c r="J1081">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="K1081">
         <v>30</v>
@@ -83904,7 +83904,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16B400D3-5B96-4E84-BACC-6B5BB955F21D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{405788FC-1A45-492F-8DD4-5E116DC21BB9}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_BRA_grids/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA_grids/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66103B3E-E8AE-4E57-88B3-5E4208A241B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4FB13706-99F2-4DCB-A3CA-9BFC95AA15A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{BD8071A4-C4E2-42CB-9A59-5BDAD86672C0}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{80DEA6E1-89D8-4BD7-81BE-295FBB59E2FC}"/>
   </bookViews>
   <sheets>
     <sheet name="additional_hydro_pot" sheetId="5" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13152" uniqueCount="2311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13142" uniqueCount="2310">
   <si>
     <t>~fi_t</t>
   </si>
@@ -5062,9 +5062,6 @@
   </si>
   <si>
     <t>en_pc_windon_wind_069</t>
-  </si>
-  <si>
-    <t>en_pc_windon_wind_500</t>
   </si>
   <si>
     <t>en_pc_windon_wind_G100000906282</t>
@@ -7343,7 +7340,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4F5BF11-1D5E-43FD-8D42-DED1F214DFA8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32204DE5-2072-4790-A826-CBA73B2258C4}">
   <dimension ref="B9:O18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7360,25 +7357,25 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
+        <v>2279</v>
+      </c>
+      <c r="D10" t="s">
         <v>2280</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>2281</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>2282</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>2283</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>2284</v>
       </c>
-      <c r="H10" t="s">
-        <v>2285</v>
-      </c>
       <c r="J10" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="K10" t="s">
         <v>1</v>
@@ -7387,10 +7384,10 @@
         <v>974</v>
       </c>
       <c r="M10" t="s">
+        <v>2298</v>
+      </c>
+      <c r="N10" t="s">
         <v>2299</v>
-      </c>
-      <c r="N10" t="s">
-        <v>2300</v>
       </c>
       <c r="O10" t="s">
         <v>977</v>
@@ -7398,7 +7395,7 @@
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>2286</v>
+        <v>2285</v>
       </c>
       <c r="C11" t="s">
         <v>478</v>
@@ -7419,33 +7416,33 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="J11" t="s">
+        <v>2300</v>
+      </c>
+      <c r="K11" t="s">
+        <v>2285</v>
+      </c>
+      <c r="L11" t="s">
         <v>2301</v>
       </c>
-      <c r="K11" t="s">
-        <v>2286</v>
-      </c>
-      <c r="L11" t="s">
+      <c r="M11" t="s">
+        <v>982</v>
+      </c>
+      <c r="N11" t="s">
+        <v>981</v>
+      </c>
+      <c r="O11" t="s">
         <v>2302</v>
-      </c>
-      <c r="M11" t="s">
-        <v>982</v>
-      </c>
-      <c r="N11" t="s">
-        <v>981</v>
-      </c>
-      <c r="O11" t="s">
-        <v>2303</v>
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="C12" t="s">
         <v>478</v>
       </c>
       <c r="D12" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="E12">
         <v>8</v>
@@ -7460,13 +7457,13 @@
         <v>0.48</v>
       </c>
       <c r="J12" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="K12" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="L12" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="M12" t="s">
         <v>982</v>
@@ -7475,18 +7472,18 @@
         <v>981</v>
       </c>
       <c r="O12" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="C13" t="s">
         <v>478</v>
       </c>
       <c r="D13" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="E13">
         <v>4</v>
@@ -7501,13 +7498,13 @@
         <v>0.52</v>
       </c>
       <c r="J13" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="K13" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="L13" t="s">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="M13" t="s">
         <v>982</v>
@@ -7516,12 +7513,12 @@
         <v>981</v>
       </c>
       <c r="O13" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="C14" t="s">
         <v>478</v>
@@ -7542,13 +7539,13 @@
         <v>0.45</v>
       </c>
       <c r="J14" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="K14" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="L14" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="M14" t="s">
         <v>982</v>
@@ -7557,12 +7554,12 @@
         <v>981</v>
       </c>
       <c r="O14" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
       <c r="C15" t="s">
         <v>478</v>
@@ -7583,13 +7580,13 @@
         <v>0.5</v>
       </c>
       <c r="J15" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="K15" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
       <c r="L15" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
       <c r="M15" t="s">
         <v>982</v>
@@ -7598,12 +7595,12 @@
         <v>981</v>
       </c>
       <c r="O15" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
       <c r="C16" t="s">
         <v>478</v>
@@ -7624,13 +7621,13 @@
         <v>0.4</v>
       </c>
       <c r="J16" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="K16" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
       <c r="L16" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="M16" t="s">
         <v>982</v>
@@ -7639,18 +7636,18 @@
         <v>981</v>
       </c>
       <c r="O16" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="C17" t="s">
         <v>478</v>
       </c>
       <c r="D17" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="E17">
         <v>6</v>
@@ -7665,13 +7662,13 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="J17" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="K17" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="L17" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="M17" t="s">
         <v>982</v>
@@ -7680,18 +7677,18 @@
         <v>981</v>
       </c>
       <c r="O17" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="C18" t="s">
         <v>478</v>
       </c>
       <c r="D18" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="E18">
         <v>8</v>
@@ -7706,13 +7703,13 @@
         <v>0.42</v>
       </c>
       <c r="J18" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="K18" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="L18" t="s">
-        <v>2310</v>
+        <v>2309</v>
       </c>
       <c r="M18" t="s">
         <v>982</v>
@@ -7721,7 +7718,7 @@
         <v>981</v>
       </c>
       <c r="O18" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
     </row>
   </sheetData>
@@ -7730,7 +7727,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB9F51E6-44A5-422B-B456-AFD673EAB488}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC7BDC3-029F-44B2-B0BF-52C1AEC4E1DB}">
   <dimension ref="B9:T192"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7765,13 +7762,13 @@
         <v>9</v>
       </c>
       <c r="I10" t="s">
+        <v>1912</v>
+      </c>
+      <c r="J10" t="s">
         <v>1913</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>1914</v>
-      </c>
-      <c r="K10" t="s">
-        <v>1915</v>
       </c>
       <c r="L10" t="s">
         <v>10</v>
@@ -7800,7 +7797,7 @@
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="C11" t="s">
         <v>355</v>
@@ -7836,10 +7833,10 @@
         <v>979</v>
       </c>
       <c r="O11" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="P11" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="Q11" t="s">
         <v>981</v>
@@ -7856,7 +7853,7 @@
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="C12" t="s">
         <v>355</v>
@@ -7892,10 +7889,10 @@
         <v>979</v>
       </c>
       <c r="O12" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="P12" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
       <c r="Q12" t="s">
         <v>981</v>
@@ -7912,7 +7909,7 @@
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="C13" t="s">
         <v>355</v>
@@ -7948,10 +7945,10 @@
         <v>979</v>
       </c>
       <c r="O13" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="P13" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="Q13" t="s">
         <v>981</v>
@@ -7968,7 +7965,7 @@
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="C14" t="s">
         <v>355</v>
@@ -8004,10 +8001,10 @@
         <v>979</v>
       </c>
       <c r="O14" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="P14" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="Q14" t="s">
         <v>981</v>
@@ -8024,7 +8021,7 @@
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="C15" t="s">
         <v>355</v>
@@ -8060,10 +8057,10 @@
         <v>979</v>
       </c>
       <c r="O15" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="P15" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="Q15" t="s">
         <v>981</v>
@@ -8080,7 +8077,7 @@
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="C16" t="s">
         <v>355</v>
@@ -8116,10 +8113,10 @@
         <v>979</v>
       </c>
       <c r="O16" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="P16" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="Q16" t="s">
         <v>981</v>
@@ -8136,7 +8133,7 @@
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="C17" t="s">
         <v>355</v>
@@ -8172,10 +8169,10 @@
         <v>979</v>
       </c>
       <c r="O17" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="P17" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="Q17" t="s">
         <v>981</v>
@@ -8192,7 +8189,7 @@
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="C18" t="s">
         <v>355</v>
@@ -8228,10 +8225,10 @@
         <v>979</v>
       </c>
       <c r="O18" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="P18" t="s">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="Q18" t="s">
         <v>981</v>
@@ -8248,7 +8245,7 @@
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="C19" t="s">
         <v>355</v>
@@ -8284,10 +8281,10 @@
         <v>979</v>
       </c>
       <c r="O19" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
       <c r="P19" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="Q19" t="s">
         <v>981</v>
@@ -8304,7 +8301,7 @@
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="C20" t="s">
         <v>355</v>
@@ -8340,10 +8337,10 @@
         <v>979</v>
       </c>
       <c r="O20" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="P20" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="Q20" t="s">
         <v>981</v>
@@ -8360,7 +8357,7 @@
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="C21" t="s">
         <v>355</v>
@@ -8396,10 +8393,10 @@
         <v>979</v>
       </c>
       <c r="O21" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="P21" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="Q21" t="s">
         <v>981</v>
@@ -8416,7 +8413,7 @@
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="C22" t="s">
         <v>355</v>
@@ -8452,10 +8449,10 @@
         <v>979</v>
       </c>
       <c r="O22" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="P22" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="Q22" t="s">
         <v>981</v>
@@ -8472,7 +8469,7 @@
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="C23" t="s">
         <v>355</v>
@@ -8508,10 +8505,10 @@
         <v>979</v>
       </c>
       <c r="O23" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="P23" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="Q23" t="s">
         <v>981</v>
@@ -8528,7 +8525,7 @@
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="C24" t="s">
         <v>355</v>
@@ -8564,10 +8561,10 @@
         <v>979</v>
       </c>
       <c r="O24" t="s">
-        <v>1929</v>
+        <v>1928</v>
       </c>
       <c r="P24" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="Q24" t="s">
         <v>981</v>
@@ -8584,7 +8581,7 @@
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="C25" t="s">
         <v>329</v>
@@ -8620,10 +8617,10 @@
         <v>979</v>
       </c>
       <c r="O25" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
       <c r="P25" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="Q25" t="s">
         <v>981</v>
@@ -8640,7 +8637,7 @@
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="C26" t="s">
         <v>329</v>
@@ -8676,10 +8673,10 @@
         <v>979</v>
       </c>
       <c r="O26" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="P26" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="Q26" t="s">
         <v>981</v>
@@ -8696,7 +8693,7 @@
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="C27" t="s">
         <v>355</v>
@@ -8732,10 +8729,10 @@
         <v>979</v>
       </c>
       <c r="O27" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="P27" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="Q27" t="s">
         <v>981</v>
@@ -8752,7 +8749,7 @@
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="C28" t="s">
         <v>355</v>
@@ -8788,10 +8785,10 @@
         <v>979</v>
       </c>
       <c r="O28" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="P28" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="Q28" t="s">
         <v>981</v>
@@ -8808,7 +8805,7 @@
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="C29" t="s">
         <v>355</v>
@@ -8844,10 +8841,10 @@
         <v>979</v>
       </c>
       <c r="O29" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="P29" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="Q29" t="s">
         <v>981</v>
@@ -8864,7 +8861,7 @@
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="C30" t="s">
         <v>355</v>
@@ -8900,10 +8897,10 @@
         <v>979</v>
       </c>
       <c r="O30" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="P30" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="Q30" t="s">
         <v>981</v>
@@ -8920,7 +8917,7 @@
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="C31" t="s">
         <v>355</v>
@@ -8956,10 +8953,10 @@
         <v>979</v>
       </c>
       <c r="O31" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="P31" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
       <c r="Q31" t="s">
         <v>981</v>
@@ -8976,7 +8973,7 @@
     </row>
     <row r="32" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="C32" t="s">
         <v>355</v>
@@ -9012,10 +9009,10 @@
         <v>979</v>
       </c>
       <c r="O32" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="P32" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="Q32" t="s">
         <v>981</v>
@@ -9032,7 +9029,7 @@
     </row>
     <row r="33" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="C33" t="s">
         <v>355</v>
@@ -9068,10 +9065,10 @@
         <v>979</v>
       </c>
       <c r="O33" t="s">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="P33" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="Q33" t="s">
         <v>981</v>
@@ -9088,7 +9085,7 @@
     </row>
     <row r="34" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="C34" t="s">
         <v>355</v>
@@ -9124,10 +9121,10 @@
         <v>979</v>
       </c>
       <c r="O34" t="s">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="P34" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="Q34" t="s">
         <v>981</v>
@@ -9144,7 +9141,7 @@
     </row>
     <row r="35" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="C35" t="s">
         <v>355</v>
@@ -9180,10 +9177,10 @@
         <v>979</v>
       </c>
       <c r="O35" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="P35" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="Q35" t="s">
         <v>981</v>
@@ -9200,7 +9197,7 @@
     </row>
     <row r="36" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="C36" t="s">
         <v>355</v>
@@ -9236,10 +9233,10 @@
         <v>979</v>
       </c>
       <c r="O36" t="s">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="P36" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="Q36" t="s">
         <v>981</v>
@@ -9256,7 +9253,7 @@
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="C37" t="s">
         <v>355</v>
@@ -9292,10 +9289,10 @@
         <v>979</v>
       </c>
       <c r="O37" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
       <c r="P37" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
       <c r="Q37" t="s">
         <v>981</v>
@@ -9312,7 +9309,7 @@
     </row>
     <row r="38" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="C38" t="s">
         <v>355</v>
@@ -9348,10 +9345,10 @@
         <v>979</v>
       </c>
       <c r="O38" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="P38" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
       <c r="Q38" t="s">
         <v>981</v>
@@ -9368,7 +9365,7 @@
     </row>
     <row r="39" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="C39" t="s">
         <v>355</v>
@@ -9404,10 +9401,10 @@
         <v>979</v>
       </c>
       <c r="O39" t="s">
-        <v>1944</v>
+        <v>1943</v>
       </c>
       <c r="P39" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="Q39" t="s">
         <v>981</v>
@@ -9424,7 +9421,7 @@
     </row>
     <row r="40" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="C40" t="s">
         <v>355</v>
@@ -9460,10 +9457,10 @@
         <v>979</v>
       </c>
       <c r="O40" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="P40" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
       <c r="Q40" t="s">
         <v>981</v>
@@ -9480,7 +9477,7 @@
     </row>
     <row r="41" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="C41" t="s">
         <v>355</v>
@@ -9516,10 +9513,10 @@
         <v>979</v>
       </c>
       <c r="O41" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="P41" t="s">
-        <v>2128</v>
+        <v>2127</v>
       </c>
       <c r="Q41" t="s">
         <v>981</v>
@@ -9536,7 +9533,7 @@
     </row>
     <row r="42" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="C42" t="s">
         <v>355</v>
@@ -9572,10 +9569,10 @@
         <v>979</v>
       </c>
       <c r="O42" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="P42" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="Q42" t="s">
         <v>981</v>
@@ -9592,7 +9589,7 @@
     </row>
     <row r="43" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="C43" t="s">
         <v>329</v>
@@ -9628,10 +9625,10 @@
         <v>979</v>
       </c>
       <c r="O43" t="s">
-        <v>1948</v>
+        <v>1947</v>
       </c>
       <c r="P43" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="Q43" t="s">
         <v>981</v>
@@ -9648,7 +9645,7 @@
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B44" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="C44" t="s">
         <v>329</v>
@@ -9684,10 +9681,10 @@
         <v>979</v>
       </c>
       <c r="O44" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="P44" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="Q44" t="s">
         <v>981</v>
@@ -9704,7 +9701,7 @@
     </row>
     <row r="45" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B45" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="C45" t="s">
         <v>329</v>
@@ -9740,10 +9737,10 @@
         <v>979</v>
       </c>
       <c r="O45" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="P45" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="Q45" t="s">
         <v>981</v>
@@ -9760,7 +9757,7 @@
     </row>
     <row r="46" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B46" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="C46" t="s">
         <v>329</v>
@@ -9796,10 +9793,10 @@
         <v>979</v>
       </c>
       <c r="O46" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="P46" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="Q46" t="s">
         <v>981</v>
@@ -9816,7 +9813,7 @@
     </row>
     <row r="47" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="C47" t="s">
         <v>329</v>
@@ -9852,10 +9849,10 @@
         <v>979</v>
       </c>
       <c r="O47" t="s">
-        <v>1952</v>
+        <v>1951</v>
       </c>
       <c r="P47" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="Q47" t="s">
         <v>981</v>
@@ -9872,7 +9869,7 @@
     </row>
     <row r="48" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="C48" t="s">
         <v>329</v>
@@ -9908,10 +9905,10 @@
         <v>979</v>
       </c>
       <c r="O48" t="s">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="P48" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="Q48" t="s">
         <v>981</v>
@@ -9928,7 +9925,7 @@
     </row>
     <row r="49" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="C49" t="s">
         <v>329</v>
@@ -9964,10 +9961,10 @@
         <v>979</v>
       </c>
       <c r="O49" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
       <c r="P49" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="Q49" t="s">
         <v>981</v>
@@ -9984,7 +9981,7 @@
     </row>
     <row r="50" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="C50" t="s">
         <v>329</v>
@@ -10020,10 +10017,10 @@
         <v>979</v>
       </c>
       <c r="O50" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="P50" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="Q50" t="s">
         <v>981</v>
@@ -10040,7 +10037,7 @@
     </row>
     <row r="51" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="C51" t="s">
         <v>329</v>
@@ -10076,10 +10073,10 @@
         <v>979</v>
       </c>
       <c r="O51" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="P51" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="Q51" t="s">
         <v>981</v>
@@ -10096,7 +10093,7 @@
     </row>
     <row r="52" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="C52" t="s">
         <v>329</v>
@@ -10132,10 +10129,10 @@
         <v>979</v>
       </c>
       <c r="O52" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="P52" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="Q52" t="s">
         <v>981</v>
@@ -10152,7 +10149,7 @@
     </row>
     <row r="53" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B53" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="C53" t="s">
         <v>329</v>
@@ -10188,10 +10185,10 @@
         <v>979</v>
       </c>
       <c r="O53" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="P53" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="Q53" t="s">
         <v>981</v>
@@ -10208,7 +10205,7 @@
     </row>
     <row r="54" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B54" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="C54" t="s">
         <v>329</v>
@@ -10244,10 +10241,10 @@
         <v>979</v>
       </c>
       <c r="O54" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="P54" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="Q54" t="s">
         <v>981</v>
@@ -10264,7 +10261,7 @@
     </row>
     <row r="55" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B55" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="C55" t="s">
         <v>329</v>
@@ -10300,10 +10297,10 @@
         <v>979</v>
       </c>
       <c r="O55" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="P55" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="Q55" t="s">
         <v>981</v>
@@ -10320,7 +10317,7 @@
     </row>
     <row r="56" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B56" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="C56" t="s">
         <v>329</v>
@@ -10356,10 +10353,10 @@
         <v>979</v>
       </c>
       <c r="O56" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="P56" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="Q56" t="s">
         <v>981</v>
@@ -10376,7 +10373,7 @@
     </row>
     <row r="57" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="C57" t="s">
         <v>329</v>
@@ -10412,10 +10409,10 @@
         <v>979</v>
       </c>
       <c r="O57" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="P57" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="Q57" t="s">
         <v>981</v>
@@ -10432,7 +10429,7 @@
     </row>
     <row r="58" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="C58" t="s">
         <v>329</v>
@@ -10468,10 +10465,10 @@
         <v>979</v>
       </c>
       <c r="O58" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="P58" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="Q58" t="s">
         <v>981</v>
@@ -10488,7 +10485,7 @@
     </row>
     <row r="59" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B59" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="C59" t="s">
         <v>329</v>
@@ -10524,10 +10521,10 @@
         <v>979</v>
       </c>
       <c r="O59" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="P59" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="Q59" t="s">
         <v>981</v>
@@ -10544,7 +10541,7 @@
     </row>
     <row r="60" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B60" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="C60" t="s">
         <v>329</v>
@@ -10580,10 +10577,10 @@
         <v>979</v>
       </c>
       <c r="O60" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="P60" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="Q60" t="s">
         <v>981</v>
@@ -10600,7 +10597,7 @@
     </row>
     <row r="61" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B61" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="C61" t="s">
         <v>355</v>
@@ -10636,10 +10633,10 @@
         <v>979</v>
       </c>
       <c r="O61" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="P61" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="Q61" t="s">
         <v>981</v>
@@ -10656,7 +10653,7 @@
     </row>
     <row r="62" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B62" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="C62" t="s">
         <v>355</v>
@@ -10692,10 +10689,10 @@
         <v>979</v>
       </c>
       <c r="O62" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="P62" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="Q62" t="s">
         <v>981</v>
@@ -10712,7 +10709,7 @@
     </row>
     <row r="63" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B63" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="C63" t="s">
         <v>355</v>
@@ -10748,10 +10745,10 @@
         <v>979</v>
       </c>
       <c r="O63" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="P63" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="Q63" t="s">
         <v>981</v>
@@ -10768,7 +10765,7 @@
     </row>
     <row r="64" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B64" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="C64" t="s">
         <v>355</v>
@@ -10804,10 +10801,10 @@
         <v>979</v>
       </c>
       <c r="O64" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="P64" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="Q64" t="s">
         <v>981</v>
@@ -10824,7 +10821,7 @@
     </row>
     <row r="65" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B65" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="C65" t="s">
         <v>355</v>
@@ -10860,10 +10857,10 @@
         <v>979</v>
       </c>
       <c r="O65" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="P65" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="Q65" t="s">
         <v>981</v>
@@ -10880,7 +10877,7 @@
     </row>
     <row r="66" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B66" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="C66" t="s">
         <v>355</v>
@@ -10916,10 +10913,10 @@
         <v>979</v>
       </c>
       <c r="O66" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="P66" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="Q66" t="s">
         <v>981</v>
@@ -10936,7 +10933,7 @@
     </row>
     <row r="67" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B67" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="C67" t="s">
         <v>355</v>
@@ -10972,10 +10969,10 @@
         <v>979</v>
       </c>
       <c r="O67" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="P67" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="Q67" t="s">
         <v>981</v>
@@ -10992,7 +10989,7 @@
     </row>
     <row r="68" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B68" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="C68" t="s">
         <v>355</v>
@@ -11028,10 +11025,10 @@
         <v>979</v>
       </c>
       <c r="O68" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="P68" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
       <c r="Q68" t="s">
         <v>981</v>
@@ -11048,7 +11045,7 @@
     </row>
     <row r="69" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B69" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="C69" t="s">
         <v>355</v>
@@ -11084,10 +11081,10 @@
         <v>979</v>
       </c>
       <c r="O69" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="P69" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="Q69" t="s">
         <v>981</v>
@@ -11104,7 +11101,7 @@
     </row>
     <row r="70" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B70" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="C70" t="s">
         <v>355</v>
@@ -11140,10 +11137,10 @@
         <v>979</v>
       </c>
       <c r="O70" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="P70" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="Q70" t="s">
         <v>981</v>
@@ -11160,7 +11157,7 @@
     </row>
     <row r="71" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B71" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="C71" t="s">
         <v>355</v>
@@ -11196,10 +11193,10 @@
         <v>979</v>
       </c>
       <c r="O71" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="P71" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="Q71" t="s">
         <v>981</v>
@@ -11216,7 +11213,7 @@
     </row>
     <row r="72" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B72" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="C72" t="s">
         <v>355</v>
@@ -11252,10 +11249,10 @@
         <v>979</v>
       </c>
       <c r="O72" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="P72" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="Q72" t="s">
         <v>981</v>
@@ -11272,7 +11269,7 @@
     </row>
     <row r="73" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B73" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="C73" t="s">
         <v>355</v>
@@ -11308,10 +11305,10 @@
         <v>979</v>
       </c>
       <c r="O73" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="P73" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="Q73" t="s">
         <v>981</v>
@@ -11328,7 +11325,7 @@
     </row>
     <row r="74" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B74" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="C74" t="s">
         <v>355</v>
@@ -11364,10 +11361,10 @@
         <v>979</v>
       </c>
       <c r="O74" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="P74" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="Q74" t="s">
         <v>981</v>
@@ -11384,7 +11381,7 @@
     </row>
     <row r="75" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B75" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="C75" t="s">
         <v>355</v>
@@ -11420,10 +11417,10 @@
         <v>979</v>
       </c>
       <c r="O75" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="P75" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="Q75" t="s">
         <v>981</v>
@@ -11440,7 +11437,7 @@
     </row>
     <row r="76" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B76" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="C76" t="s">
         <v>355</v>
@@ -11476,10 +11473,10 @@
         <v>979</v>
       </c>
       <c r="O76" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="P76" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="Q76" t="s">
         <v>981</v>
@@ -11496,7 +11493,7 @@
     </row>
     <row r="77" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B77" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="C77" t="s">
         <v>355</v>
@@ -11532,10 +11529,10 @@
         <v>979</v>
       </c>
       <c r="O77" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="P77" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="Q77" t="s">
         <v>981</v>
@@ -11552,7 +11549,7 @@
     </row>
     <row r="78" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B78" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="C78" t="s">
         <v>355</v>
@@ -11588,10 +11585,10 @@
         <v>979</v>
       </c>
       <c r="O78" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="P78" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="Q78" t="s">
         <v>981</v>
@@ -11608,7 +11605,7 @@
     </row>
     <row r="79" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B79" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="C79" t="s">
         <v>355</v>
@@ -11644,10 +11641,10 @@
         <v>979</v>
       </c>
       <c r="O79" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="P79" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="Q79" t="s">
         <v>981</v>
@@ -11664,7 +11661,7 @@
     </row>
     <row r="80" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B80" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="C80" t="s">
         <v>355</v>
@@ -11700,10 +11697,10 @@
         <v>979</v>
       </c>
       <c r="O80" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="P80" t="s">
-        <v>2167</v>
+        <v>2166</v>
       </c>
       <c r="Q80" t="s">
         <v>981</v>
@@ -11720,7 +11717,7 @@
     </row>
     <row r="81" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B81" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="C81" t="s">
         <v>355</v>
@@ -11756,10 +11753,10 @@
         <v>979</v>
       </c>
       <c r="O81" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="P81" t="s">
-        <v>2168</v>
+        <v>2167</v>
       </c>
       <c r="Q81" t="s">
         <v>981</v>
@@ -11776,7 +11773,7 @@
     </row>
     <row r="82" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B82" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="C82" t="s">
         <v>355</v>
@@ -11812,10 +11809,10 @@
         <v>979</v>
       </c>
       <c r="O82" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="P82" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="Q82" t="s">
         <v>981</v>
@@ -11832,7 +11829,7 @@
     </row>
     <row r="83" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B83" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="C83" t="s">
         <v>355</v>
@@ -11868,10 +11865,10 @@
         <v>979</v>
       </c>
       <c r="O83" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="P83" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="Q83" t="s">
         <v>981</v>
@@ -11888,7 +11885,7 @@
     </row>
     <row r="84" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B84" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="C84" t="s">
         <v>355</v>
@@ -11924,10 +11921,10 @@
         <v>979</v>
       </c>
       <c r="O84" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="P84" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="Q84" t="s">
         <v>981</v>
@@ -11944,7 +11941,7 @@
     </row>
     <row r="85" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B85" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="C85" t="s">
         <v>355</v>
@@ -11980,10 +11977,10 @@
         <v>979</v>
       </c>
       <c r="O85" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="P85" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="Q85" t="s">
         <v>981</v>
@@ -12000,7 +11997,7 @@
     </row>
     <row r="86" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B86" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="C86" t="s">
         <v>355</v>
@@ -12036,10 +12033,10 @@
         <v>979</v>
       </c>
       <c r="O86" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="P86" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="Q86" t="s">
         <v>981</v>
@@ -12056,7 +12053,7 @@
     </row>
     <row r="87" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B87" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="C87" t="s">
         <v>355</v>
@@ -12092,10 +12089,10 @@
         <v>979</v>
       </c>
       <c r="O87" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="P87" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
       <c r="Q87" t="s">
         <v>981</v>
@@ -12112,7 +12109,7 @@
     </row>
     <row r="88" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B88" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="C88" t="s">
         <v>355</v>
@@ -12148,10 +12145,10 @@
         <v>979</v>
       </c>
       <c r="O88" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="P88" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="Q88" t="s">
         <v>981</v>
@@ -12168,7 +12165,7 @@
     </row>
     <row r="89" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B89" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="C89" t="s">
         <v>355</v>
@@ -12204,10 +12201,10 @@
         <v>979</v>
       </c>
       <c r="O89" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="P89" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="Q89" t="s">
         <v>981</v>
@@ -12224,7 +12221,7 @@
     </row>
     <row r="90" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B90" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="C90" t="s">
         <v>355</v>
@@ -12260,10 +12257,10 @@
         <v>979</v>
       </c>
       <c r="O90" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="P90" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="Q90" t="s">
         <v>981</v>
@@ -12280,7 +12277,7 @@
     </row>
     <row r="91" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B91" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="C91" t="s">
         <v>355</v>
@@ -12316,10 +12313,10 @@
         <v>979</v>
       </c>
       <c r="O91" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="P91" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="Q91" t="s">
         <v>981</v>
@@ -12336,7 +12333,7 @@
     </row>
     <row r="92" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B92" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="C92" t="s">
         <v>355</v>
@@ -12372,10 +12369,10 @@
         <v>979</v>
       </c>
       <c r="O92" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="P92" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
       <c r="Q92" t="s">
         <v>981</v>
@@ -12392,7 +12389,7 @@
     </row>
     <row r="93" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B93" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="C93" t="s">
         <v>355</v>
@@ -12428,10 +12425,10 @@
         <v>979</v>
       </c>
       <c r="O93" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="P93" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="Q93" t="s">
         <v>981</v>
@@ -12448,7 +12445,7 @@
     </row>
     <row r="94" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B94" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="C94" t="s">
         <v>355</v>
@@ -12484,10 +12481,10 @@
         <v>979</v>
       </c>
       <c r="O94" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="P94" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="Q94" t="s">
         <v>981</v>
@@ -12504,7 +12501,7 @@
     </row>
     <row r="95" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B95" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="C95" t="s">
         <v>355</v>
@@ -12540,10 +12537,10 @@
         <v>979</v>
       </c>
       <c r="O95" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="P95" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="Q95" t="s">
         <v>981</v>
@@ -12560,7 +12557,7 @@
     </row>
     <row r="96" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B96" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C96" t="s">
         <v>355</v>
@@ -12596,10 +12593,10 @@
         <v>979</v>
       </c>
       <c r="O96" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="P96" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
       <c r="Q96" t="s">
         <v>981</v>
@@ -12616,7 +12613,7 @@
     </row>
     <row r="97" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B97" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="C97" t="s">
         <v>355</v>
@@ -12652,10 +12649,10 @@
         <v>979</v>
       </c>
       <c r="O97" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="P97" t="s">
-        <v>2184</v>
+        <v>2183</v>
       </c>
       <c r="Q97" t="s">
         <v>981</v>
@@ -12672,7 +12669,7 @@
     </row>
     <row r="98" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B98" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="C98" t="s">
         <v>355</v>
@@ -12708,10 +12705,10 @@
         <v>979</v>
       </c>
       <c r="O98" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="P98" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="Q98" t="s">
         <v>981</v>
@@ -12728,7 +12725,7 @@
     </row>
     <row r="99" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B99" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="C99" t="s">
         <v>355</v>
@@ -12764,10 +12761,10 @@
         <v>979</v>
       </c>
       <c r="O99" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="P99" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="Q99" t="s">
         <v>981</v>
@@ -12784,7 +12781,7 @@
     </row>
     <row r="100" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B100" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="C100" t="s">
         <v>355</v>
@@ -12820,10 +12817,10 @@
         <v>979</v>
       </c>
       <c r="O100" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="P100" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
       <c r="Q100" t="s">
         <v>981</v>
@@ -12840,7 +12837,7 @@
     </row>
     <row r="101" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B101" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="C101" t="s">
         <v>355</v>
@@ -12876,10 +12873,10 @@
         <v>979</v>
       </c>
       <c r="O101" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="P101" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="Q101" t="s">
         <v>981</v>
@@ -12896,7 +12893,7 @@
     </row>
     <row r="102" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B102" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="C102" t="s">
         <v>355</v>
@@ -12932,10 +12929,10 @@
         <v>979</v>
       </c>
       <c r="O102" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="P102" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="Q102" t="s">
         <v>981</v>
@@ -12952,7 +12949,7 @@
     </row>
     <row r="103" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B103" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="C103" t="s">
         <v>355</v>
@@ -12988,10 +12985,10 @@
         <v>979</v>
       </c>
       <c r="O103" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="P103" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="Q103" t="s">
         <v>981</v>
@@ -13008,7 +13005,7 @@
     </row>
     <row r="104" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B104" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="C104" t="s">
         <v>355</v>
@@ -13044,10 +13041,10 @@
         <v>979</v>
       </c>
       <c r="O104" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="P104" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="Q104" t="s">
         <v>981</v>
@@ -13064,7 +13061,7 @@
     </row>
     <row r="105" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B105" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="C105" t="s">
         <v>355</v>
@@ -13100,10 +13097,10 @@
         <v>979</v>
       </c>
       <c r="O105" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="P105" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="Q105" t="s">
         <v>981</v>
@@ -13120,7 +13117,7 @@
     </row>
     <row r="106" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B106" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="C106" t="s">
         <v>355</v>
@@ -13156,10 +13153,10 @@
         <v>979</v>
       </c>
       <c r="O106" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="P106" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
       <c r="Q106" t="s">
         <v>981</v>
@@ -13176,7 +13173,7 @@
     </row>
     <row r="107" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B107" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="C107" t="s">
         <v>355</v>
@@ -13212,10 +13209,10 @@
         <v>979</v>
       </c>
       <c r="O107" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="P107" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
       <c r="Q107" t="s">
         <v>981</v>
@@ -13232,7 +13229,7 @@
     </row>
     <row r="108" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B108" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="C108" t="s">
         <v>355</v>
@@ -13268,10 +13265,10 @@
         <v>979</v>
       </c>
       <c r="O108" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="P108" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
       <c r="Q108" t="s">
         <v>981</v>
@@ -13288,7 +13285,7 @@
     </row>
     <row r="109" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B109" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="C109" t="s">
         <v>355</v>
@@ -13324,10 +13321,10 @@
         <v>979</v>
       </c>
       <c r="O109" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="P109" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="Q109" t="s">
         <v>981</v>
@@ -13344,7 +13341,7 @@
     </row>
     <row r="110" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B110" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="C110" t="s">
         <v>355</v>
@@ -13380,10 +13377,10 @@
         <v>979</v>
       </c>
       <c r="O110" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="P110" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="Q110" t="s">
         <v>981</v>
@@ -13400,7 +13397,7 @@
     </row>
     <row r="111" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B111" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="C111" t="s">
         <v>355</v>
@@ -13436,10 +13433,10 @@
         <v>979</v>
       </c>
       <c r="O111" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="P111" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
       <c r="Q111" t="s">
         <v>981</v>
@@ -13456,7 +13453,7 @@
     </row>
     <row r="112" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B112" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="C112" t="s">
         <v>355</v>
@@ -13492,10 +13489,10 @@
         <v>979</v>
       </c>
       <c r="O112" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="P112" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
       <c r="Q112" t="s">
         <v>981</v>
@@ -13512,7 +13509,7 @@
     </row>
     <row r="113" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B113" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C113" t="s">
         <v>355</v>
@@ -13548,10 +13545,10 @@
         <v>979</v>
       </c>
       <c r="O113" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="P113" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
       <c r="Q113" t="s">
         <v>981</v>
@@ -13568,7 +13565,7 @@
     </row>
     <row r="114" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B114" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C114" t="s">
         <v>355</v>
@@ -13604,10 +13601,10 @@
         <v>979</v>
       </c>
       <c r="O114" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="P114" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="Q114" t="s">
         <v>981</v>
@@ -13624,7 +13621,7 @@
     </row>
     <row r="115" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B115" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C115" t="s">
         <v>355</v>
@@ -13660,10 +13657,10 @@
         <v>979</v>
       </c>
       <c r="O115" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="P115" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="Q115" t="s">
         <v>981</v>
@@ -13680,7 +13677,7 @@
     </row>
     <row r="116" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B116" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C116" t="s">
         <v>355</v>
@@ -13716,10 +13713,10 @@
         <v>979</v>
       </c>
       <c r="O116" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="P116" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="Q116" t="s">
         <v>981</v>
@@ -13736,7 +13733,7 @@
     </row>
     <row r="117" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B117" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C117" t="s">
         <v>355</v>
@@ -13772,10 +13769,10 @@
         <v>979</v>
       </c>
       <c r="O117" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="P117" t="s">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="Q117" t="s">
         <v>981</v>
@@ -13792,7 +13789,7 @@
     </row>
     <row r="118" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B118" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C118" t="s">
         <v>355</v>
@@ -13828,10 +13825,10 @@
         <v>979</v>
       </c>
       <c r="O118" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="P118" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="Q118" t="s">
         <v>981</v>
@@ -13848,7 +13845,7 @@
     </row>
     <row r="119" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B119" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C119" t="s">
         <v>355</v>
@@ -13884,10 +13881,10 @@
         <v>979</v>
       </c>
       <c r="O119" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="P119" t="s">
-        <v>2206</v>
+        <v>2205</v>
       </c>
       <c r="Q119" t="s">
         <v>981</v>
@@ -13904,7 +13901,7 @@
     </row>
     <row r="120" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B120" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C120" t="s">
         <v>355</v>
@@ -13940,10 +13937,10 @@
         <v>979</v>
       </c>
       <c r="O120" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="P120" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="Q120" t="s">
         <v>981</v>
@@ -13960,7 +13957,7 @@
     </row>
     <row r="121" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B121" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C121" t="s">
         <v>355</v>
@@ -13996,10 +13993,10 @@
         <v>979</v>
       </c>
       <c r="O121" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="P121" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="Q121" t="s">
         <v>981</v>
@@ -14016,7 +14013,7 @@
     </row>
     <row r="122" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B122" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C122" t="s">
         <v>355</v>
@@ -14052,10 +14049,10 @@
         <v>979</v>
       </c>
       <c r="O122" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="P122" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
       <c r="Q122" t="s">
         <v>981</v>
@@ -14072,7 +14069,7 @@
     </row>
     <row r="123" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B123" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C123" t="s">
         <v>355</v>
@@ -14108,10 +14105,10 @@
         <v>979</v>
       </c>
       <c r="O123" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="P123" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
       <c r="Q123" t="s">
         <v>981</v>
@@ -14128,7 +14125,7 @@
     </row>
     <row r="124" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B124" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="C124" t="s">
         <v>355</v>
@@ -14164,10 +14161,10 @@
         <v>979</v>
       </c>
       <c r="O124" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="P124" t="s">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="Q124" t="s">
         <v>981</v>
@@ -14184,7 +14181,7 @@
     </row>
     <row r="125" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B125" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="C125" t="s">
         <v>355</v>
@@ -14220,10 +14217,10 @@
         <v>979</v>
       </c>
       <c r="O125" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="P125" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="Q125" t="s">
         <v>981</v>
@@ -14240,7 +14237,7 @@
     </row>
     <row r="126" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B126" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C126" t="s">
         <v>355</v>
@@ -14276,10 +14273,10 @@
         <v>979</v>
       </c>
       <c r="O126" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="P126" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
       <c r="Q126" t="s">
         <v>981</v>
@@ -14296,7 +14293,7 @@
     </row>
     <row r="127" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B127" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="C127" t="s">
         <v>355</v>
@@ -14332,10 +14329,10 @@
         <v>979</v>
       </c>
       <c r="O127" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="P127" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
       <c r="Q127" t="s">
         <v>981</v>
@@ -14352,7 +14349,7 @@
     </row>
     <row r="128" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B128" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="C128" t="s">
         <v>355</v>
@@ -14388,10 +14385,10 @@
         <v>979</v>
       </c>
       <c r="O128" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="P128" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="Q128" t="s">
         <v>981</v>
@@ -14408,7 +14405,7 @@
     </row>
     <row r="129" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B129" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="C129" t="s">
         <v>355</v>
@@ -14444,10 +14441,10 @@
         <v>979</v>
       </c>
       <c r="O129" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="P129" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
       <c r="Q129" t="s">
         <v>981</v>
@@ -14464,7 +14461,7 @@
     </row>
     <row r="130" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B130" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="C130" t="s">
         <v>355</v>
@@ -14500,10 +14497,10 @@
         <v>979</v>
       </c>
       <c r="O130" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="P130" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="Q130" t="s">
         <v>981</v>
@@ -14520,7 +14517,7 @@
     </row>
     <row r="131" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B131" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="C131" t="s">
         <v>355</v>
@@ -14556,10 +14553,10 @@
         <v>979</v>
       </c>
       <c r="O131" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="P131" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
       <c r="Q131" t="s">
         <v>981</v>
@@ -14576,7 +14573,7 @@
     </row>
     <row r="132" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B132" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="C132" t="s">
         <v>355</v>
@@ -14612,10 +14609,10 @@
         <v>979</v>
       </c>
       <c r="O132" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="P132" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
       <c r="Q132" t="s">
         <v>981</v>
@@ -14632,7 +14629,7 @@
     </row>
     <row r="133" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B133" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="C133" t="s">
         <v>355</v>
@@ -14668,10 +14665,10 @@
         <v>979</v>
       </c>
       <c r="O133" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="P133" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="Q133" t="s">
         <v>981</v>
@@ -14688,7 +14685,7 @@
     </row>
     <row r="134" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B134" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="C134" t="s">
         <v>355</v>
@@ -14724,10 +14721,10 @@
         <v>979</v>
       </c>
       <c r="O134" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="P134" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="Q134" t="s">
         <v>981</v>
@@ -14744,7 +14741,7 @@
     </row>
     <row r="135" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B135" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="C135" t="s">
         <v>355</v>
@@ -14780,10 +14777,10 @@
         <v>979</v>
       </c>
       <c r="O135" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="P135" t="s">
-        <v>2222</v>
+        <v>2221</v>
       </c>
       <c r="Q135" t="s">
         <v>981</v>
@@ -14800,7 +14797,7 @@
     </row>
     <row r="136" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B136" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="C136" t="s">
         <v>355</v>
@@ -14836,10 +14833,10 @@
         <v>979</v>
       </c>
       <c r="O136" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="P136" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="Q136" t="s">
         <v>981</v>
@@ -14856,7 +14853,7 @@
     </row>
     <row r="137" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B137" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="C137" t="s">
         <v>355</v>
@@ -14892,10 +14889,10 @@
         <v>979</v>
       </c>
       <c r="O137" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="P137" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
       <c r="Q137" t="s">
         <v>981</v>
@@ -14912,7 +14909,7 @@
     </row>
     <row r="138" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B138" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="C138" t="s">
         <v>355</v>
@@ -14948,10 +14945,10 @@
         <v>979</v>
       </c>
       <c r="O138" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="P138" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="Q138" t="s">
         <v>981</v>
@@ -14968,7 +14965,7 @@
     </row>
     <row r="139" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B139" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="C139" t="s">
         <v>355</v>
@@ -15004,10 +15001,10 @@
         <v>979</v>
       </c>
       <c r="O139" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="P139" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="Q139" t="s">
         <v>981</v>
@@ -15024,7 +15021,7 @@
     </row>
     <row r="140" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B140" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="C140" t="s">
         <v>355</v>
@@ -15060,10 +15057,10 @@
         <v>979</v>
       </c>
       <c r="O140" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="P140" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
       <c r="Q140" t="s">
         <v>981</v>
@@ -15080,7 +15077,7 @@
     </row>
     <row r="141" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B141" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="C141" t="s">
         <v>355</v>
@@ -15116,10 +15113,10 @@
         <v>979</v>
       </c>
       <c r="O141" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="P141" t="s">
-        <v>2228</v>
+        <v>2227</v>
       </c>
       <c r="Q141" t="s">
         <v>981</v>
@@ -15136,7 +15133,7 @@
     </row>
     <row r="142" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B142" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="C142" t="s">
         <v>355</v>
@@ -15172,10 +15169,10 @@
         <v>979</v>
       </c>
       <c r="O142" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="P142" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="Q142" t="s">
         <v>981</v>
@@ -15192,7 +15189,7 @@
     </row>
     <row r="143" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B143" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="C143" t="s">
         <v>355</v>
@@ -15228,10 +15225,10 @@
         <v>979</v>
       </c>
       <c r="O143" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="P143" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
       <c r="Q143" t="s">
         <v>981</v>
@@ -15248,7 +15245,7 @@
     </row>
     <row r="144" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B144" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="C144" t="s">
         <v>355</v>
@@ -15284,10 +15281,10 @@
         <v>979</v>
       </c>
       <c r="O144" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="P144" t="s">
-        <v>2231</v>
+        <v>2230</v>
       </c>
       <c r="Q144" t="s">
         <v>981</v>
@@ -15304,7 +15301,7 @@
     </row>
     <row r="145" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B145" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="C145" t="s">
         <v>355</v>
@@ -15340,10 +15337,10 @@
         <v>979</v>
       </c>
       <c r="O145" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="P145" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="Q145" t="s">
         <v>981</v>
@@ -15360,7 +15357,7 @@
     </row>
     <row r="146" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B146" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="C146" t="s">
         <v>355</v>
@@ -15396,10 +15393,10 @@
         <v>979</v>
       </c>
       <c r="O146" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="P146" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="Q146" t="s">
         <v>981</v>
@@ -15416,7 +15413,7 @@
     </row>
     <row r="147" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B147" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="C147" t="s">
         <v>355</v>
@@ -15452,10 +15449,10 @@
         <v>979</v>
       </c>
       <c r="O147" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="P147" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="Q147" t="s">
         <v>981</v>
@@ -15472,7 +15469,7 @@
     </row>
     <row r="148" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B148" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="C148" t="s">
         <v>355</v>
@@ -15508,10 +15505,10 @@
         <v>979</v>
       </c>
       <c r="O148" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="P148" t="s">
-        <v>2235</v>
+        <v>2234</v>
       </c>
       <c r="Q148" t="s">
         <v>981</v>
@@ -15528,7 +15525,7 @@
     </row>
     <row r="149" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B149" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="C149" t="s">
         <v>355</v>
@@ -15564,10 +15561,10 @@
         <v>979</v>
       </c>
       <c r="O149" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="P149" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="Q149" t="s">
         <v>981</v>
@@ -15584,7 +15581,7 @@
     </row>
     <row r="150" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B150" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="C150" t="s">
         <v>355</v>
@@ -15620,10 +15617,10 @@
         <v>979</v>
       </c>
       <c r="O150" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="P150" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="Q150" t="s">
         <v>981</v>
@@ -15640,7 +15637,7 @@
     </row>
     <row r="151" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B151" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="C151" t="s">
         <v>355</v>
@@ -15676,10 +15673,10 @@
         <v>979</v>
       </c>
       <c r="O151" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="P151" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="Q151" t="s">
         <v>981</v>
@@ -15696,7 +15693,7 @@
     </row>
     <row r="152" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B152" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="C152" t="s">
         <v>355</v>
@@ -15732,10 +15729,10 @@
         <v>979</v>
       </c>
       <c r="O152" t="s">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="P152" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="Q152" t="s">
         <v>981</v>
@@ -15752,7 +15749,7 @@
     </row>
     <row r="153" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B153" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="C153" t="s">
         <v>355</v>
@@ -15788,10 +15785,10 @@
         <v>979</v>
       </c>
       <c r="O153" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="P153" t="s">
-        <v>2240</v>
+        <v>2239</v>
       </c>
       <c r="Q153" t="s">
         <v>981</v>
@@ -15808,7 +15805,7 @@
     </row>
     <row r="154" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B154" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="C154" t="s">
         <v>355</v>
@@ -15844,10 +15841,10 @@
         <v>979</v>
       </c>
       <c r="O154" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="P154" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
       <c r="Q154" t="s">
         <v>981</v>
@@ -15864,7 +15861,7 @@
     </row>
     <row r="155" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B155" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="C155" t="s">
         <v>355</v>
@@ -15900,10 +15897,10 @@
         <v>979</v>
       </c>
       <c r="O155" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="P155" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
       <c r="Q155" t="s">
         <v>981</v>
@@ -15920,7 +15917,7 @@
     </row>
     <row r="156" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B156" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="C156" t="s">
         <v>355</v>
@@ -15956,10 +15953,10 @@
         <v>979</v>
       </c>
       <c r="O156" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
       <c r="P156" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="Q156" t="s">
         <v>981</v>
@@ -15976,7 +15973,7 @@
     </row>
     <row r="157" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B157" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="C157" t="s">
         <v>355</v>
@@ -16012,10 +16009,10 @@
         <v>979</v>
       </c>
       <c r="O157" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="P157" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="Q157" t="s">
         <v>981</v>
@@ -16032,7 +16029,7 @@
     </row>
     <row r="158" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B158" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="C158" t="s">
         <v>355</v>
@@ -16068,10 +16065,10 @@
         <v>979</v>
       </c>
       <c r="O158" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="P158" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
       <c r="Q158" t="s">
         <v>981</v>
@@ -16088,7 +16085,7 @@
     </row>
     <row r="159" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B159" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="C159" t="s">
         <v>715</v>
@@ -16124,10 +16121,10 @@
         <v>979</v>
       </c>
       <c r="O159" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
       <c r="P159" t="s">
-        <v>2246</v>
+        <v>2245</v>
       </c>
       <c r="Q159" t="s">
         <v>981</v>
@@ -16144,7 +16141,7 @@
     </row>
     <row r="160" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B160" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="C160" t="s">
         <v>715</v>
@@ -16180,10 +16177,10 @@
         <v>979</v>
       </c>
       <c r="O160" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="P160" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="Q160" t="s">
         <v>981</v>
@@ -16200,7 +16197,7 @@
     </row>
     <row r="161" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B161" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="C161" t="s">
         <v>715</v>
@@ -16236,10 +16233,10 @@
         <v>979</v>
       </c>
       <c r="O161" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="P161" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="Q161" t="s">
         <v>981</v>
@@ -16256,7 +16253,7 @@
     </row>
     <row r="162" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B162" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="C162" t="s">
         <v>715</v>
@@ -16292,10 +16289,10 @@
         <v>979</v>
       </c>
       <c r="O162" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="P162" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="Q162" t="s">
         <v>981</v>
@@ -16312,7 +16309,7 @@
     </row>
     <row r="163" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B163" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="C163" t="s">
         <v>715</v>
@@ -16348,10 +16345,10 @@
         <v>979</v>
       </c>
       <c r="O163" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="P163" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="Q163" t="s">
         <v>981</v>
@@ -16368,7 +16365,7 @@
     </row>
     <row r="164" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B164" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="C164" t="s">
         <v>715</v>
@@ -16404,10 +16401,10 @@
         <v>979</v>
       </c>
       <c r="O164" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="P164" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
       <c r="Q164" t="s">
         <v>981</v>
@@ -16424,7 +16421,7 @@
     </row>
     <row r="165" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B165" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="C165" t="s">
         <v>715</v>
@@ -16460,10 +16457,10 @@
         <v>979</v>
       </c>
       <c r="O165" t="s">
-        <v>2070</v>
+        <v>2069</v>
       </c>
       <c r="P165" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="Q165" t="s">
         <v>981</v>
@@ -16480,7 +16477,7 @@
     </row>
     <row r="166" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B166" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="C166" t="s">
         <v>715</v>
@@ -16516,10 +16513,10 @@
         <v>979</v>
       </c>
       <c r="O166" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="P166" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="Q166" t="s">
         <v>981</v>
@@ -16536,7 +16533,7 @@
     </row>
     <row r="167" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B167" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="C167" t="s">
         <v>715</v>
@@ -16572,10 +16569,10 @@
         <v>979</v>
       </c>
       <c r="O167" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="P167" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="Q167" t="s">
         <v>981</v>
@@ -16592,7 +16589,7 @@
     </row>
     <row r="168" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B168" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="C168" t="s">
         <v>715</v>
@@ -16628,10 +16625,10 @@
         <v>979</v>
       </c>
       <c r="O168" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="P168" t="s">
-        <v>2255</v>
+        <v>2254</v>
       </c>
       <c r="Q168" t="s">
         <v>981</v>
@@ -16648,7 +16645,7 @@
     </row>
     <row r="169" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B169" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="C169" t="s">
         <v>715</v>
@@ -16684,10 +16681,10 @@
         <v>979</v>
       </c>
       <c r="O169" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="P169" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="Q169" t="s">
         <v>981</v>
@@ -16704,7 +16701,7 @@
     </row>
     <row r="170" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B170" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="C170" t="s">
         <v>715</v>
@@ -16740,10 +16737,10 @@
         <v>979</v>
       </c>
       <c r="O170" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="P170" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
       <c r="Q170" t="s">
         <v>981</v>
@@ -16760,7 +16757,7 @@
     </row>
     <row r="171" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B171" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="C171" t="s">
         <v>715</v>
@@ -16796,10 +16793,10 @@
         <v>979</v>
       </c>
       <c r="O171" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="P171" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
       <c r="Q171" t="s">
         <v>981</v>
@@ -16816,7 +16813,7 @@
     </row>
     <row r="172" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B172" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="C172" t="s">
         <v>715</v>
@@ -16852,10 +16849,10 @@
         <v>979</v>
       </c>
       <c r="O172" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="P172" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="Q172" t="s">
         <v>981</v>
@@ -16872,7 +16869,7 @@
     </row>
     <row r="173" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B173" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="C173" t="s">
         <v>715</v>
@@ -16908,10 +16905,10 @@
         <v>979</v>
       </c>
       <c r="O173" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="P173" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="Q173" t="s">
         <v>981</v>
@@ -16928,7 +16925,7 @@
     </row>
     <row r="174" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B174" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="C174" t="s">
         <v>715</v>
@@ -16964,10 +16961,10 @@
         <v>979</v>
       </c>
       <c r="O174" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="P174" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="Q174" t="s">
         <v>981</v>
@@ -16984,7 +16981,7 @@
     </row>
     <row r="175" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B175" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="C175" t="s">
         <v>715</v>
@@ -17020,10 +17017,10 @@
         <v>979</v>
       </c>
       <c r="O175" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="P175" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="Q175" t="s">
         <v>981</v>
@@ -17040,7 +17037,7 @@
     </row>
     <row r="176" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B176" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="C176" t="s">
         <v>715</v>
@@ -17076,10 +17073,10 @@
         <v>979</v>
       </c>
       <c r="O176" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="P176" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="Q176" t="s">
         <v>981</v>
@@ -17096,7 +17093,7 @@
     </row>
     <row r="177" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B177" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="C177" t="s">
         <v>715</v>
@@ -17132,10 +17129,10 @@
         <v>979</v>
       </c>
       <c r="O177" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="P177" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="Q177" t="s">
         <v>981</v>
@@ -17152,7 +17149,7 @@
     </row>
     <row r="178" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B178" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C178" t="s">
         <v>715</v>
@@ -17188,10 +17185,10 @@
         <v>979</v>
       </c>
       <c r="O178" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="P178" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="Q178" t="s">
         <v>981</v>
@@ -17208,7 +17205,7 @@
     </row>
     <row r="179" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B179" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
       <c r="C179" t="s">
         <v>715</v>
@@ -17244,10 +17241,10 @@
         <v>979</v>
       </c>
       <c r="O179" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
       <c r="P179" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="Q179" t="s">
         <v>981</v>
@@ -17264,7 +17261,7 @@
     </row>
     <row r="180" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B180" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="C180" t="s">
         <v>715</v>
@@ -17300,10 +17297,10 @@
         <v>979</v>
       </c>
       <c r="O180" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="P180" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="Q180" t="s">
         <v>981</v>
@@ -17320,7 +17317,7 @@
     </row>
     <row r="181" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B181" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="C181" t="s">
         <v>715</v>
@@ -17356,10 +17353,10 @@
         <v>979</v>
       </c>
       <c r="O181" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="P181" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="Q181" t="s">
         <v>981</v>
@@ -17376,7 +17373,7 @@
     </row>
     <row r="182" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B182" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="C182" t="s">
         <v>715</v>
@@ -17412,10 +17409,10 @@
         <v>979</v>
       </c>
       <c r="O182" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="P182" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="Q182" t="s">
         <v>981</v>
@@ -17432,7 +17429,7 @@
     </row>
     <row r="183" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B183" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="C183" t="s">
         <v>715</v>
@@ -17468,10 +17465,10 @@
         <v>979</v>
       </c>
       <c r="O183" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="P183" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="Q183" t="s">
         <v>981</v>
@@ -17488,7 +17485,7 @@
     </row>
     <row r="184" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B184" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="C184" t="s">
         <v>715</v>
@@ -17524,10 +17521,10 @@
         <v>979</v>
       </c>
       <c r="O184" t="s">
-        <v>2089</v>
+        <v>2088</v>
       </c>
       <c r="P184" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="Q184" t="s">
         <v>981</v>
@@ -17544,7 +17541,7 @@
     </row>
     <row r="185" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B185" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="C185" t="s">
         <v>715</v>
@@ -17580,10 +17577,10 @@
         <v>979</v>
       </c>
       <c r="O185" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="P185" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="Q185" t="s">
         <v>981</v>
@@ -17600,7 +17597,7 @@
     </row>
     <row r="186" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B186" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="C186" t="s">
         <v>715</v>
@@ -17636,10 +17633,10 @@
         <v>979</v>
       </c>
       <c r="O186" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="P186" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="Q186" t="s">
         <v>981</v>
@@ -17656,7 +17653,7 @@
     </row>
     <row r="187" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B187" t="s">
-        <v>2092</v>
+        <v>2091</v>
       </c>
       <c r="C187" t="s">
         <v>715</v>
@@ -17692,10 +17689,10 @@
         <v>979</v>
       </c>
       <c r="O187" t="s">
-        <v>2092</v>
+        <v>2091</v>
       </c>
       <c r="P187" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="Q187" t="s">
         <v>981</v>
@@ -17712,7 +17709,7 @@
     </row>
     <row r="188" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B188" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="C188" t="s">
         <v>715</v>
@@ -17748,10 +17745,10 @@
         <v>979</v>
       </c>
       <c r="O188" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="P188" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
       <c r="Q188" t="s">
         <v>981</v>
@@ -17768,7 +17765,7 @@
     </row>
     <row r="189" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B189" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="C189" t="s">
         <v>715</v>
@@ -17804,10 +17801,10 @@
         <v>979</v>
       </c>
       <c r="O189" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="P189" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
       <c r="Q189" t="s">
         <v>981</v>
@@ -17824,7 +17821,7 @@
     </row>
     <row r="190" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B190" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="C190" t="s">
         <v>715</v>
@@ -17860,10 +17857,10 @@
         <v>979</v>
       </c>
       <c r="O190" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="P190" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
       <c r="Q190" t="s">
         <v>981</v>
@@ -17880,7 +17877,7 @@
     </row>
     <row r="191" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B191" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
       <c r="C191" t="s">
         <v>715</v>
@@ -17916,10 +17913,10 @@
         <v>979</v>
       </c>
       <c r="O191" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
       <c r="P191" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
       <c r="Q191" t="s">
         <v>981</v>
@@ -17936,7 +17933,7 @@
     </row>
     <row r="192" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B192" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="C192" t="s">
         <v>715</v>
@@ -17972,10 +17969,10 @@
         <v>979</v>
       </c>
       <c r="O192" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="P192" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
       <c r="Q192" t="s">
         <v>981</v>
@@ -17996,8 +17993,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{166AA898-0546-405F-BE40-65547AD8FE37}">
-  <dimension ref="B9:T297"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38952182-ED34-4AB4-AB94-4251EF87A23F}">
+  <dimension ref="B9:T296"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="9" spans="2:20" x14ac:dyDescent="0.45">
@@ -18102,7 +18099,7 @@
         <v>1393</v>
       </c>
       <c r="P11" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="Q11" t="s">
         <v>981</v>
@@ -18155,7 +18152,7 @@
         <v>1394</v>
       </c>
       <c r="P12" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="Q12" t="s">
         <v>981</v>
@@ -18208,7 +18205,7 @@
         <v>1395</v>
       </c>
       <c r="P13" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="Q13" t="s">
         <v>981</v>
@@ -18261,7 +18258,7 @@
         <v>1396</v>
       </c>
       <c r="P14" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="Q14" t="s">
         <v>981</v>
@@ -18314,7 +18311,7 @@
         <v>1397</v>
       </c>
       <c r="P15" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="Q15" t="s">
         <v>981</v>
@@ -18367,7 +18364,7 @@
         <v>1398</v>
       </c>
       <c r="P16" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="Q16" t="s">
         <v>981</v>
@@ -18420,7 +18417,7 @@
         <v>1399</v>
       </c>
       <c r="P17" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="Q17" t="s">
         <v>981</v>
@@ -18473,7 +18470,7 @@
         <v>1400</v>
       </c>
       <c r="P18" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="Q18" t="s">
         <v>981</v>
@@ -18526,7 +18523,7 @@
         <v>1401</v>
       </c>
       <c r="P19" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="Q19" t="s">
         <v>981</v>
@@ -18579,7 +18576,7 @@
         <v>1402</v>
       </c>
       <c r="P20" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="Q20" t="s">
         <v>981</v>
@@ -18632,7 +18629,7 @@
         <v>1403</v>
       </c>
       <c r="P21" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="Q21" t="s">
         <v>981</v>
@@ -18685,7 +18682,7 @@
         <v>1404</v>
       </c>
       <c r="P22" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="Q22" t="s">
         <v>981</v>
@@ -18738,7 +18735,7 @@
         <v>1405</v>
       </c>
       <c r="P23" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="Q23" t="s">
         <v>981</v>
@@ -18791,7 +18788,7 @@
         <v>1406</v>
       </c>
       <c r="P24" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="Q24" t="s">
         <v>981</v>
@@ -18844,7 +18841,7 @@
         <v>1407</v>
       </c>
       <c r="P25" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="Q25" t="s">
         <v>981</v>
@@ -18897,7 +18894,7 @@
         <v>1408</v>
       </c>
       <c r="P26" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="Q26" t="s">
         <v>981</v>
@@ -18950,7 +18947,7 @@
         <v>1409</v>
       </c>
       <c r="P27" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="Q27" t="s">
         <v>981</v>
@@ -19003,7 +19000,7 @@
         <v>1410</v>
       </c>
       <c r="P28" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="Q28" t="s">
         <v>981</v>
@@ -19056,7 +19053,7 @@
         <v>1412</v>
       </c>
       <c r="P29" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="Q29" t="s">
         <v>981</v>
@@ -19109,7 +19106,7 @@
         <v>1413</v>
       </c>
       <c r="P30" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="Q30" t="s">
         <v>981</v>
@@ -19162,7 +19159,7 @@
         <v>1415</v>
       </c>
       <c r="P31" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="Q31" t="s">
         <v>981</v>
@@ -19215,7 +19212,7 @@
         <v>1416</v>
       </c>
       <c r="P32" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="Q32" t="s">
         <v>981</v>
@@ -19268,7 +19265,7 @@
         <v>1417</v>
       </c>
       <c r="P33" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="Q33" t="s">
         <v>981</v>
@@ -19321,7 +19318,7 @@
         <v>1418</v>
       </c>
       <c r="P34" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="Q34" t="s">
         <v>981</v>
@@ -19374,7 +19371,7 @@
         <v>1419</v>
       </c>
       <c r="P35" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="Q35" t="s">
         <v>981</v>
@@ -19427,7 +19424,7 @@
         <v>1420</v>
       </c>
       <c r="P36" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="Q36" t="s">
         <v>981</v>
@@ -19480,7 +19477,7 @@
         <v>1421</v>
       </c>
       <c r="P37" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="Q37" t="s">
         <v>981</v>
@@ -19533,7 +19530,7 @@
         <v>1422</v>
       </c>
       <c r="P38" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="Q38" t="s">
         <v>981</v>
@@ -19586,7 +19583,7 @@
         <v>1423</v>
       </c>
       <c r="P39" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="Q39" t="s">
         <v>981</v>
@@ -19639,7 +19636,7 @@
         <v>1424</v>
       </c>
       <c r="P40" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="Q40" t="s">
         <v>981</v>
@@ -19692,7 +19689,7 @@
         <v>1425</v>
       </c>
       <c r="P41" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="Q41" t="s">
         <v>981</v>
@@ -19745,7 +19742,7 @@
         <v>1426</v>
       </c>
       <c r="P42" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="Q42" t="s">
         <v>981</v>
@@ -19798,7 +19795,7 @@
         <v>1427</v>
       </c>
       <c r="P43" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="Q43" t="s">
         <v>981</v>
@@ -19851,7 +19848,7 @@
         <v>1428</v>
       </c>
       <c r="P44" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="Q44" t="s">
         <v>981</v>
@@ -19904,7 +19901,7 @@
         <v>1429</v>
       </c>
       <c r="P45" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="Q45" t="s">
         <v>981</v>
@@ -19957,7 +19954,7 @@
         <v>1430</v>
       </c>
       <c r="P46" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="Q46" t="s">
         <v>981</v>
@@ -20010,7 +20007,7 @@
         <v>1431</v>
       </c>
       <c r="P47" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="Q47" t="s">
         <v>981</v>
@@ -20063,7 +20060,7 @@
         <v>1432</v>
       </c>
       <c r="P48" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="Q48" t="s">
         <v>981</v>
@@ -20116,7 +20113,7 @@
         <v>1433</v>
       </c>
       <c r="P49" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="Q49" t="s">
         <v>981</v>
@@ -20169,7 +20166,7 @@
         <v>1434</v>
       </c>
       <c r="P50" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="Q50" t="s">
         <v>981</v>
@@ -20225,7 +20222,7 @@
         <v>1436</v>
       </c>
       <c r="P51" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="Q51" t="s">
         <v>981</v>
@@ -20281,7 +20278,7 @@
         <v>1437</v>
       </c>
       <c r="P52" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="Q52" t="s">
         <v>981</v>
@@ -20337,7 +20334,7 @@
         <v>1438</v>
       </c>
       <c r="P53" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="Q53" t="s">
         <v>981</v>
@@ -20393,7 +20390,7 @@
         <v>1439</v>
       </c>
       <c r="P54" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="Q54" t="s">
         <v>981</v>
@@ -20449,7 +20446,7 @@
         <v>1440</v>
       </c>
       <c r="P55" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="Q55" t="s">
         <v>981</v>
@@ -20505,7 +20502,7 @@
         <v>1441</v>
       </c>
       <c r="P56" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="Q56" t="s">
         <v>981</v>
@@ -20561,7 +20558,7 @@
         <v>1442</v>
       </c>
       <c r="P57" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="Q57" t="s">
         <v>981</v>
@@ -20617,7 +20614,7 @@
         <v>1443</v>
       </c>
       <c r="P58" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="Q58" t="s">
         <v>981</v>
@@ -20673,7 +20670,7 @@
         <v>1444</v>
       </c>
       <c r="P59" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="Q59" t="s">
         <v>981</v>
@@ -20729,7 +20726,7 @@
         <v>1445</v>
       </c>
       <c r="P60" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="Q60" t="s">
         <v>981</v>
@@ -20785,7 +20782,7 @@
         <v>1446</v>
       </c>
       <c r="P61" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="Q61" t="s">
         <v>981</v>
@@ -20841,7 +20838,7 @@
         <v>1447</v>
       </c>
       <c r="P62" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="Q62" t="s">
         <v>981</v>
@@ -20897,7 +20894,7 @@
         <v>1449</v>
       </c>
       <c r="P63" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="Q63" t="s">
         <v>981</v>
@@ -20953,7 +20950,7 @@
         <v>1450</v>
       </c>
       <c r="P64" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="Q64" t="s">
         <v>981</v>
@@ -21009,7 +21006,7 @@
         <v>1453</v>
       </c>
       <c r="P65" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="Q65" t="s">
         <v>981</v>
@@ -21065,7 +21062,7 @@
         <v>1455</v>
       </c>
       <c r="P66" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="Q66" t="s">
         <v>981</v>
@@ -21121,7 +21118,7 @@
         <v>1457</v>
       </c>
       <c r="P67" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="Q67" t="s">
         <v>981</v>
@@ -21177,7 +21174,7 @@
         <v>1459</v>
       </c>
       <c r="P68" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="Q68" t="s">
         <v>981</v>
@@ -21233,7 +21230,7 @@
         <v>1461</v>
       </c>
       <c r="P69" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="Q69" t="s">
         <v>981</v>
@@ -21289,7 +21286,7 @@
         <v>1462</v>
       </c>
       <c r="P70" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="Q70" t="s">
         <v>981</v>
@@ -21345,7 +21342,7 @@
         <v>1463</v>
       </c>
       <c r="P71" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="Q71" t="s">
         <v>981</v>
@@ -21401,7 +21398,7 @@
         <v>1464</v>
       </c>
       <c r="P72" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="Q72" t="s">
         <v>981</v>
@@ -21457,7 +21454,7 @@
         <v>1465</v>
       </c>
       <c r="P73" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="Q73" t="s">
         <v>981</v>
@@ -21513,7 +21510,7 @@
         <v>1467</v>
       </c>
       <c r="P74" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="Q74" t="s">
         <v>981</v>
@@ -21569,7 +21566,7 @@
         <v>1468</v>
       </c>
       <c r="P75" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="Q75" t="s">
         <v>981</v>
@@ -21625,7 +21622,7 @@
         <v>1469</v>
       </c>
       <c r="P76" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="Q76" t="s">
         <v>981</v>
@@ -21681,7 +21678,7 @@
         <v>1470</v>
       </c>
       <c r="P77" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="Q77" t="s">
         <v>981</v>
@@ -21737,7 +21734,7 @@
         <v>1471</v>
       </c>
       <c r="P78" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="Q78" t="s">
         <v>981</v>
@@ -21793,7 +21790,7 @@
         <v>1472</v>
       </c>
       <c r="P79" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="Q79" t="s">
         <v>981</v>
@@ -21849,7 +21846,7 @@
         <v>1473</v>
       </c>
       <c r="P80" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="Q80" t="s">
         <v>981</v>
@@ -21905,7 +21902,7 @@
         <v>1474</v>
       </c>
       <c r="P81" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="Q81" t="s">
         <v>981</v>
@@ -21961,7 +21958,7 @@
         <v>1475</v>
       </c>
       <c r="P82" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="Q82" t="s">
         <v>981</v>
@@ -22017,7 +22014,7 @@
         <v>1476</v>
       </c>
       <c r="P83" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="Q83" t="s">
         <v>981</v>
@@ -22073,7 +22070,7 @@
         <v>1477</v>
       </c>
       <c r="P84" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="Q84" t="s">
         <v>981</v>
@@ -22129,7 +22126,7 @@
         <v>1479</v>
       </c>
       <c r="P85" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="Q85" t="s">
         <v>981</v>
@@ -22185,7 +22182,7 @@
         <v>1481</v>
       </c>
       <c r="P86" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="Q86" t="s">
         <v>981</v>
@@ -22241,7 +22238,7 @@
         <v>1482</v>
       </c>
       <c r="P87" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="Q87" t="s">
         <v>981</v>
@@ -22297,7 +22294,7 @@
         <v>1483</v>
       </c>
       <c r="P88" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="Q88" t="s">
         <v>981</v>
@@ -22353,7 +22350,7 @@
         <v>1484</v>
       </c>
       <c r="P89" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="Q89" t="s">
         <v>981</v>
@@ -22409,7 +22406,7 @@
         <v>1485</v>
       </c>
       <c r="P90" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="Q90" t="s">
         <v>981</v>
@@ -22465,7 +22462,7 @@
         <v>1486</v>
       </c>
       <c r="P91" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="Q91" t="s">
         <v>981</v>
@@ -22521,7 +22518,7 @@
         <v>1487</v>
       </c>
       <c r="P92" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="Q92" t="s">
         <v>981</v>
@@ -22577,7 +22574,7 @@
         <v>1488</v>
       </c>
       <c r="P93" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="Q93" t="s">
         <v>981</v>
@@ -22633,7 +22630,7 @@
         <v>1489</v>
       </c>
       <c r="P94" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="Q94" t="s">
         <v>981</v>
@@ -22689,7 +22686,7 @@
         <v>1490</v>
       </c>
       <c r="P95" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="Q95" t="s">
         <v>981</v>
@@ -22745,7 +22742,7 @@
         <v>1491</v>
       </c>
       <c r="P96" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="Q96" t="s">
         <v>981</v>
@@ -22801,7 +22798,7 @@
         <v>1492</v>
       </c>
       <c r="P97" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="Q97" t="s">
         <v>981</v>
@@ -22857,7 +22854,7 @@
         <v>1493</v>
       </c>
       <c r="P98" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="Q98" t="s">
         <v>981</v>
@@ -22913,7 +22910,7 @@
         <v>1494</v>
       </c>
       <c r="P99" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="Q99" t="s">
         <v>981</v>
@@ -22969,7 +22966,7 @@
         <v>1495</v>
       </c>
       <c r="P100" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="Q100" t="s">
         <v>981</v>
@@ -23025,7 +23022,7 @@
         <v>1496</v>
       </c>
       <c r="P101" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="Q101" t="s">
         <v>981</v>
@@ -23081,7 +23078,7 @@
         <v>1497</v>
       </c>
       <c r="P102" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="Q102" t="s">
         <v>981</v>
@@ -23137,7 +23134,7 @@
         <v>1498</v>
       </c>
       <c r="P103" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="Q103" t="s">
         <v>981</v>
@@ -23193,7 +23190,7 @@
         <v>1499</v>
       </c>
       <c r="P104" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="Q104" t="s">
         <v>981</v>
@@ -23249,7 +23246,7 @@
         <v>1501</v>
       </c>
       <c r="P105" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="Q105" t="s">
         <v>981</v>
@@ -23305,7 +23302,7 @@
         <v>1502</v>
       </c>
       <c r="P106" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="Q106" t="s">
         <v>981</v>
@@ -23361,7 +23358,7 @@
         <v>1503</v>
       </c>
       <c r="P107" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="Q107" t="s">
         <v>981</v>
@@ -23417,7 +23414,7 @@
         <v>1504</v>
       </c>
       <c r="P108" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="Q108" t="s">
         <v>981</v>
@@ -23473,7 +23470,7 @@
         <v>1506</v>
       </c>
       <c r="P109" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="Q109" t="s">
         <v>981</v>
@@ -23529,7 +23526,7 @@
         <v>1508</v>
       </c>
       <c r="P110" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="Q110" t="s">
         <v>981</v>
@@ -23585,7 +23582,7 @@
         <v>1510</v>
       </c>
       <c r="P111" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="Q111" t="s">
         <v>981</v>
@@ -23641,7 +23638,7 @@
         <v>1511</v>
       </c>
       <c r="P112" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="Q112" t="s">
         <v>981</v>
@@ -23697,7 +23694,7 @@
         <v>1512</v>
       </c>
       <c r="P113" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="Q113" t="s">
         <v>981</v>
@@ -23753,7 +23750,7 @@
         <v>1513</v>
       </c>
       <c r="P114" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="Q114" t="s">
         <v>981</v>
@@ -23809,7 +23806,7 @@
         <v>1514</v>
       </c>
       <c r="P115" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="Q115" t="s">
         <v>981</v>
@@ -23865,7 +23862,7 @@
         <v>1515</v>
       </c>
       <c r="P116" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="Q116" t="s">
         <v>981</v>
@@ -23921,7 +23918,7 @@
         <v>1516</v>
       </c>
       <c r="P117" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="Q117" t="s">
         <v>981</v>
@@ -23974,7 +23971,7 @@
         <v>1517</v>
       </c>
       <c r="P118" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="Q118" t="s">
         <v>981</v>
@@ -24027,7 +24024,7 @@
         <v>1518</v>
       </c>
       <c r="P119" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q119" t="s">
         <v>981</v>
@@ -24080,7 +24077,7 @@
         <v>1519</v>
       </c>
       <c r="P120" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q120" t="s">
         <v>981</v>
@@ -24133,7 +24130,7 @@
         <v>1520</v>
       </c>
       <c r="P121" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q121" t="s">
         <v>981</v>
@@ -24186,7 +24183,7 @@
         <v>1521</v>
       </c>
       <c r="P122" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q122" t="s">
         <v>981</v>
@@ -24239,7 +24236,7 @@
         <v>1522</v>
       </c>
       <c r="P123" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="Q123" t="s">
         <v>981</v>
@@ -24292,7 +24289,7 @@
         <v>1523</v>
       </c>
       <c r="P124" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="Q124" t="s">
         <v>981</v>
@@ -24345,7 +24342,7 @@
         <v>1524</v>
       </c>
       <c r="P125" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="Q125" t="s">
         <v>981</v>
@@ -24398,7 +24395,7 @@
         <v>1525</v>
       </c>
       <c r="P126" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="Q126" t="s">
         <v>981</v>
@@ -24451,7 +24448,7 @@
         <v>1526</v>
       </c>
       <c r="P127" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="Q127" t="s">
         <v>981</v>
@@ -24504,7 +24501,7 @@
         <v>1527</v>
       </c>
       <c r="P128" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="Q128" t="s">
         <v>981</v>
@@ -24557,7 +24554,7 @@
         <v>1528</v>
       </c>
       <c r="P129" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="Q129" t="s">
         <v>981</v>
@@ -24610,7 +24607,7 @@
         <v>1529</v>
       </c>
       <c r="P130" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q130" t="s">
         <v>981</v>
@@ -24663,7 +24660,7 @@
         <v>1530</v>
       </c>
       <c r="P131" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q131" t="s">
         <v>981</v>
@@ -24716,7 +24713,7 @@
         <v>1531</v>
       </c>
       <c r="P132" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="Q132" t="s">
         <v>981</v>
@@ -24769,7 +24766,7 @@
         <v>1532</v>
       </c>
       <c r="P133" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="Q133" t="s">
         <v>981</v>
@@ -24822,7 +24819,7 @@
         <v>1533</v>
       </c>
       <c r="P134" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="Q134" t="s">
         <v>981</v>
@@ -24875,7 +24872,7 @@
         <v>1534</v>
       </c>
       <c r="P135" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="Q135" t="s">
         <v>981</v>
@@ -24928,7 +24925,7 @@
         <v>1535</v>
       </c>
       <c r="P136" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="Q136" t="s">
         <v>981</v>
@@ -24981,7 +24978,7 @@
         <v>1536</v>
       </c>
       <c r="P137" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="Q137" t="s">
         <v>981</v>
@@ -25034,7 +25031,7 @@
         <v>1537</v>
       </c>
       <c r="P138" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="Q138" t="s">
         <v>981</v>
@@ -25087,7 +25084,7 @@
         <v>1538</v>
       </c>
       <c r="P139" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="Q139" t="s">
         <v>981</v>
@@ -25140,7 +25137,7 @@
         <v>1539</v>
       </c>
       <c r="P140" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="Q140" t="s">
         <v>981</v>
@@ -25193,7 +25190,7 @@
         <v>1540</v>
       </c>
       <c r="P141" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="Q141" t="s">
         <v>981</v>
@@ -25246,7 +25243,7 @@
         <v>1541</v>
       </c>
       <c r="P142" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="Q142" t="s">
         <v>981</v>
@@ -25299,7 +25296,7 @@
         <v>1542</v>
       </c>
       <c r="P143" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="Q143" t="s">
         <v>981</v>
@@ -25352,7 +25349,7 @@
         <v>1543</v>
       </c>
       <c r="P144" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="Q144" t="s">
         <v>981</v>
@@ -25405,7 +25402,7 @@
         <v>1544</v>
       </c>
       <c r="P145" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="Q145" t="s">
         <v>981</v>
@@ -25458,7 +25455,7 @@
         <v>1545</v>
       </c>
       <c r="P146" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="Q146" t="s">
         <v>981</v>
@@ -25511,7 +25508,7 @@
         <v>1546</v>
       </c>
       <c r="P147" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="Q147" t="s">
         <v>981</v>
@@ -25564,7 +25561,7 @@
         <v>1547</v>
       </c>
       <c r="P148" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="Q148" t="s">
         <v>981</v>
@@ -25617,7 +25614,7 @@
         <v>1548</v>
       </c>
       <c r="P149" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="Q149" t="s">
         <v>981</v>
@@ -25670,7 +25667,7 @@
         <v>1549</v>
       </c>
       <c r="P150" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q150" t="s">
         <v>981</v>
@@ -25723,7 +25720,7 @@
         <v>1550</v>
       </c>
       <c r="P151" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="Q151" t="s">
         <v>981</v>
@@ -25776,7 +25773,7 @@
         <v>1551</v>
       </c>
       <c r="P152" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="Q152" t="s">
         <v>981</v>
@@ -25829,7 +25826,7 @@
         <v>1552</v>
       </c>
       <c r="P153" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="Q153" t="s">
         <v>981</v>
@@ -25882,7 +25879,7 @@
         <v>1553</v>
       </c>
       <c r="P154" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="Q154" t="s">
         <v>981</v>
@@ -25935,7 +25932,7 @@
         <v>1554</v>
       </c>
       <c r="P155" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="Q155" t="s">
         <v>981</v>
@@ -25991,7 +25988,7 @@
         <v>1555</v>
       </c>
       <c r="P156" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q156" t="s">
         <v>981</v>
@@ -26047,7 +26044,7 @@
         <v>1556</v>
       </c>
       <c r="P157" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q157" t="s">
         <v>981</v>
@@ -26103,7 +26100,7 @@
         <v>1557</v>
       </c>
       <c r="P158" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q158" t="s">
         <v>981</v>
@@ -26159,7 +26156,7 @@
         <v>1558</v>
       </c>
       <c r="P159" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q159" t="s">
         <v>981</v>
@@ -26215,7 +26212,7 @@
         <v>1559</v>
       </c>
       <c r="P160" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q160" t="s">
         <v>981</v>
@@ -26271,7 +26268,7 @@
         <v>1560</v>
       </c>
       <c r="P161" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q161" t="s">
         <v>981</v>
@@ -26327,7 +26324,7 @@
         <v>1561</v>
       </c>
       <c r="P162" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q162" t="s">
         <v>981</v>
@@ -26383,7 +26380,7 @@
         <v>1562</v>
       </c>
       <c r="P163" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q163" t="s">
         <v>981</v>
@@ -26439,7 +26436,7 @@
         <v>1563</v>
       </c>
       <c r="P164" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q164" t="s">
         <v>981</v>
@@ -26495,7 +26492,7 @@
         <v>1564</v>
       </c>
       <c r="P165" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q165" t="s">
         <v>981</v>
@@ -26551,7 +26548,7 @@
         <v>1565</v>
       </c>
       <c r="P166" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q166" t="s">
         <v>981</v>
@@ -26607,7 +26604,7 @@
         <v>1566</v>
       </c>
       <c r="P167" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q167" t="s">
         <v>981</v>
@@ -26663,7 +26660,7 @@
         <v>1567</v>
       </c>
       <c r="P168" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q168" t="s">
         <v>981</v>
@@ -26719,7 +26716,7 @@
         <v>1568</v>
       </c>
       <c r="P169" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q169" t="s">
         <v>981</v>
@@ -26775,7 +26772,7 @@
         <v>1569</v>
       </c>
       <c r="P170" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q170" t="s">
         <v>981</v>
@@ -26831,7 +26828,7 @@
         <v>1570</v>
       </c>
       <c r="P171" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q171" t="s">
         <v>981</v>
@@ -26887,7 +26884,7 @@
         <v>1571</v>
       </c>
       <c r="P172" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q172" t="s">
         <v>981</v>
@@ -26943,7 +26940,7 @@
         <v>1572</v>
       </c>
       <c r="P173" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q173" t="s">
         <v>981</v>
@@ -26999,7 +26996,7 @@
         <v>1573</v>
       </c>
       <c r="P174" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q174" t="s">
         <v>981</v>
@@ -27055,7 +27052,7 @@
         <v>1574</v>
       </c>
       <c r="P175" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q175" t="s">
         <v>981</v>
@@ -27111,7 +27108,7 @@
         <v>1575</v>
       </c>
       <c r="P176" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q176" t="s">
         <v>981</v>
@@ -27167,7 +27164,7 @@
         <v>1576</v>
       </c>
       <c r="P177" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q177" t="s">
         <v>981</v>
@@ -27223,7 +27220,7 @@
         <v>1577</v>
       </c>
       <c r="P178" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q178" t="s">
         <v>981</v>
@@ -27279,7 +27276,7 @@
         <v>1578</v>
       </c>
       <c r="P179" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q179" t="s">
         <v>981</v>
@@ -27335,7 +27332,7 @@
         <v>1579</v>
       </c>
       <c r="P180" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q180" t="s">
         <v>981</v>
@@ -27391,7 +27388,7 @@
         <v>1580</v>
       </c>
       <c r="P181" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q181" t="s">
         <v>981</v>
@@ -27447,7 +27444,7 @@
         <v>1581</v>
       </c>
       <c r="P182" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q182" t="s">
         <v>981</v>
@@ -27503,7 +27500,7 @@
         <v>1582</v>
       </c>
       <c r="P183" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q183" t="s">
         <v>981</v>
@@ -27559,7 +27556,7 @@
         <v>1583</v>
       </c>
       <c r="P184" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q184" t="s">
         <v>981</v>
@@ -27615,7 +27612,7 @@
         <v>1584</v>
       </c>
       <c r="P185" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q185" t="s">
         <v>981</v>
@@ -27671,7 +27668,7 @@
         <v>1585</v>
       </c>
       <c r="P186" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q186" t="s">
         <v>981</v>
@@ -27727,7 +27724,7 @@
         <v>1586</v>
       </c>
       <c r="P187" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q187" t="s">
         <v>981</v>
@@ -27783,7 +27780,7 @@
         <v>1587</v>
       </c>
       <c r="P188" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q188" t="s">
         <v>981</v>
@@ -27839,7 +27836,7 @@
         <v>1588</v>
       </c>
       <c r="P189" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q189" t="s">
         <v>981</v>
@@ -27895,7 +27892,7 @@
         <v>1589</v>
       </c>
       <c r="P190" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q190" t="s">
         <v>981</v>
@@ -27951,7 +27948,7 @@
         <v>1590</v>
       </c>
       <c r="P191" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q191" t="s">
         <v>981</v>
@@ -28007,7 +28004,7 @@
         <v>1591</v>
       </c>
       <c r="P192" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q192" t="s">
         <v>981</v>
@@ -28063,7 +28060,7 @@
         <v>1592</v>
       </c>
       <c r="P193" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="Q193" t="s">
         <v>981</v>
@@ -28119,7 +28116,7 @@
         <v>1593</v>
       </c>
       <c r="P194" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="Q194" t="s">
         <v>981</v>
@@ -28175,7 +28172,7 @@
         <v>1594</v>
       </c>
       <c r="P195" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="Q195" t="s">
         <v>981</v>
@@ -28231,7 +28228,7 @@
         <v>1595</v>
       </c>
       <c r="P196" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="Q196" t="s">
         <v>981</v>
@@ -28287,7 +28284,7 @@
         <v>1596</v>
       </c>
       <c r="P197" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="Q197" t="s">
         <v>981</v>
@@ -28343,7 +28340,7 @@
         <v>1597</v>
       </c>
       <c r="P198" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="Q198" t="s">
         <v>981</v>
@@ -28399,7 +28396,7 @@
         <v>1598</v>
       </c>
       <c r="P199" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="Q199" t="s">
         <v>981</v>
@@ -28455,7 +28452,7 @@
         <v>1599</v>
       </c>
       <c r="P200" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="Q200" t="s">
         <v>981</v>
@@ -28511,7 +28508,7 @@
         <v>1600</v>
       </c>
       <c r="P201" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="Q201" t="s">
         <v>981</v>
@@ -28567,7 +28564,7 @@
         <v>1601</v>
       </c>
       <c r="P202" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="Q202" t="s">
         <v>981</v>
@@ -28623,7 +28620,7 @@
         <v>1602</v>
       </c>
       <c r="P203" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
       <c r="Q203" t="s">
         <v>981</v>
@@ -28679,7 +28676,7 @@
         <v>1603</v>
       </c>
       <c r="P204" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
       <c r="Q204" t="s">
         <v>981</v>
@@ -28735,7 +28732,7 @@
         <v>1604</v>
       </c>
       <c r="P205" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="Q205" t="s">
         <v>981</v>
@@ -28791,7 +28788,7 @@
         <v>1605</v>
       </c>
       <c r="P206" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="Q206" t="s">
         <v>981</v>
@@ -28847,7 +28844,7 @@
         <v>1606</v>
       </c>
       <c r="P207" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="Q207" t="s">
         <v>981</v>
@@ -28903,7 +28900,7 @@
         <v>1607</v>
       </c>
       <c r="P208" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="Q208" t="s">
         <v>981</v>
@@ -28959,7 +28956,7 @@
         <v>1608</v>
       </c>
       <c r="P209" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="Q209" t="s">
         <v>981</v>
@@ -29015,7 +29012,7 @@
         <v>1609</v>
       </c>
       <c r="P210" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="Q210" t="s">
         <v>981</v>
@@ -29071,7 +29068,7 @@
         <v>1610</v>
       </c>
       <c r="P211" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="Q211" t="s">
         <v>981</v>
@@ -29127,7 +29124,7 @@
         <v>1611</v>
       </c>
       <c r="P212" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="Q212" t="s">
         <v>981</v>
@@ -29183,7 +29180,7 @@
         <v>1612</v>
       </c>
       <c r="P213" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="Q213" t="s">
         <v>981</v>
@@ -29239,7 +29236,7 @@
         <v>1613</v>
       </c>
       <c r="P214" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="Q214" t="s">
         <v>981</v>
@@ -29295,7 +29292,7 @@
         <v>1614</v>
       </c>
       <c r="P215" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="Q215" t="s">
         <v>981</v>
@@ -29351,7 +29348,7 @@
         <v>1615</v>
       </c>
       <c r="P216" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="Q216" t="s">
         <v>981</v>
@@ -29407,7 +29404,7 @@
         <v>1616</v>
       </c>
       <c r="P217" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="Q217" t="s">
         <v>981</v>
@@ -29463,7 +29460,7 @@
         <v>1617</v>
       </c>
       <c r="P218" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="Q218" t="s">
         <v>981</v>
@@ -29519,7 +29516,7 @@
         <v>1618</v>
       </c>
       <c r="P219" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="Q219" t="s">
         <v>981</v>
@@ -29575,7 +29572,7 @@
         <v>1619</v>
       </c>
       <c r="P220" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="Q220" t="s">
         <v>981</v>
@@ -29631,7 +29628,7 @@
         <v>1620</v>
       </c>
       <c r="P221" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="Q221" t="s">
         <v>981</v>
@@ -29687,7 +29684,7 @@
         <v>1621</v>
       </c>
       <c r="P222" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="Q222" t="s">
         <v>981</v>
@@ -29743,7 +29740,7 @@
         <v>1622</v>
       </c>
       <c r="P223" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="Q223" t="s">
         <v>981</v>
@@ -29799,7 +29796,7 @@
         <v>1623</v>
       </c>
       <c r="P224" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="Q224" t="s">
         <v>981</v>
@@ -29855,7 +29852,7 @@
         <v>1624</v>
       </c>
       <c r="P225" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="Q225" t="s">
         <v>981</v>
@@ -29911,7 +29908,7 @@
         <v>1625</v>
       </c>
       <c r="P226" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="Q226" t="s">
         <v>981</v>
@@ -29967,7 +29964,7 @@
         <v>1626</v>
       </c>
       <c r="P227" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="Q227" t="s">
         <v>981</v>
@@ -30023,7 +30020,7 @@
         <v>1627</v>
       </c>
       <c r="P228" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="Q228" t="s">
         <v>981</v>
@@ -30079,7 +30076,7 @@
         <v>1628</v>
       </c>
       <c r="P229" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="Q229" t="s">
         <v>981</v>
@@ -30135,7 +30132,7 @@
         <v>1629</v>
       </c>
       <c r="P230" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="Q230" t="s">
         <v>981</v>
@@ -30191,7 +30188,7 @@
         <v>1630</v>
       </c>
       <c r="P231" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="Q231" t="s">
         <v>981</v>
@@ -30247,7 +30244,7 @@
         <v>1631</v>
       </c>
       <c r="P232" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="Q232" t="s">
         <v>981</v>
@@ -30303,7 +30300,7 @@
         <v>1633</v>
       </c>
       <c r="P233" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="Q233" t="s">
         <v>981</v>
@@ -30359,7 +30356,7 @@
         <v>1634</v>
       </c>
       <c r="P234" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="Q234" t="s">
         <v>981</v>
@@ -30415,7 +30412,7 @@
         <v>1635</v>
       </c>
       <c r="P235" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="Q235" t="s">
         <v>981</v>
@@ -30471,7 +30468,7 @@
         <v>1636</v>
       </c>
       <c r="P236" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="Q236" t="s">
         <v>981</v>
@@ -30527,7 +30524,7 @@
         <v>1637</v>
       </c>
       <c r="P237" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="Q237" t="s">
         <v>981</v>
@@ -30583,7 +30580,7 @@
         <v>1638</v>
       </c>
       <c r="P238" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="Q238" t="s">
         <v>981</v>
@@ -30639,7 +30636,7 @@
         <v>1639</v>
       </c>
       <c r="P239" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="Q239" t="s">
         <v>981</v>
@@ -30695,7 +30692,7 @@
         <v>1640</v>
       </c>
       <c r="P240" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="Q240" t="s">
         <v>981</v>
@@ -30751,7 +30748,7 @@
         <v>1641</v>
       </c>
       <c r="P241" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="Q241" t="s">
         <v>981</v>
@@ -30807,7 +30804,7 @@
         <v>1642</v>
       </c>
       <c r="P242" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="Q242" t="s">
         <v>981</v>
@@ -30863,7 +30860,7 @@
         <v>1644</v>
       </c>
       <c r="P243" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="Q243" t="s">
         <v>981</v>
@@ -30919,7 +30916,7 @@
         <v>1645</v>
       </c>
       <c r="P244" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="Q244" t="s">
         <v>981</v>
@@ -30975,7 +30972,7 @@
         <v>1646</v>
       </c>
       <c r="P245" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="Q245" t="s">
         <v>981</v>
@@ -31031,7 +31028,7 @@
         <v>1647</v>
       </c>
       <c r="P246" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="Q246" t="s">
         <v>981</v>
@@ -31087,7 +31084,7 @@
         <v>1648</v>
       </c>
       <c r="P247" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="Q247" t="s">
         <v>981</v>
@@ -31143,7 +31140,7 @@
         <v>1649</v>
       </c>
       <c r="P248" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="Q248" t="s">
         <v>981</v>
@@ -31199,7 +31196,7 @@
         <v>1650</v>
       </c>
       <c r="P249" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="Q249" t="s">
         <v>981</v>
@@ -31255,7 +31252,7 @@
         <v>1651</v>
       </c>
       <c r="P250" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="Q250" t="s">
         <v>981</v>
@@ -31311,7 +31308,7 @@
         <v>1652</v>
       </c>
       <c r="P251" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="Q251" t="s">
         <v>981</v>
@@ -31367,7 +31364,7 @@
         <v>1653</v>
       </c>
       <c r="P252" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="Q252" t="s">
         <v>981</v>
@@ -31423,7 +31420,7 @@
         <v>1654</v>
       </c>
       <c r="P253" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="Q253" t="s">
         <v>981</v>
@@ -31479,7 +31476,7 @@
         <v>1655</v>
       </c>
       <c r="P254" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="Q254" t="s">
         <v>981</v>
@@ -31535,7 +31532,7 @@
         <v>1656</v>
       </c>
       <c r="P255" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="Q255" t="s">
         <v>981</v>
@@ -31591,7 +31588,7 @@
         <v>1657</v>
       </c>
       <c r="P256" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="Q256" t="s">
         <v>981</v>
@@ -31647,7 +31644,7 @@
         <v>1658</v>
       </c>
       <c r="P257" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="Q257" t="s">
         <v>981</v>
@@ -31703,7 +31700,7 @@
         <v>1659</v>
       </c>
       <c r="P258" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="Q258" t="s">
         <v>981</v>
@@ -31759,7 +31756,7 @@
         <v>1660</v>
       </c>
       <c r="P259" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="Q259" t="s">
         <v>981</v>
@@ -31815,7 +31812,7 @@
         <v>1661</v>
       </c>
       <c r="P260" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q260" t="s">
         <v>981</v>
@@ -31871,7 +31868,7 @@
         <v>1662</v>
       </c>
       <c r="P261" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q261" t="s">
         <v>981</v>
@@ -31927,7 +31924,7 @@
         <v>1663</v>
       </c>
       <c r="P262" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q262" t="s">
         <v>981</v>
@@ -31956,19 +31953,19 @@
         <v>2025</v>
       </c>
       <c r="F263">
-        <v>0.30159999999999998</v>
+        <v>0.43179999999999996</v>
       </c>
       <c r="G263">
         <v>1</v>
       </c>
       <c r="H263">
-        <v>1836.0000000000002</v>
+        <v>1836.0000000000007</v>
       </c>
       <c r="I263">
-        <v>46.800000000000004</v>
+        <v>46.800000000000011</v>
       </c>
       <c r="J263">
-        <v>2.16</v>
+        <v>2.1600000000000006</v>
       </c>
       <c r="K263">
         <v>30</v>
@@ -31983,7 +31980,7 @@
         <v>1664</v>
       </c>
       <c r="P263" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q263" t="s">
         <v>981</v>
@@ -32039,7 +32036,7 @@
         <v>1665</v>
       </c>
       <c r="P264" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q264" t="s">
         <v>981</v>
@@ -32095,7 +32092,7 @@
         <v>1666</v>
       </c>
       <c r="P265" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q265" t="s">
         <v>981</v>
@@ -32151,7 +32148,7 @@
         <v>1667</v>
       </c>
       <c r="P266" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q266" t="s">
         <v>981</v>
@@ -32207,7 +32204,7 @@
         <v>1668</v>
       </c>
       <c r="P267" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q267" t="s">
         <v>981</v>
@@ -32263,7 +32260,7 @@
         <v>1670</v>
       </c>
       <c r="P268" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q268" t="s">
         <v>981</v>
@@ -32319,7 +32316,7 @@
         <v>1671</v>
       </c>
       <c r="P269" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q269" t="s">
         <v>981</v>
@@ -32375,7 +32372,7 @@
         <v>1672</v>
       </c>
       <c r="P270" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q270" t="s">
         <v>981</v>
@@ -32431,7 +32428,7 @@
         <v>1673</v>
       </c>
       <c r="P271" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="Q271" t="s">
         <v>981</v>
@@ -32487,7 +32484,7 @@
         <v>1674</v>
       </c>
       <c r="P272" t="s">
-        <v>1792</v>
+        <v>1889</v>
       </c>
       <c r="Q272" t="s">
         <v>981</v>
@@ -32499,7 +32496,7 @@
         <v>1380</v>
       </c>
       <c r="T272" t="s">
-        <v>984</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="273" spans="2:20" x14ac:dyDescent="0.45">
@@ -32566,31 +32563,31 @@
         <v>928</v>
       </c>
       <c r="D274" t="s">
-        <v>748</v>
+        <v>946</v>
       </c>
       <c r="E274">
         <v>2025</v>
       </c>
       <c r="F274">
-        <v>0.13019999999999998</v>
+        <v>0.8</v>
       </c>
       <c r="G274">
         <v>1</v>
       </c>
       <c r="H274">
-        <v>1836</v>
+        <v>1360</v>
       </c>
       <c r="I274">
-        <v>46.800000000000011</v>
+        <v>36</v>
       </c>
       <c r="J274">
-        <v>2.16</v>
+        <v>1.8</v>
       </c>
       <c r="K274">
         <v>30</v>
       </c>
       <c r="L274">
-        <v>0.301118298078066</v>
+        <v>0.1753554352256321</v>
       </c>
       <c r="N274" t="s">
         <v>979</v>
@@ -32628,19 +32625,19 @@
         <v>2025</v>
       </c>
       <c r="F275">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="G275">
         <v>1</v>
       </c>
       <c r="H275">
-        <v>1360</v>
+        <v>1563.9999999999998</v>
       </c>
       <c r="I275">
-        <v>36</v>
+        <v>39.6</v>
       </c>
       <c r="J275">
-        <v>1.8</v>
+        <v>1.9800000000000004</v>
       </c>
       <c r="K275">
         <v>30</v>
@@ -32684,7 +32681,7 @@
         <v>2025</v>
       </c>
       <c r="F276">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G276">
         <v>1</v>
@@ -32696,7 +32693,7 @@
         <v>39.6</v>
       </c>
       <c r="J276">
-        <v>1.9800000000000004</v>
+        <v>1.9800000000000002</v>
       </c>
       <c r="K276">
         <v>30</v>
@@ -32734,31 +32731,31 @@
         <v>928</v>
       </c>
       <c r="D277" t="s">
-        <v>946</v>
+        <v>957</v>
       </c>
       <c r="E277">
         <v>2025</v>
       </c>
       <c r="F277">
-        <v>0.2</v>
+        <v>0.76</v>
       </c>
       <c r="G277">
         <v>1</v>
       </c>
       <c r="H277">
-        <v>1563.9999999999998</v>
+        <v>1360</v>
       </c>
       <c r="I277">
-        <v>39.6</v>
+        <v>36</v>
       </c>
       <c r="J277">
-        <v>1.9800000000000002</v>
+        <v>1.8</v>
       </c>
       <c r="K277">
         <v>30</v>
       </c>
       <c r="L277">
-        <v>0.1753554352256321</v>
+        <v>0.2346271116098167</v>
       </c>
       <c r="N277" t="s">
         <v>979</v>
@@ -32790,13 +32787,13 @@
         <v>928</v>
       </c>
       <c r="D278" t="s">
-        <v>957</v>
+        <v>946</v>
       </c>
       <c r="E278">
         <v>2025</v>
       </c>
       <c r="F278">
-        <v>0.76</v>
+        <v>0.5</v>
       </c>
       <c r="G278">
         <v>1</v>
@@ -32814,7 +32811,7 @@
         <v>30</v>
       </c>
       <c r="L278">
-        <v>0.2346271116098167</v>
+        <v>0.1753554352256321</v>
       </c>
       <c r="N278" t="s">
         <v>979</v>
@@ -32852,7 +32849,7 @@
         <v>2025</v>
       </c>
       <c r="F279">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G279">
         <v>1</v>
@@ -32902,13 +32899,13 @@
         <v>928</v>
       </c>
       <c r="D280" t="s">
-        <v>946</v>
+        <v>931</v>
       </c>
       <c r="E280">
         <v>2025</v>
       </c>
       <c r="F280">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="G280">
         <v>1</v>
@@ -32926,7 +32923,7 @@
         <v>30</v>
       </c>
       <c r="L280">
-        <v>0.1753554352256321</v>
+        <v>0.4126741487712175</v>
       </c>
       <c r="N280" t="s">
         <v>979</v>
@@ -32964,19 +32961,19 @@
         <v>2025</v>
       </c>
       <c r="F281">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="G281">
         <v>1</v>
       </c>
       <c r="H281">
-        <v>1360</v>
+        <v>1563.9999999999998</v>
       </c>
       <c r="I281">
-        <v>36</v>
+        <v>39.6</v>
       </c>
       <c r="J281">
-        <v>1.8</v>
+        <v>1.9800000000000002</v>
       </c>
       <c r="K281">
         <v>30</v>
@@ -33014,31 +33011,31 @@
         <v>928</v>
       </c>
       <c r="D282" t="s">
-        <v>931</v>
+        <v>961</v>
       </c>
       <c r="E282">
         <v>2025</v>
       </c>
       <c r="F282">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="G282">
         <v>1</v>
       </c>
       <c r="H282">
-        <v>1563.9999999999998</v>
+        <v>1360</v>
       </c>
       <c r="I282">
-        <v>39.6</v>
+        <v>36</v>
       </c>
       <c r="J282">
-        <v>1.9800000000000002</v>
+        <v>1.8</v>
       </c>
       <c r="K282">
         <v>30</v>
       </c>
       <c r="L282">
-        <v>0.4126741487712175</v>
+        <v>0.2822979932934005</v>
       </c>
       <c r="N282" t="s">
         <v>979</v>
@@ -33070,7 +33067,7 @@
         <v>928</v>
       </c>
       <c r="D283" t="s">
-        <v>961</v>
+        <v>931</v>
       </c>
       <c r="E283">
         <v>2025</v>
@@ -33094,7 +33091,7 @@
         <v>30</v>
       </c>
       <c r="L283">
-        <v>0.2822979932934005</v>
+        <v>0.4126741487712175</v>
       </c>
       <c r="N283" t="s">
         <v>979</v>
@@ -33132,19 +33129,19 @@
         <v>2025</v>
       </c>
       <c r="F284">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G284">
         <v>1</v>
       </c>
       <c r="H284">
-        <v>1360</v>
+        <v>1563.9999999999998</v>
       </c>
       <c r="I284">
-        <v>36</v>
+        <v>39.6</v>
       </c>
       <c r="J284">
-        <v>1.8</v>
+        <v>1.9800000000000002</v>
       </c>
       <c r="K284">
         <v>30</v>
@@ -33182,31 +33179,31 @@
         <v>928</v>
       </c>
       <c r="D285" t="s">
-        <v>931</v>
+        <v>957</v>
       </c>
       <c r="E285">
         <v>2025</v>
       </c>
       <c r="F285">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="G285">
         <v>1</v>
       </c>
       <c r="H285">
-        <v>1563.9999999999998</v>
+        <v>1360</v>
       </c>
       <c r="I285">
-        <v>39.6</v>
+        <v>36</v>
       </c>
       <c r="J285">
-        <v>1.9800000000000002</v>
+        <v>1.8</v>
       </c>
       <c r="K285">
         <v>30</v>
       </c>
       <c r="L285">
-        <v>0.4126741487712175</v>
+        <v>0.2346271116098167</v>
       </c>
       <c r="N285" t="s">
         <v>979</v>
@@ -33238,13 +33235,13 @@
         <v>928</v>
       </c>
       <c r="D286" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="E286">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F286">
-        <v>0.45</v>
+        <v>0.45600000000000002</v>
       </c>
       <c r="G286">
         <v>1</v>
@@ -33259,10 +33256,10 @@
         <v>1.8</v>
       </c>
       <c r="K286">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L286">
-        <v>0.2346271116098167</v>
+        <v>0.2822979932934005</v>
       </c>
       <c r="N286" t="s">
         <v>979</v>
@@ -33294,13 +33291,13 @@
         <v>928</v>
       </c>
       <c r="D287" t="s">
-        <v>961</v>
+        <v>929</v>
       </c>
       <c r="E287">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F287">
-        <v>0.45600000000000002</v>
+        <v>0.47099999999999997</v>
       </c>
       <c r="G287">
         <v>1</v>
@@ -33315,10 +33312,10 @@
         <v>1.8</v>
       </c>
       <c r="K287">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L287">
-        <v>0.2822979932934005</v>
+        <v>0.308797255699787</v>
       </c>
       <c r="N287" t="s">
         <v>979</v>
@@ -33350,13 +33347,13 @@
         <v>928</v>
       </c>
       <c r="D288" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="E288">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F288">
-        <v>0.47099999999999997</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="G288">
         <v>1</v>
@@ -33371,10 +33368,10 @@
         <v>1.8</v>
       </c>
       <c r="K288">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L288">
-        <v>0.308797255699787</v>
+        <v>0.34785235138275827</v>
       </c>
       <c r="N288" t="s">
         <v>979</v>
@@ -33462,37 +33459,37 @@
         <v>928</v>
       </c>
       <c r="D290" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="E290">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F290">
-        <v>0.42499999999999999</v>
+        <v>0.23100000000000001</v>
       </c>
       <c r="G290">
         <v>1</v>
       </c>
       <c r="H290">
-        <v>1360</v>
+        <v>1563.9999999999998</v>
       </c>
       <c r="I290">
-        <v>36</v>
+        <v>39.6</v>
       </c>
       <c r="J290">
-        <v>1.8</v>
+        <v>1.9800000000000002</v>
       </c>
       <c r="K290">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L290">
-        <v>0.34785235138275827</v>
+        <v>0.41267414877121755</v>
       </c>
       <c r="N290" t="s">
         <v>979</v>
       </c>
       <c r="O290" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="P290" t="s">
         <v>1907</v>
@@ -33518,31 +33515,31 @@
         <v>928</v>
       </c>
       <c r="D291" t="s">
-        <v>931</v>
+        <v>1692</v>
       </c>
       <c r="E291">
         <v>2025</v>
       </c>
       <c r="F291">
-        <v>0.23100000000000001</v>
+        <v>0.55400000000000005</v>
       </c>
       <c r="G291">
         <v>1</v>
       </c>
       <c r="H291">
-        <v>1563.9999999999998</v>
+        <v>1360</v>
       </c>
       <c r="I291">
-        <v>39.6</v>
+        <v>36</v>
       </c>
       <c r="J291">
-        <v>1.9800000000000002</v>
+        <v>1.8</v>
       </c>
       <c r="K291">
         <v>30</v>
       </c>
       <c r="L291">
-        <v>0.41267414877121755</v>
+        <v>0.2685515567592453</v>
       </c>
       <c r="N291" t="s">
         <v>979</v>
@@ -33568,13 +33565,13 @@
     </row>
     <row r="292" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B292" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="C292" t="s">
         <v>928</v>
       </c>
       <c r="D292" t="s">
-        <v>1693</v>
+        <v>933</v>
       </c>
       <c r="E292">
         <v>2025</v>
@@ -33598,7 +33595,7 @@
         <v>30</v>
       </c>
       <c r="L292">
-        <v>0.2685515567592453</v>
+        <v>0.34785235138275827</v>
       </c>
       <c r="N292" t="s">
         <v>979</v>
@@ -33616,10 +33613,10 @@
         <v>982</v>
       </c>
       <c r="S292" t="s">
-        <v>1380</v>
+        <v>983</v>
       </c>
       <c r="T292" t="s">
-        <v>1006</v>
+        <v>984</v>
       </c>
     </row>
     <row r="293" spans="2:20" x14ac:dyDescent="0.45">
@@ -33630,13 +33627,13 @@
         <v>928</v>
       </c>
       <c r="D293" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="E293">
         <v>2025</v>
       </c>
       <c r="F293">
-        <v>0.55400000000000005</v>
+        <v>0.75600000000000001</v>
       </c>
       <c r="G293">
         <v>1</v>
@@ -33654,7 +33651,7 @@
         <v>30</v>
       </c>
       <c r="L293">
-        <v>0.34785235138275827</v>
+        <v>0.4126741487712175</v>
       </c>
       <c r="N293" t="s">
         <v>979</v>
@@ -33675,7 +33672,7 @@
         <v>983</v>
       </c>
       <c r="T293" t="s">
-        <v>984</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="294" spans="2:20" x14ac:dyDescent="0.45">
@@ -33683,34 +33680,31 @@
         <v>1695</v>
       </c>
       <c r="C294" t="s">
-        <v>928</v>
+        <v>478</v>
       </c>
       <c r="D294" t="s">
-        <v>931</v>
+        <v>356</v>
       </c>
       <c r="E294">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="F294">
-        <v>0.75600000000000001</v>
+        <v>6.4000000000000001E-2</v>
       </c>
       <c r="G294">
         <v>1</v>
       </c>
       <c r="H294">
-        <v>1360</v>
+        <v>2150.5</v>
       </c>
       <c r="I294">
-        <v>36</v>
+        <v>54.45000000000001</v>
       </c>
       <c r="J294">
-        <v>1.8</v>
+        <v>2.4750000000000001</v>
       </c>
       <c r="K294">
-        <v>30</v>
-      </c>
-      <c r="L294">
-        <v>0.4126741487712175</v>
+        <v>100</v>
       </c>
       <c r="N294" t="s">
         <v>979</v>
@@ -33742,13 +33736,13 @@
         <v>478</v>
       </c>
       <c r="D295" t="s">
-        <v>356</v>
+        <v>621</v>
       </c>
       <c r="E295">
         <v>2028</v>
       </c>
       <c r="F295">
-        <v>6.4000000000000001E-2</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G295">
         <v>1</v>
@@ -33764,27 +33758,6 @@
       </c>
       <c r="K295">
         <v>100</v>
-      </c>
-      <c r="N295" t="s">
-        <v>979</v>
-      </c>
-      <c r="O295" t="s">
-        <v>1698</v>
-      </c>
-      <c r="P295" t="s">
-        <v>1912</v>
-      </c>
-      <c r="Q295" t="s">
-        <v>981</v>
-      </c>
-      <c r="R295" t="s">
-        <v>982</v>
-      </c>
-      <c r="S295" t="s">
-        <v>983</v>
-      </c>
-      <c r="T295" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="296" spans="2:20" x14ac:dyDescent="0.45">
@@ -33795,59 +33768,27 @@
         <v>478</v>
       </c>
       <c r="D296" t="s">
-        <v>621</v>
+        <v>37</v>
       </c>
       <c r="E296">
         <v>2028</v>
       </c>
       <c r="F296">
-        <v>0.14000000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="G296">
         <v>1</v>
       </c>
       <c r="H296">
-        <v>2150.5</v>
+        <v>1870</v>
       </c>
       <c r="I296">
-        <v>54.45000000000001</v>
+        <v>49.5</v>
       </c>
       <c r="J296">
-        <v>2.4750000000000001</v>
+        <v>2.25</v>
       </c>
       <c r="K296">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="297" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B297" t="s">
-        <v>1698</v>
-      </c>
-      <c r="C297" t="s">
-        <v>478</v>
-      </c>
-      <c r="D297" t="s">
-        <v>37</v>
-      </c>
-      <c r="E297">
-        <v>2028</v>
-      </c>
-      <c r="F297">
-        <v>0.32</v>
-      </c>
-      <c r="G297">
-        <v>1</v>
-      </c>
-      <c r="H297">
-        <v>1870</v>
-      </c>
-      <c r="I297">
-        <v>49.5</v>
-      </c>
-      <c r="J297">
-        <v>2.25</v>
-      </c>
-      <c r="K297">
         <v>100</v>
       </c>
     </row>
@@ -33857,7 +33798,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEA4DC7F-37AA-4617-AA48-F8E219C6528C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAC46F51-1BAD-438B-A0C8-F135D9782F06}">
   <dimension ref="B9:T1097"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -34652,7 +34593,7 @@
         <v>36</v>
       </c>
       <c r="P24" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="Q24" t="s">
         <v>981</v>
@@ -34705,7 +34646,7 @@
         <v>36</v>
       </c>
       <c r="P25" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="Q25" t="s">
         <v>981</v>
@@ -44934,7 +44875,7 @@
         <v>289</v>
       </c>
       <c r="P218" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="Q218" t="s">
         <v>981</v>
@@ -44987,7 +44928,7 @@
         <v>289</v>
       </c>
       <c r="P219" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="Q219" t="s">
         <v>981</v>
@@ -45570,7 +45511,7 @@
         <v>303</v>
       </c>
       <c r="P230" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="Q230" t="s">
         <v>981</v>
@@ -45623,7 +45564,7 @@
         <v>303</v>
       </c>
       <c r="P231" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="Q231" t="s">
         <v>981</v>
@@ -65133,7 +65074,7 @@
         <v>827</v>
       </c>
       <c r="P617" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="Q617" t="s">
         <v>981</v>
@@ -65186,7 +65127,7 @@
         <v>827</v>
       </c>
       <c r="P618" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="Q618" t="s">
         <v>981</v>
@@ -67695,7 +67636,7 @@
         <v>907</v>
       </c>
       <c r="P665" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="Q665" t="s">
         <v>981</v>
@@ -67751,7 +67692,7 @@
         <v>907</v>
       </c>
       <c r="P666" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="Q666" t="s">
         <v>981</v>
@@ -68031,7 +67972,7 @@
         <v>917</v>
       </c>
       <c r="P671" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="Q671" t="s">
         <v>981</v>
@@ -68087,7 +68028,7 @@
         <v>917</v>
       </c>
       <c r="P672" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="Q672" t="s">
         <v>981</v>
@@ -76502,7 +76443,7 @@
         <v>2025</v>
       </c>
       <c r="F891">
-        <v>0.57679999999999998</v>
+        <v>0.28860000000000002</v>
       </c>
       <c r="G891">
         <v>1</v>
@@ -76511,7 +76452,7 @@
         <v>1032.75</v>
       </c>
       <c r="I891">
-        <v>17.550000000000004</v>
+        <v>17.55</v>
       </c>
       <c r="J891">
         <v>0</v>
@@ -76520,7 +76461,7 @@
         <v>30</v>
       </c>
       <c r="L891">
-        <v>0.22305009092480443</v>
+        <v>0.22305009092480438</v>
       </c>
     </row>
     <row r="892" spans="2:12" x14ac:dyDescent="0.45">
@@ -76537,7 +76478,7 @@
         <v>2025</v>
       </c>
       <c r="F892">
-        <v>0.28860000000000002</v>
+        <v>0.57679999999999998</v>
       </c>
       <c r="G892">
         <v>1</v>
@@ -76546,7 +76487,7 @@
         <v>1032.75</v>
       </c>
       <c r="I892">
-        <v>17.55</v>
+        <v>17.550000000000004</v>
       </c>
       <c r="J892">
         <v>0</v>
@@ -76555,7 +76496,7 @@
         <v>30</v>
       </c>
       <c r="L892">
-        <v>0.22305009092480438</v>
+        <v>0.22305009092480443</v>
       </c>
     </row>
     <row r="893" spans="2:12" x14ac:dyDescent="0.45">
@@ -79763,7 +79704,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L984">
-        <v>0.301118298078066</v>
+        <v>0.30111829807806606</v>
       </c>
     </row>
     <row r="985" spans="2:12" x14ac:dyDescent="0.45">
@@ -79786,7 +79727,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L985">
-        <v>0.301118298078066</v>
+        <v>0.30111829807806606</v>
       </c>
     </row>
     <row r="986" spans="2:12" x14ac:dyDescent="0.45">
@@ -79809,7 +79750,7 @@
         <v>0.33123000000000008</v>
       </c>
       <c r="L986">
-        <v>0.301118298078066</v>
+        <v>0.30111829807806606</v>
       </c>
     </row>
     <row r="987" spans="2:12" x14ac:dyDescent="0.45">
@@ -81926,19 +81867,19 @@
         <v>2025</v>
       </c>
       <c r="F1047">
-        <v>2.2800000000000001E-2</v>
+        <v>5.1299999999999998E-2</v>
       </c>
       <c r="G1047">
         <v>1</v>
       </c>
       <c r="H1047">
-        <v>1836</v>
+        <v>1563.9999999999998</v>
       </c>
       <c r="I1047">
-        <v>46.800000000000004</v>
+        <v>39.6</v>
       </c>
       <c r="J1047">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="K1047">
         <v>30</v>
@@ -81961,19 +81902,19 @@
         <v>2025</v>
       </c>
       <c r="F1048">
-        <v>5.1299999999999998E-2</v>
+        <v>2.2800000000000001E-2</v>
       </c>
       <c r="G1048">
         <v>1</v>
       </c>
       <c r="H1048">
-        <v>1563.9999999999998</v>
+        <v>1836</v>
       </c>
       <c r="I1048">
-        <v>39.6</v>
+        <v>46.800000000000004</v>
       </c>
       <c r="J1048">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="K1048">
         <v>30</v>
@@ -83703,7 +83644,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{939AF961-31CC-4836-8CB5-1C0D24D32ED3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F624056-50CE-44E8-A8BF-1786D37BEF1E}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_BRA_grids/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA_grids/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4FB13706-99F2-4DCB-A3CA-9BFC95AA15A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{80CE44EA-CD53-4477-B02B-DC2260B86F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{80DEA6E1-89D8-4BD7-81BE-295FBB59E2FC}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B8758C4B-E8BA-4294-BF73-F87EEE908E64}"/>
   </bookViews>
   <sheets>
     <sheet name="additional_hydro_pot" sheetId="5" r:id="rId1"/>
@@ -7340,7 +7340,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32204DE5-2072-4790-A826-CBA73B2258C4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB4CFC47-B2F3-46B8-AE81-28C269295CAF}">
   <dimension ref="B9:O18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7727,7 +7727,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC7BDC3-029F-44B2-B0BF-52C1AEC4E1DB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0B78F4F-0F51-4B75-811D-2DDB9025A5D6}">
   <dimension ref="B9:T192"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17993,7 +17993,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38952182-ED34-4AB4-AB94-4251EF87A23F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB2F403B-1267-4719-A2A2-3935C690C91D}">
   <dimension ref="B9:T296"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -33798,7 +33798,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAC46F51-1BAD-438B-A0C8-F135D9782F06}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78D3FAB4-5F16-4A2F-8941-7156FD481FC8}">
   <dimension ref="B9:T1097"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -35017,7 +35017,7 @@
         <v>47</v>
       </c>
       <c r="P32" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="Q32" t="s">
         <v>981</v>
@@ -35070,7 +35070,7 @@
         <v>47</v>
       </c>
       <c r="P33" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="Q33" t="s">
         <v>981</v>
@@ -44875,7 +44875,7 @@
         <v>289</v>
       </c>
       <c r="P218" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="Q218" t="s">
         <v>981</v>
@@ -44928,7 +44928,7 @@
         <v>289</v>
       </c>
       <c r="P219" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="Q219" t="s">
         <v>981</v>
@@ -45511,7 +45511,7 @@
         <v>303</v>
       </c>
       <c r="P230" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="Q230" t="s">
         <v>981</v>
@@ -45564,7 +45564,7 @@
         <v>303</v>
       </c>
       <c r="P231" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="Q231" t="s">
         <v>981</v>
@@ -65710,7 +65710,7 @@
         <v>849</v>
       </c>
       <c r="P629" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="Q629" t="s">
         <v>981</v>
@@ -65763,7 +65763,7 @@
         <v>849</v>
       </c>
       <c r="P630" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="Q630" t="s">
         <v>981</v>
@@ -65869,7 +65869,7 @@
         <v>853</v>
       </c>
       <c r="P632" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="Q632" t="s">
         <v>981</v>
@@ -65922,7 +65922,7 @@
         <v>853</v>
       </c>
       <c r="P633" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="Q633" t="s">
         <v>981</v>
@@ -66708,7 +66708,7 @@
         <v>883</v>
       </c>
       <c r="P648" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="Q648" t="s">
         <v>981</v>
@@ -66752,7 +66752,7 @@
         <v>883</v>
       </c>
       <c r="P649" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="Q649" t="s">
         <v>981</v>
@@ -67300,7 +67300,7 @@
         <v>900</v>
       </c>
       <c r="P659" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="Q659" t="s">
         <v>981</v>
@@ -67356,7 +67356,7 @@
         <v>900</v>
       </c>
       <c r="P660" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="Q660" t="s">
         <v>981</v>
@@ -67412,7 +67412,7 @@
         <v>901</v>
       </c>
       <c r="P661" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="Q661" t="s">
         <v>981</v>
@@ -67468,7 +67468,7 @@
         <v>901</v>
       </c>
       <c r="P662" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="Q662" t="s">
         <v>981</v>
@@ -67636,7 +67636,7 @@
         <v>907</v>
       </c>
       <c r="P665" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="Q665" t="s">
         <v>981</v>
@@ -67692,7 +67692,7 @@
         <v>907</v>
       </c>
       <c r="P666" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="Q666" t="s">
         <v>981</v>
@@ -67972,7 +67972,7 @@
         <v>917</v>
       </c>
       <c r="P671" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="Q671" t="s">
         <v>981</v>
@@ -68028,7 +68028,7 @@
         <v>917</v>
       </c>
       <c r="P672" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="Q672" t="s">
         <v>981</v>
@@ -69092,7 +69092,7 @@
         <v>949</v>
       </c>
       <c r="P691" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="Q691" t="s">
         <v>981</v>
@@ -69148,7 +69148,7 @@
         <v>949</v>
       </c>
       <c r="P692" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="Q692" t="s">
         <v>981</v>
@@ -69484,7 +69484,7 @@
         <v>960</v>
       </c>
       <c r="P698" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="Q698" t="s">
         <v>981</v>
@@ -69540,7 +69540,7 @@
         <v>960</v>
       </c>
       <c r="P699" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="Q699" t="s">
         <v>981</v>
@@ -76443,7 +76443,7 @@
         <v>2025</v>
       </c>
       <c r="F891">
-        <v>0.28860000000000002</v>
+        <v>0.57679999999999998</v>
       </c>
       <c r="G891">
         <v>1</v>
@@ -76452,7 +76452,7 @@
         <v>1032.75</v>
       </c>
       <c r="I891">
-        <v>17.55</v>
+        <v>17.550000000000004</v>
       </c>
       <c r="J891">
         <v>0</v>
@@ -76461,7 +76461,7 @@
         <v>30</v>
       </c>
       <c r="L891">
-        <v>0.22305009092480438</v>
+        <v>0.22305009092480443</v>
       </c>
     </row>
     <row r="892" spans="2:12" x14ac:dyDescent="0.45">
@@ -76478,7 +76478,7 @@
         <v>2025</v>
       </c>
       <c r="F892">
-        <v>0.57679999999999998</v>
+        <v>0.28860000000000002</v>
       </c>
       <c r="G892">
         <v>1</v>
@@ -76487,7 +76487,7 @@
         <v>1032.75</v>
       </c>
       <c r="I892">
-        <v>17.550000000000004</v>
+        <v>17.55</v>
       </c>
       <c r="J892">
         <v>0</v>
@@ -76496,7 +76496,7 @@
         <v>30</v>
       </c>
       <c r="L892">
-        <v>0.22305009092480443</v>
+        <v>0.22305009092480438</v>
       </c>
     </row>
     <row r="893" spans="2:12" x14ac:dyDescent="0.45">
@@ -79704,7 +79704,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L984">
-        <v>0.30111829807806606</v>
+        <v>0.301118298078066</v>
       </c>
     </row>
     <row r="985" spans="2:12" x14ac:dyDescent="0.45">
@@ -79727,7 +79727,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L985">
-        <v>0.30111829807806606</v>
+        <v>0.301118298078066</v>
       </c>
     </row>
     <row r="986" spans="2:12" x14ac:dyDescent="0.45">
@@ -79750,7 +79750,7 @@
         <v>0.33123000000000008</v>
       </c>
       <c r="L986">
-        <v>0.30111829807806606</v>
+        <v>0.301118298078066</v>
       </c>
     </row>
     <row r="987" spans="2:12" x14ac:dyDescent="0.45">
@@ -81867,19 +81867,19 @@
         <v>2025</v>
       </c>
       <c r="F1047">
-        <v>5.1299999999999998E-2</v>
+        <v>2.2800000000000001E-2</v>
       </c>
       <c r="G1047">
         <v>1</v>
       </c>
       <c r="H1047">
-        <v>1563.9999999999998</v>
+        <v>1836</v>
       </c>
       <c r="I1047">
-        <v>39.6</v>
+        <v>46.800000000000004</v>
       </c>
       <c r="J1047">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="K1047">
         <v>30</v>
@@ -81902,19 +81902,19 @@
         <v>2025</v>
       </c>
       <c r="F1048">
-        <v>2.2800000000000001E-2</v>
+        <v>5.1299999999999998E-2</v>
       </c>
       <c r="G1048">
         <v>1</v>
       </c>
       <c r="H1048">
-        <v>1836</v>
+        <v>1563.9999999999998</v>
       </c>
       <c r="I1048">
-        <v>46.800000000000004</v>
+        <v>39.6</v>
       </c>
       <c r="J1048">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="K1048">
         <v>30</v>
@@ -83644,7 +83644,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F624056-50CE-44E8-A8BF-1786D37BEF1E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4302522F-3036-4E53-AEC2-E48F71C7F386}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_BRA_grids/vt_vervestacks_BRA_v1.xlsx
+++ b/VerveStacks_BRA_grids/vt_vervestacks_BRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8CD44062-27E0-4AE6-AE5A-38602934C6E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A226535B-F176-4C1B-B128-B0A08796ED42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{312119E4-57ED-446A-BCC5-A2C967D02897}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{99EFC442-FED1-4AF6-90EA-54AD6C6FB697}"/>
   </bookViews>
   <sheets>
     <sheet name="additional_hydro_pot" sheetId="5" r:id="rId1"/>
@@ -7370,7 +7370,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2239CCDC-82AC-4A69-B5A2-8012B25BB23B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F15016C1-EA46-4938-A650-8DDABFCBA226}">
   <dimension ref="B9:O18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7757,7 +7757,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C26D3FCF-A653-425E-AA74-596E35A8767D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C620490-20C9-41C4-9558-A5B29EA3FE05}">
   <dimension ref="B9:T192"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -18023,7 +18023,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58F98D74-E1C7-410E-9703-005A7637FCA0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7890ED53-7498-486F-81BF-68C5EEF4ED1C}">
   <dimension ref="B9:T295"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -33772,7 +33772,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51D5B73A-D99D-4023-89EF-0334237B38A9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{521A6098-8295-4DB5-8BEF-6A57EC950380}">
   <dimension ref="B9:T1104"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -34567,7 +34567,7 @@
         <v>36</v>
       </c>
       <c r="P24" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="Q24" t="s">
         <v>991</v>
@@ -34620,7 +34620,7 @@
         <v>36</v>
       </c>
       <c r="P25" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="Q25" t="s">
         <v>991</v>
@@ -44849,7 +44849,7 @@
         <v>289</v>
       </c>
       <c r="P218" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="Q218" t="s">
         <v>991</v>
@@ -44902,7 +44902,7 @@
         <v>289</v>
       </c>
       <c r="P219" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="Q219" t="s">
         <v>991</v>
@@ -64836,7 +64836,7 @@
         <v>819</v>
       </c>
       <c r="P613" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="Q613" t="s">
         <v>991</v>
@@ -64889,7 +64889,7 @@
         <v>819</v>
       </c>
       <c r="P614" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="Q614" t="s">
         <v>991</v>
@@ -64995,7 +64995,7 @@
         <v>823</v>
       </c>
       <c r="P616" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="Q616" t="s">
         <v>991</v>
@@ -65048,7 +65048,7 @@
         <v>823</v>
       </c>
       <c r="P617" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="Q617" t="s">
         <v>991</v>
@@ -65101,7 +65101,7 @@
         <v>825</v>
       </c>
       <c r="P618" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="Q618" t="s">
         <v>991</v>
@@ -65154,7 +65154,7 @@
         <v>825</v>
       </c>
       <c r="P619" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="Q619" t="s">
         <v>991</v>
@@ -66161,7 +66161,7 @@
         <v>858</v>
       </c>
       <c r="P638" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="Q638" t="s">
         <v>991</v>
@@ -66214,7 +66214,7 @@
         <v>858</v>
       </c>
       <c r="P639" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="Q639" t="s">
         <v>991</v>
@@ -66770,7 +66770,7 @@
         <v>872</v>
       </c>
       <c r="P650" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="Q650" t="s">
         <v>991</v>
@@ -66826,7 +66826,7 @@
         <v>872</v>
       </c>
       <c r="P651" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="Q651" t="s">
         <v>991</v>
@@ -69234,7 +69234,7 @@
         <v>953</v>
       </c>
       <c r="P694" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="Q694" t="s">
         <v>991</v>
@@ -69290,7 +69290,7 @@
         <v>953</v>
       </c>
       <c r="P695" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="Q695" t="s">
         <v>991</v>
@@ -84010,7 +84010,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40C3720A-72DF-490C-981F-53CF8F307AB8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{304D4898-D259-45DA-A98A-99EA2C7BD4E8}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
